--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0740A181-7A61-4B51-99A6-5F783EC08746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4075880-9274-485C-9C33-A26211BDBB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20520" yWindow="2970" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23085" yWindow="2805" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="122">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -440,6 +443,14 @@
   </si>
   <si>
     <t>\</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id_sample_val</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(10,20)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -766,21 +777,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.75" customWidth="1"/>
     <col min="2" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="9.125" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="1" customWidth="1"/>
-    <col min="6" max="7" width="10.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="9.375" customWidth="1"/>
+    <col min="4" max="5" width="9.125" customWidth="1"/>
+    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="10.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,38 +805,41 @@
         <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -839,40 +853,43 @@
         <v>111</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="I2" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O2" t="s">
         <v>115</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P2" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -886,40 +903,43 @@
         <v>111</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="I3" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="N3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" t="s">
         <v>118</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -933,40 +953,43 @@
         <v>111</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N4" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O4" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -980,40 +1003,43 @@
         <v>111</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N5" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1027,40 +1053,43 @@
         <v>111</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O6" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1074,40 +1103,43 @@
         <v>111</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N7" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O7" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1121,40 +1153,43 @@
         <v>111</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O8" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1168,40 +1203,43 @@
         <v>111</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O9" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1215,40 +1253,43 @@
         <v>111</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O10" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -1262,40 +1303,43 @@
         <v>111</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O11" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1309,40 +1353,43 @@
         <v>111</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N12" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O12" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1356,40 +1403,43 @@
         <v>111</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O13" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1403,40 +1453,43 @@
         <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N14" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O14" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,40 +1503,43 @@
         <v>111</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="H15" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O15" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
@@ -1497,40 +1553,43 @@
         <v>111</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O16" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1544,40 +1603,43 @@
         <v>111</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O17" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
@@ -1591,40 +1653,43 @@
         <v>112</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="N18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1638,40 +1703,43 @@
         <v>112</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="N19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1685,40 +1753,43 @@
         <v>112</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" t="s">
+      <c r="N20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O20" t="s">
         <v>113</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -1732,40 +1803,43 @@
         <v>112</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N21" t="s">
+      <c r="N21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O21" t="s">
         <v>113</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -1779,40 +1853,43 @@
         <v>112</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="N22" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
@@ -1826,40 +1903,43 @@
         <v>112</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="N23" s="1" t="s">
         <v>54</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>68</v>
       </c>
@@ -1873,40 +1953,43 @@
         <v>112</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" t="s">
+      <c r="N24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O24" t="s">
         <v>114</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>69</v>
       </c>
@@ -1920,40 +2003,43 @@
         <v>112</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" t="s">
+      <c r="N25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O25" t="s">
         <v>114</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -1967,40 +2053,43 @@
         <v>111</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="L26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="N26" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O26" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>83</v>
       </c>
@@ -2014,36 +2103,39 @@
         <v>111</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>100</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="L27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>119</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4075880-9274-485C-9C33-A26211BDBB00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F700A097-AF1A-48B0-A6C5-24177BE83A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23085" yWindow="2805" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="126">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -451,6 +451,22 @@
   </si>
   <si>
     <t>(10,20)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,21 +793,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.75" customWidth="1"/>
-    <col min="2" max="3" width="5" customWidth="1"/>
-    <col min="4" max="5" width="9.125" customWidth="1"/>
-    <col min="6" max="6" width="12.25" style="1" customWidth="1"/>
-    <col min="7" max="8" width="10.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
+    <col min="2" max="4" width="5" customWidth="1"/>
+    <col min="5" max="6" width="9.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
+    <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -802,44 +818,47 @@
         <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="M1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -850,46 +869,49 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>96</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q2" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>93</v>
       </c>
@@ -900,46 +922,49 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>96</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K3" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O3" t="s">
+      <c r="O3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" t="s">
         <v>118</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q3" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -950,46 +975,49 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P4" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1000,46 +1028,49 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P5" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1050,46 +1081,49 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P6" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1100,46 +1134,49 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P7" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -1150,46 +1187,49 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P8" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1200,46 +1240,49 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P9" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
@@ -1250,46 +1293,49 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I10" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P10" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -1300,46 +1346,49 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F11" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I11" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K11" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="N11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="O11" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O11" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P11" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
@@ -1350,46 +1399,49 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F12" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I12" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P12" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1400,46 +1452,49 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I13" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P13" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
@@ -1450,46 +1505,49 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F14" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P14" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
@@ -1500,46 +1558,49 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P15" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>40</v>
       </c>
@@ -1550,46 +1611,49 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P16" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1600,46 +1664,49 @@
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P17" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
@@ -1650,46 +1717,49 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O18" s="1" t="s">
         <v>54</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1700,46 +1770,49 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O19" s="1" t="s">
         <v>54</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>58</v>
       </c>
@@ -1750,46 +1823,49 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F20" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="N20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="O20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P20" t="s">
         <v>113</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>59</v>
       </c>
@@ -1800,46 +1876,49 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F21" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="O21" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P21" t="s">
         <v>113</v>
       </c>
-      <c r="P21" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>66</v>
       </c>
@@ -1850,46 +1929,49 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F22" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O22" s="1" t="s">
         <v>54</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>67</v>
       </c>
@@ -1900,46 +1982,49 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="N23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="N23" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O23" s="1" t="s">
         <v>54</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>68</v>
       </c>
@@ -1950,46 +2035,49 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O24" t="s">
+      <c r="O24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P24" t="s">
         <v>114</v>
       </c>
-      <c r="P24" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>69</v>
       </c>
@@ -2000,46 +2088,49 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>101</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="O25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P25" t="s">
         <v>114</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>82</v>
       </c>
@@ -2050,46 +2141,49 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P26" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>83</v>
       </c>
@@ -2100,42 +2194,45 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F27" s="1" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>100</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="M27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O27" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="P27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q27" s="1" t="s">
         <v>119</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F700A097-AF1A-48B0-A6C5-24177BE83A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2331A3-A70D-40C7-8D35-8DF0CA5882B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20625" yWindow="2475" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2331A3-A70D-40C7-8D35-8DF0CA5882B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A371C36-0949-4A89-AE42-01A853DECECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20625" yWindow="2475" windowWidth="14130" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="259">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,18 +54,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\gt_sf_1</t>
-  </si>
-  <si>
     <t>I:\Datasets\BioSR\F-actin_Nonlinear\train.txt</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\Microtubules2\raw_noise_9</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\gt_sf_1</t>
-  </si>
-  <si>
     <t>SimuBeads3D-128-31-0-0-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -435,10 +426,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\raw_noise_9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>E:\qiqilu\Project\2023 cytoSR\code\checkpoints\Microtubules2\forward\kernet_fp_bs_1_lr_0.001_ker_31_gauss_9_poiss_1_sf_1_mse_over2_inter_normx_fft_ratio_1_ts_0_1_s100\epoch_500.pt</t>
   </si>
   <si>
@@ -467,6 +454,513 @@
   </si>
   <si>
     <t>0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-7</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-6</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-5</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-4</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-3</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-2</t>
+  </si>
+  <si>
+    <t>F-actin-nonlinear-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>Microtubules2-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-3</t>
+  </si>
+  <si>
+    <t>Microtubules2-2</t>
+  </si>
+  <si>
+    <t>Microtubules2-1</t>
+  </si>
+  <si>
+    <t>Microtubules2-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\test.txt</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-7</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-6</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-5</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\test.txt</t>
+  </si>
+  <si>
+    <t>F-actin-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-10</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-9</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-8</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-7</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-6</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-5</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\test.txt</t>
+  </si>
+  <si>
+    <t>ER-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\gt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,9 +1004,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -793,53 +1293,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.75" customWidth="1"/>
-    <col min="2" max="4" width="5" customWidth="1"/>
+    <col min="1" max="1" width="33.25" customWidth="1"/>
+    <col min="2" max="3" width="5" style="3" customWidth="1"/>
+    <col min="4" max="4" width="5" style="2" customWidth="1"/>
     <col min="5" max="6" width="9.125" customWidth="1"/>
     <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
     <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="9.375" customWidth="1"/>
+    <col min="12" max="12" width="53.375" customWidth="1"/>
+    <col min="13" max="13" width="37.875" customWidth="1"/>
+    <col min="14" max="14" width="46.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>2</v>
@@ -851,10 +1353,10 @@
         <v>4</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q1" s="1"/>
     </row>
@@ -862,1378 +1364,3447 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>2</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>123</v>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P2" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="Q2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P3" t="s">
-        <v>118</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>119</v>
+      </c>
       <c r="E4" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>15</v>
+        <v>138</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1">
-        <v>3</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>16</v>
+        <v>139</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>18</v>
+        <v>147</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>18</v>
+        <v>149</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
+      </c>
+      <c r="P11" t="s">
+        <v>114</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>123</v>
+        <v>150</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>123</v>
+        <v>154</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="1">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>124</v>
+        <v>155</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="1">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>125</v>
+        <v>156</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>37</v>
+        <v>161</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>123</v>
+        <v>157</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>123</v>
+        <v>151</v>
+      </c>
+      <c r="B17" s="2">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>123</v>
+        <v>152</v>
+      </c>
+      <c r="B18" s="2">
+        <v>2</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="L18" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="Q18" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>174</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L20" t="s">
+        <v>175</v>
+      </c>
+      <c r="M20" t="s">
+        <v>176</v>
+      </c>
+      <c r="N20" t="s">
+        <v>177</v>
+      </c>
+      <c r="O20" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L21" t="s">
+        <v>180</v>
+      </c>
+      <c r="M21" t="s">
+        <v>181</v>
+      </c>
+      <c r="N21" t="s">
+        <v>177</v>
+      </c>
+      <c r="O21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>182</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L22" t="s">
+        <v>183</v>
+      </c>
+      <c r="M22" t="s">
+        <v>184</v>
+      </c>
+      <c r="N22" t="s">
+        <v>177</v>
+      </c>
+      <c r="O22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>185</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23" t="s">
+        <v>186</v>
+      </c>
+      <c r="M23" t="s">
+        <v>187</v>
+      </c>
+      <c r="N23" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L24" t="s">
+        <v>189</v>
+      </c>
+      <c r="M24" t="s">
+        <v>190</v>
+      </c>
+      <c r="N24" t="s">
+        <v>177</v>
+      </c>
+      <c r="O24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L25" t="s">
+        <v>192</v>
+      </c>
+      <c r="M25" t="s">
+        <v>193</v>
+      </c>
+      <c r="N25" t="s">
+        <v>177</v>
+      </c>
+      <c r="O25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>194</v>
+      </c>
+      <c r="B26" s="3">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L26" t="s">
+        <v>195</v>
+      </c>
+      <c r="M26" t="s">
+        <v>196</v>
+      </c>
+      <c r="N26" t="s">
+        <v>177</v>
+      </c>
+      <c r="O26" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>197</v>
+      </c>
+      <c r="B27" s="3">
+        <v>2</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L27" t="s">
+        <v>198</v>
+      </c>
+      <c r="M27" t="s">
+        <v>199</v>
+      </c>
+      <c r="N27" t="s">
+        <v>177</v>
+      </c>
+      <c r="O27" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>200</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L28" t="s">
+        <v>201</v>
+      </c>
+      <c r="M28" t="s">
+        <v>202</v>
+      </c>
+      <c r="N28" t="s">
+        <v>177</v>
+      </c>
+      <c r="O28" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>203</v>
+      </c>
+      <c r="B29" s="3">
+        <v>2</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L29" t="s">
+        <v>204</v>
+      </c>
+      <c r="M29" t="s">
+        <v>205</v>
+      </c>
+      <c r="N29" t="s">
+        <v>206</v>
+      </c>
+      <c r="O29" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>207</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="2">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L30" t="s">
+        <v>208</v>
+      </c>
+      <c r="M30" t="s">
+        <v>209</v>
+      </c>
+      <c r="N30" t="s">
+        <v>206</v>
+      </c>
+      <c r="O30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L31" t="s">
+        <v>211</v>
+      </c>
+      <c r="M31" t="s">
+        <v>212</v>
+      </c>
+      <c r="N31" t="s">
+        <v>206</v>
+      </c>
+      <c r="O31" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" s="3">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L32" t="s">
+        <v>214</v>
+      </c>
+      <c r="M32" t="s">
+        <v>215</v>
+      </c>
+      <c r="N32" t="s">
+        <v>206</v>
+      </c>
+      <c r="O32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="2">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L33" t="s">
+        <v>217</v>
+      </c>
+      <c r="M33" t="s">
+        <v>218</v>
+      </c>
+      <c r="N33" t="s">
+        <v>206</v>
+      </c>
+      <c r="O33" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>219</v>
+      </c>
+      <c r="B34" s="3">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L34" t="s">
+        <v>220</v>
+      </c>
+      <c r="M34" t="s">
+        <v>221</v>
+      </c>
+      <c r="N34" t="s">
+        <v>206</v>
+      </c>
+      <c r="O34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B35" s="3">
+        <v>2</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="2">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L35" t="s">
+        <v>223</v>
+      </c>
+      <c r="M35" t="s">
+        <v>224</v>
+      </c>
+      <c r="N35" t="s">
+        <v>206</v>
+      </c>
+      <c r="O35" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>225</v>
+      </c>
+      <c r="B36" s="3">
+        <v>2</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L36" t="s">
+        <v>226</v>
+      </c>
+      <c r="M36" t="s">
+        <v>227</v>
+      </c>
+      <c r="N36" t="s">
+        <v>206</v>
+      </c>
+      <c r="O36" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B37" s="3">
+        <v>2</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+      <c r="D37" s="2">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L37" t="s">
+        <v>229</v>
+      </c>
+      <c r="M37" t="s">
+        <v>230</v>
+      </c>
+      <c r="N37" t="s">
+        <v>206</v>
+      </c>
+      <c r="O37" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>231</v>
+      </c>
+      <c r="B38" s="3">
+        <v>2</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="2">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" t="s">
+        <v>232</v>
+      </c>
+      <c r="M38" t="s">
+        <v>233</v>
+      </c>
+      <c r="N38" t="s">
+        <v>206</v>
+      </c>
+      <c r="O38" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="3">
+        <v>2</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" t="s">
+        <v>235</v>
+      </c>
+      <c r="M39" t="s">
+        <v>236</v>
+      </c>
+      <c r="N39" t="s">
+        <v>206</v>
+      </c>
+      <c r="O39" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>237</v>
+      </c>
+      <c r="B40" s="3">
+        <v>2</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L40" t="s">
+        <v>238</v>
+      </c>
+      <c r="M40" t="s">
+        <v>239</v>
+      </c>
+      <c r="N40" t="s">
+        <v>206</v>
+      </c>
+      <c r="O40" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="3">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L41" t="s">
+        <v>241</v>
+      </c>
+      <c r="M41" t="s">
+        <v>242</v>
+      </c>
+      <c r="N41" t="s">
+        <v>243</v>
+      </c>
+      <c r="O41" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>244</v>
+      </c>
+      <c r="B42" s="3">
+        <v>2</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="2">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L42" t="s">
+        <v>245</v>
+      </c>
+      <c r="M42" t="s">
+        <v>246</v>
+      </c>
+      <c r="N42" t="s">
+        <v>243</v>
+      </c>
+      <c r="O42" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>247</v>
+      </c>
+      <c r="B43" s="3">
+        <v>2</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="2">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L43" t="s">
+        <v>248</v>
+      </c>
+      <c r="M43" t="s">
+        <v>249</v>
+      </c>
+      <c r="N43" t="s">
+        <v>243</v>
+      </c>
+      <c r="O43" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>250</v>
+      </c>
+      <c r="B44" s="3">
+        <v>2</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="2">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L44" t="s">
+        <v>251</v>
+      </c>
+      <c r="M44" t="s">
+        <v>252</v>
+      </c>
+      <c r="N44" t="s">
+        <v>243</v>
+      </c>
+      <c r="O44" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>253</v>
+      </c>
+      <c r="B45" s="3">
+        <v>2</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L45" t="s">
+        <v>254</v>
+      </c>
+      <c r="M45" t="s">
+        <v>255</v>
+      </c>
+      <c r="N45" t="s">
+        <v>243</v>
+      </c>
+      <c r="O45" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>256</v>
+      </c>
+      <c r="B46" s="3">
+        <v>2</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="2">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L46" t="s">
+        <v>257</v>
+      </c>
+      <c r="M46" t="s">
+        <v>258</v>
+      </c>
+      <c r="N46" t="s">
+        <v>243</v>
+      </c>
+      <c r="O46" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2">
+        <v>3</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="2">
+        <v>3</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2">
+        <v>3</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" s="2">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="2">
+        <v>3</v>
+      </c>
+      <c r="C51" s="2">
+        <v>1</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" s="2">
+        <v>3</v>
+      </c>
+      <c r="C52" s="2">
+        <v>1</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53" s="2">
+        <v>3</v>
+      </c>
+      <c r="C53" s="2">
+        <v>1</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="2">
+        <v>3</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" s="2">
+        <v>3</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="2">
+        <v>3</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" s="2">
+        <v>3</v>
+      </c>
+      <c r="C57" s="2">
+        <v>1</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="2">
+        <v>3</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="2">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="2">
+        <v>3</v>
+      </c>
+      <c r="C60" s="2">
+        <v>1</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A61" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B61" s="2">
+        <v>3</v>
+      </c>
+      <c r="C61" s="2">
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N61" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="1">
+      <c r="O61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B62" s="2">
         <v>3</v>
       </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="C62" s="2">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I62" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="J62" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A63" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" s="2">
+        <v>3</v>
+      </c>
+      <c r="C63" s="2">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M19" s="1" t="s">
+      <c r="J63" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P63" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q19" s="1" t="s">
+      <c r="B64" s="2">
+        <v>3</v>
+      </c>
+      <c r="C64" s="2">
+        <v>1</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="E64" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L64" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="1">
+      <c r="M64" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P64" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
         <v>3</v>
       </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="C65" s="2">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I65" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="J65" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>3</v>
+      </c>
+      <c r="C66" s="2">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I66" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P20" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q20" s="1" t="s">
+      <c r="J66" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>3</v>
+      </c>
+      <c r="C67" s="2">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="1">
+      <c r="E67" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P67" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
         <v>3</v>
       </c>
-      <c r="C21" s="1">
-        <v>1</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="C68" s="2">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I68" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="J68" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P68" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="2">
+        <v>3</v>
+      </c>
+      <c r="C69" s="2">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I69" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P21" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q21" s="1" t="s">
+      <c r="J69" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B70" s="2">
+        <v>3</v>
+      </c>
+      <c r="C70" s="2">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="E70" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="1">
-        <v>3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P24" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P25" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L26" s="1" t="s">
+      <c r="J70" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="1" t="s">
+      <c r="O70" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>119</v>
+      <c r="P70" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A371C36-0949-4A89-AE42-01A853DECECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767730ED-0772-46FD-AF56-84D48FCCBFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2580" yWindow="1845" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="253">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -397,10 +397,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>path_fp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>id_sample</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -413,26 +409,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E:\qiqilu\Project\2023 cytoSR\code\checkpoints\Microtubule2\forward\kernet_fp_bs_4_lr_0.01_ker_3_gauss_0_poiss_0_sf_1_mse_over2_inter_normx_fft_ratio_1_ts_0_4_s100\epoch_500.pt</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\Project\2023 cytoSR\code\checkpoints\Nuclear_Pore_complex2\forward\kernet_fp_bs_4_lr_0.01_ker_3_gauss_0_poiss_0_sf_1_mse_over2_inter_normx_fft_ratio_1_ts_0_4_s100\epoch_500.pt</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\Project\2023 cytoSR\code\checkpoints\F-actin_Nonlinear\forward\kernet_fp_bs_1_lr_0.001_ker_31_gauss_9_poiss_1_sf_1_mse_over2_inter_normx_fft_ratio_1_ts_0_1_s100\epoch_500.pt</t>
-  </si>
-  <si>
     <t>I:\Datasets\BioSR\Microtubules2\train.txt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>E:\qiqilu\Project\2023 cytoSR\code\checkpoints\Microtubules2\forward\kernet_fp_bs_1_lr_0.001_ker_31_gauss_9_poiss_1_sf_1_mse_over2_inter_normx_fft_ratio_1_ts_0_1_s100\epoch_500.pt</t>
-  </si>
-  <si>
-    <t>\</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>id_sample_val</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -479,488 +459,489 @@
     <t>F-actin-nonlinear-2</t>
   </si>
   <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>Microtubules2-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-3</t>
+  </si>
+  <si>
+    <t>Microtubules2-2</t>
+  </si>
+  <si>
+    <t>Microtubules2-1</t>
+  </si>
+  <si>
+    <t>Microtubules2-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Microtubules2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-7</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-6</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-5</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CCPs-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-10</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-9</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-8</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-7</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-6</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-5</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-actin-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>ER-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-4</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-2</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ER-1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\gt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\CCPs\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\F-actin\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioSR\ER\train.txt</t>
+  </si>
+  <si>
     <t>F-actin-nonlinear-1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\gt</t>
-  </si>
-  <si>
-    <t>Microtubules2-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubules2-3</t>
-  </si>
-  <si>
-    <t>Microtubules2-2</t>
-  </si>
-  <si>
-    <t>Microtubules2-1</t>
-  </si>
-  <si>
-    <t>Microtubules2-7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubules2-6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubules2-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Microtubules2-4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-9</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\test.txt</t>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-7</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-6</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-5</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-4</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-2</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CCPs-1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-12</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\test.txt</t>
-  </si>
-  <si>
-    <t>F-actin-11</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-10</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-9</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-8</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-7</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-6</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-5</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-4</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-2</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>F-actin-1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ER-6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\test.txt</t>
-  </si>
-  <si>
-    <t>ER-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ER-4</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ER-3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ER-2</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ER-1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\gt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1293,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -1304,12 +1285,12 @@
     <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="53.375" customWidth="1"/>
-    <col min="13" max="13" width="37.875" customWidth="1"/>
-    <col min="14" max="14" width="46.875" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="9.125" customWidth="1"/>
+    <col min="14" max="14" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1320,13 +1301,13 @@
         <v>96</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>91</v>
@@ -1355,12 +1336,8 @@
       <c r="O1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1371,13 +1348,13 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>93</v>
@@ -1395,10 +1372,10 @@
         <v>105</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>6</v>
@@ -1406,16 +1383,10 @@
       <c r="O2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P2" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1424,13 +1395,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>93</v>
@@ -1448,10 +1419,10 @@
         <v>105</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
@@ -1459,13 +1430,10 @@
       <c r="O3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -1474,13 +1442,13 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>93</v>
@@ -1498,10 +1466,10 @@
         <v>105</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>6</v>
@@ -1509,13 +1477,10 @@
       <c r="O4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q4" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -1524,13 +1489,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>93</v>
@@ -1548,10 +1513,10 @@
         <v>105</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>6</v>
@@ -1559,13 +1524,10 @@
       <c r="O5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q5" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1574,13 +1536,13 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>93</v>
@@ -1598,10 +1560,10 @@
         <v>105</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>6</v>
@@ -1609,13 +1571,10 @@
       <c r="O6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -1624,13 +1583,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>93</v>
@@ -1648,10 +1607,10 @@
         <v>105</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>6</v>
@@ -1659,13 +1618,10 @@
       <c r="O7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -1674,13 +1630,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>93</v>
@@ -1698,10 +1654,10 @@
         <v>105</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>6</v>
@@ -1709,13 +1665,10 @@
       <c r="O8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -1724,13 +1677,13 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>93</v>
@@ -1748,10 +1701,10 @@
         <v>105</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>6</v>
@@ -1759,13 +1712,10 @@
       <c r="O9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1774,13 +1724,13 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>93</v>
@@ -1798,10 +1748,10 @@
         <v>105</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>6</v>
@@ -1809,11 +1759,8 @@
       <c r="O10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>90</v>
       </c>
@@ -1824,13 +1771,13 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>93</v>
@@ -1848,27 +1795,21 @@
         <v>105</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P11" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1877,13 +1818,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>93</v>
@@ -1901,24 +1842,21 @@
         <v>105</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q12" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1927,13 +1865,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>93</v>
@@ -1951,24 +1889,21 @@
         <v>105</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -1977,13 +1912,13 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>93</v>
@@ -2001,24 +1936,21 @@
         <v>105</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q14" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -2027,13 +1959,13 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>93</v>
@@ -2051,24 +1983,21 @@
         <v>105</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2077,13 +2006,13 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>93</v>
@@ -2101,24 +2030,21 @@
         <v>105</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q16" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2127,13 +2053,13 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>93</v>
@@ -2151,24 +2077,21 @@
         <v>105</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q17" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2177,13 +2100,13 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>93</v>
@@ -2201,24 +2124,21 @@
         <v>105</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q18" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
@@ -2227,13 +2147,13 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>93</v>
@@ -2251,24 +2171,21 @@
         <v>105</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Q19" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B20" s="3">
         <v>2</v>
@@ -2280,10 +2197,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>93</v>
@@ -2301,21 +2218,21 @@
         <v>105</v>
       </c>
       <c r="L20" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="M20" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="N20" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O20" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
@@ -2327,10 +2244,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>93</v>
@@ -2348,21 +2265,21 @@
         <v>105</v>
       </c>
       <c r="L21" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="N21" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -2374,10 +2291,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>93</v>
@@ -2395,21 +2312,21 @@
         <v>105</v>
       </c>
       <c r="L22" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="M22" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="N22" t="s">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>177</v>
-      </c>
-      <c r="O22" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>185</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -2421,10 +2338,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>93</v>
@@ -2442,21 +2359,21 @@
         <v>105</v>
       </c>
       <c r="L23" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="M23" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="N23" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O23" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
@@ -2468,10 +2385,10 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>93</v>
@@ -2489,21 +2406,21 @@
         <v>105</v>
       </c>
       <c r="L24" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="M24" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="N24" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -2515,10 +2432,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>93</v>
@@ -2536,21 +2453,21 @@
         <v>105</v>
       </c>
       <c r="L25" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="N25" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
@@ -2562,10 +2479,10 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>93</v>
@@ -2583,21 +2500,21 @@
         <v>105</v>
       </c>
       <c r="L26" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M26" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N26" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O26" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B27" s="3">
         <v>2</v>
@@ -2609,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>93</v>
@@ -2630,21 +2547,21 @@
         <v>105</v>
       </c>
       <c r="L27" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M27" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N27" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -2656,10 +2573,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>93</v>
@@ -2677,21 +2594,21 @@
         <v>105</v>
       </c>
       <c r="L28" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="M28" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="N28" t="s">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B29" s="3">
         <v>2</v>
@@ -2703,10 +2620,10 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>93</v>
@@ -2724,21 +2641,21 @@
         <v>105</v>
       </c>
       <c r="L29" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M29" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="N29" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B30" s="3">
         <v>2</v>
@@ -2750,10 +2667,10 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>93</v>
@@ -2771,21 +2688,21 @@
         <v>105</v>
       </c>
       <c r="L30" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="M30" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="N30" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B31" s="3">
         <v>2</v>
@@ -2797,10 +2714,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>93</v>
@@ -2818,21 +2735,21 @@
         <v>105</v>
       </c>
       <c r="L31" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="M31" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="N31" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B32" s="3">
         <v>2</v>
@@ -2844,10 +2761,10 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>93</v>
@@ -2865,21 +2782,21 @@
         <v>105</v>
       </c>
       <c r="L32" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M32" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N32" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
@@ -2891,10 +2808,10 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>93</v>
@@ -2912,21 +2829,21 @@
         <v>105</v>
       </c>
       <c r="L33" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="M33" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="N33" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O33" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3">
         <v>2</v>
@@ -2938,10 +2855,10 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>93</v>
@@ -2959,21 +2876,21 @@
         <v>105</v>
       </c>
       <c r="L34" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="M34" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="N34" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O34" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="B35" s="3">
         <v>2</v>
@@ -2985,10 +2902,10 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>93</v>
@@ -3006,21 +2923,21 @@
         <v>105</v>
       </c>
       <c r="L35" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="M35" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="N35" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O35" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B36" s="3">
         <v>2</v>
@@ -3032,10 +2949,10 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>93</v>
@@ -3053,21 +2970,21 @@
         <v>105</v>
       </c>
       <c r="L36" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M36" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="N36" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O36" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>2</v>
@@ -3079,10 +2996,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>93</v>
@@ -3100,21 +3017,21 @@
         <v>105</v>
       </c>
       <c r="L37" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="M37" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="N37" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O37" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B38" s="3">
         <v>2</v>
@@ -3126,10 +3043,10 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>93</v>
@@ -3147,21 +3064,21 @@
         <v>105</v>
       </c>
       <c r="L38" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M38" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N38" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O38" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B39" s="3">
         <v>2</v>
@@ -3173,10 +3090,10 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>93</v>
@@ -3194,21 +3111,21 @@
         <v>105</v>
       </c>
       <c r="L39" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M39" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N39" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O39" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="B40" s="3">
         <v>2</v>
@@ -3220,10 +3137,10 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>93</v>
@@ -3241,21 +3158,21 @@
         <v>105</v>
       </c>
       <c r="L40" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="M40" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="N40" t="s">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="O40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B41" s="3">
         <v>2</v>
@@ -3267,10 +3184,10 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>93</v>
@@ -3288,21 +3205,21 @@
         <v>105</v>
       </c>
       <c r="L41" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M41" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="N41" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O41" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
@@ -3314,10 +3231,10 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>93</v>
@@ -3335,21 +3252,21 @@
         <v>105</v>
       </c>
       <c r="L42" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="M42" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="N42" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O42" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B43" s="3">
         <v>2</v>
@@ -3361,10 +3278,10 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>93</v>
@@ -3382,21 +3299,21 @@
         <v>105</v>
       </c>
       <c r="L43" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M43" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N43" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O43" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3">
         <v>2</v>
@@ -3408,10 +3325,10 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>93</v>
@@ -3429,21 +3346,21 @@
         <v>105</v>
       </c>
       <c r="L44" t="s">
+        <v>241</v>
+      </c>
+      <c r="M44" t="s">
+        <v>242</v>
+      </c>
+      <c r="N44" t="s">
         <v>251</v>
       </c>
-      <c r="M44" t="s">
-        <v>252</v>
-      </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
         <v>243</v>
-      </c>
-      <c r="O44" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>253</v>
       </c>
       <c r="B45" s="3">
         <v>2</v>
@@ -3455,10 +3372,10 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>93</v>
@@ -3476,21 +3393,21 @@
         <v>105</v>
       </c>
       <c r="L45" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="M45" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="N45" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O45" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B46" s="3">
         <v>2</v>
@@ -3502,10 +3419,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>93</v>
@@ -3523,19 +3440,19 @@
         <v>105</v>
       </c>
       <c r="L46" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="M46" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="N46" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="O46" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>7</v>
       </c>
@@ -3546,13 +3463,13 @@
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>94</v>
@@ -3581,14 +3498,8 @@
       <c r="O47" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P47" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>8</v>
       </c>
@@ -3599,13 +3510,13 @@
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>94</v>
@@ -3634,14 +3545,8 @@
       <c r="O48" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P48" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>9</v>
       </c>
@@ -3652,13 +3557,13 @@
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>94</v>
@@ -3687,14 +3592,8 @@
       <c r="O49" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>10</v>
       </c>
@@ -3705,13 +3604,13 @@
         <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>94</v>
@@ -3740,14 +3639,8 @@
       <c r="O50" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>17</v>
       </c>
@@ -3758,13 +3651,13 @@
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>94</v>
@@ -3793,14 +3686,8 @@
       <c r="O51" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>18</v>
       </c>
@@ -3811,13 +3698,13 @@
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>94</v>
@@ -3846,14 +3733,8 @@
       <c r="O52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -3864,13 +3745,13 @@
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>94</v>
@@ -3899,14 +3780,8 @@
       <c r="O53" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
@@ -3917,13 +3792,13 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>94</v>
@@ -3952,14 +3827,8 @@
       <c r="O54" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
@@ -3970,13 +3839,13 @@
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>94</v>
@@ -4005,14 +3874,8 @@
       <c r="O55" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
@@ -4023,13 +3886,13 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>94</v>
@@ -4058,14 +3921,8 @@
       <c r="O56" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>23</v>
       </c>
@@ -4076,13 +3933,13 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>94</v>
@@ -4111,14 +3968,8 @@
       <c r="O57" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>24</v>
       </c>
@@ -4129,13 +3980,13 @@
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>94</v>
@@ -4164,14 +4015,8 @@
       <c r="O58" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P58" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>37</v>
       </c>
@@ -4182,13 +4027,13 @@
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>97</v>
@@ -4217,14 +4062,8 @@
       <c r="O59" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>38</v>
       </c>
@@ -4235,13 +4074,13 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>97</v>
@@ -4270,14 +4109,8 @@
       <c r="O60" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="P60" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>46</v>
       </c>
@@ -4288,13 +4121,13 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>98</v>
@@ -4323,14 +4156,8 @@
       <c r="O61" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>47</v>
       </c>
@@ -4341,13 +4168,13 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>98</v>
@@ -4376,14 +4203,8 @@
       <c r="O62" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>55</v>
       </c>
@@ -4394,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>98</v>
@@ -4429,14 +4250,8 @@
       <c r="O63" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P63" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>56</v>
       </c>
@@ -4447,13 +4262,13 @@
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>98</v>
@@ -4482,14 +4297,8 @@
       <c r="O64" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P64" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
@@ -4500,13 +4309,13 @@
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>98</v>
@@ -4535,14 +4344,8 @@
       <c r="O65" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
@@ -4553,13 +4356,13 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>98</v>
@@ -4588,14 +4391,8 @@
       <c r="O66" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
@@ -4606,13 +4403,13 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>98</v>
@@ -4641,14 +4438,8 @@
       <c r="O67" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P67" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,13 +4450,13 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>98</v>
@@ -4694,14 +4485,8 @@
       <c r="O68" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P68" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>79</v>
       </c>
@@ -4712,13 +4497,13 @@
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>97</v>
@@ -4747,14 +4532,8 @@
       <c r="O69" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>80</v>
       </c>
@@ -4765,13 +4544,13 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>97</v>
@@ -4799,12 +4578,6 @@
       </c>
       <c r="O70" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767730ED-0772-46FD-AF56-84D48FCCBFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB9648E-2010-4FF1-B0DA-14D88A2F6ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2580" yWindow="1845" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="3015" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="257">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -943,6 +943,19 @@
   <si>
     <t>F-actin-nonlinear-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SirDNA-1024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -4580,6 +4593,53 @@
         <v>85</v>
       </c>
     </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A71" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B71" s="3">
+        <v>3</v>
+      </c>
+      <c r="C71" s="3">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L71" t="s">
+        <v>255</v>
+      </c>
+      <c r="M71" t="s">
+        <v>256</v>
+      </c>
+      <c r="N71" t="s">
+        <v>254</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB9648E-2010-4FF1-B0DA-14D88A2F6ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B2638-0A9D-4EE7-8A51-13E43EB90449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="3015" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3690" yWindow="4020" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C4B2638-0A9D-4EE7-8A51-13E43EB90449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719EFF6-0F38-4C45-83AE-52308F9C0F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="4020" windowWidth="29715" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2130" yWindow="3750" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="291">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -956,6 +956,121 @@
   </si>
   <si>
     <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>biotisr-ccps-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-ccps-2</t>
+  </si>
+  <si>
+    <t>biotisr-ccps-3</t>
+  </si>
+  <si>
+    <t>biotisr-factin-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-factin-2</t>
+  </si>
+  <si>
+    <t>biotisr-factin-3</t>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-2</t>
+  </si>
+  <si>
+    <t>biotisr-factin-nonlinear-3</t>
+  </si>
+  <si>
+    <t>biotisr-mt-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-mt-2</t>
+  </si>
+  <si>
+    <t>biotisr-mt-3</t>
+  </si>
+  <si>
+    <t>biotisr-mito-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-mito-2</t>
+  </si>
+  <si>
+    <t>biotisr-mito-3</t>
+  </si>
+  <si>
+    <t>deepbacs-ecoli</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepbacs-saureus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sim-actin-3d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim3-mito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim5-mito</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim488-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim568-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vmsim647-patch-512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\SIM_2d-dn-rb_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\F-actin\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>I:\Datasets\BioTISR\transformed\F-actin\train.txt</t>
   </si>
 </sst>
 </file>
@@ -1287,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -4640,6 +4755,934 @@
         <v>51</v>
       </c>
     </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>257</v>
+      </c>
+      <c r="B72" s="3">
+        <v>2</v>
+      </c>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L72" t="s">
+        <v>283</v>
+      </c>
+      <c r="M72" t="s">
+        <v>281</v>
+      </c>
+      <c r="N72" t="s">
+        <v>282</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="3">
+        <v>2</v>
+      </c>
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L73" t="s">
+        <v>284</v>
+      </c>
+      <c r="M73" t="s">
+        <v>281</v>
+      </c>
+      <c r="N73" t="s">
+        <v>282</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>259</v>
+      </c>
+      <c r="B74" s="3">
+        <v>2</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L74" t="s">
+        <v>285</v>
+      </c>
+      <c r="M74" t="s">
+        <v>281</v>
+      </c>
+      <c r="N74" t="s">
+        <v>282</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>260</v>
+      </c>
+      <c r="B75" s="3">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L75" t="s">
+        <v>287</v>
+      </c>
+      <c r="M75" t="s">
+        <v>286</v>
+      </c>
+      <c r="N75" t="s">
+        <v>290</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>261</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L76" t="s">
+        <v>288</v>
+      </c>
+      <c r="M76" t="s">
+        <v>286</v>
+      </c>
+      <c r="N76" t="s">
+        <v>290</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>262</v>
+      </c>
+      <c r="B77" s="3">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="L77" t="s">
+        <v>289</v>
+      </c>
+      <c r="M77" t="s">
+        <v>286</v>
+      </c>
+      <c r="N77" t="s">
+        <v>290</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>263</v>
+      </c>
+      <c r="B78" s="3">
+        <v>2</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>264</v>
+      </c>
+      <c r="B79" s="3">
+        <v>2</v>
+      </c>
+      <c r="C79" s="3">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>265</v>
+      </c>
+      <c r="B80" s="3">
+        <v>2</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>266</v>
+      </c>
+      <c r="B81" s="3">
+        <v>2</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>267</v>
+      </c>
+      <c r="B82" s="3">
+        <v>2</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>268</v>
+      </c>
+      <c r="B83" s="3">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>269</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" s="3">
+        <v>2</v>
+      </c>
+      <c r="C85" s="3">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>271</v>
+      </c>
+      <c r="B86" s="3">
+        <v>2</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>272</v>
+      </c>
+      <c r="B87" s="3">
+        <v>2</v>
+      </c>
+      <c r="C87" s="3">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>273</v>
+      </c>
+      <c r="B88" s="3">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>274</v>
+      </c>
+      <c r="B89" s="3">
+        <v>2</v>
+      </c>
+      <c r="C89" s="3">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>275</v>
+      </c>
+      <c r="B90" s="3">
+        <v>2</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>276</v>
+      </c>
+      <c r="B91" s="3">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>277</v>
+      </c>
+      <c r="B92" s="3">
+        <v>2</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>278</v>
+      </c>
+      <c r="B93" s="3">
+        <v>2</v>
+      </c>
+      <c r="C93" s="3">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>279</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E719EFF6-0F38-4C45-83AE-52308F9C0F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F279F08B-E9DB-41DD-931A-5190DAA273F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="3750" windowWidth="16785" windowHeight="17190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="3930" windowWidth="23550" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,24 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\train.txt</t>
-  </si>
-  <si>
     <t>SimuMix3D-128-31-0-0-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,42 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\train.txt</t>
-  </si>
-  <si>
     <t>SimuMix3D-382-101-05-1-1-560</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -167,28 +113,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\train.txt</t>
-  </si>
-  <si>
     <t>path_psf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
-  </si>
-  <si>
     <t>Microtubule-3d-128-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -324,15 +252,6 @@
     <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw\PSF_odd.tif</t>
   </si>
   <si>
-    <t>I:\Datasets\RLN\SimuBeads3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\SimuMix3D_256\PSF_31.tif</t>
-  </si>
-  <si>
     <t>Microtubules2-9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1071,6 +990,87 @@
   </si>
   <si>
     <t>I:\Datasets\BioTISR\transformed\F-actin\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\gt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\train.txt</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
+  </si>
+  <si>
+    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
   </si>
 </sst>
 </file>
@@ -1413,7 +1413,7 @@
     <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="12" max="12" width="47.625" customWidth="1"/>
     <col min="13" max="13" width="9.125" customWidth="1"/>
     <col min="14" max="14" width="11.875" customWidth="1"/>
   </cols>
@@ -1426,31 +1426,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>2</v>
@@ -1462,7 +1462,7 @@
         <v>4</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1476,45 +1476,45 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1523,45 +1523,45 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -1570,45 +1570,45 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -1617,45 +1617,45 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="M5" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1664,45 +1664,45 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -1711,45 +1711,45 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -1758,45 +1758,45 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -1805,45 +1805,45 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1852,45 +1852,45 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>140</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1899,45 +1899,45 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1946,45 +1946,45 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1993,45 +1993,45 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -2040,45 +2040,45 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -2087,45 +2087,45 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2134,45 +2134,45 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2181,45 +2181,45 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2228,45 +2228,45 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
@@ -2275,45 +2275,45 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="B20" s="3">
         <v>2</v>
@@ -2325,42 +2325,42 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L20" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="N20" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O20" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
@@ -2372,42 +2372,42 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L21" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s">
-        <v>173</v>
+        <v>146</v>
       </c>
       <c r="N21" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O21" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -2419,42 +2419,42 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L22" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O22" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -2466,42 +2466,42 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L23" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="N23" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O23" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
@@ -2513,42 +2513,42 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L24" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="N24" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O24" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -2560,42 +2560,42 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L25" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="N25" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O25" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
@@ -2607,42 +2607,42 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L26" t="s">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s">
-        <v>188</v>
+        <v>161</v>
       </c>
       <c r="N26" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O26" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B27" s="3">
         <v>2</v>
@@ -2654,42 +2654,42 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L27" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="N27" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O27" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>165</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -2701,42 +2701,42 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L28" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="N28" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="O28" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="B29" s="3">
         <v>2</v>
@@ -2748,42 +2748,42 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L29" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="M29" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="N29" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O29" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="B30" s="3">
         <v>2</v>
@@ -2795,42 +2795,42 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L30" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="N30" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O30" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B31" s="3">
         <v>2</v>
@@ -2842,42 +2842,42 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L31" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="N31" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O31" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="B32" s="3">
         <v>2</v>
@@ -2889,42 +2889,42 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L32" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="M32" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="N32" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O32" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>180</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
@@ -2936,42 +2936,42 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L33" t="s">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="M33" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="N33" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O33" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>210</v>
+        <v>183</v>
       </c>
       <c r="B34" s="3">
         <v>2</v>
@@ -2983,42 +2983,42 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L34" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="M34" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="N34" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O34" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="B35" s="3">
         <v>2</v>
@@ -3030,42 +3030,42 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L35" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="N35" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O35" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="B36" s="3">
         <v>2</v>
@@ -3077,42 +3077,42 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="M36" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="N36" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O36" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="B37" s="3">
         <v>2</v>
@@ -3124,42 +3124,42 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L37" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="M37" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="N37" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O37" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="B38" s="3">
         <v>2</v>
@@ -3171,42 +3171,42 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L38" t="s">
+        <v>196</v>
+      </c>
+      <c r="M38" t="s">
+        <v>197</v>
+      </c>
+      <c r="N38" t="s">
         <v>223</v>
       </c>
-      <c r="M38" t="s">
-        <v>224</v>
-      </c>
-      <c r="N38" t="s">
-        <v>250</v>
-      </c>
       <c r="O38" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="B39" s="3">
         <v>2</v>
@@ -3218,42 +3218,42 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L39" t="s">
-        <v>226</v>
+        <v>199</v>
       </c>
       <c r="M39" t="s">
-        <v>227</v>
+        <v>200</v>
       </c>
       <c r="N39" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O39" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>228</v>
+        <v>201</v>
       </c>
       <c r="B40" s="3">
         <v>2</v>
@@ -3265,42 +3265,42 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L40" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="M40" t="s">
-        <v>230</v>
+        <v>203</v>
       </c>
       <c r="N40" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="O40" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>231</v>
+        <v>204</v>
       </c>
       <c r="B41" s="3">
         <v>2</v>
@@ -3312,42 +3312,42 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L41" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="M41" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="N41" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O41" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
@@ -3359,42 +3359,42 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L42" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="M42" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
       <c r="N42" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O42" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="B43" s="3">
         <v>2</v>
@@ -3406,42 +3406,42 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L43" t="s">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="M43" t="s">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="N43" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O43" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="B44" s="3">
         <v>2</v>
@@ -3453,42 +3453,42 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L44" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="M44" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="N44" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O44" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="B45" s="3">
         <v>2</v>
@@ -3500,42 +3500,42 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L45" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="M45" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="N45" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O45" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="B46" s="3">
         <v>2</v>
@@ -3547,37 +3547,37 @@
         <v>1</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L46" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="M46" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="N46" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="O46" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
@@ -3591,40 +3591,40 @@
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>25</v>
+        <v>264</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>87</v>
+        <v>267</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
@@ -3638,40 +3638,40 @@
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>26</v>
+        <v>268</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>87</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
@@ -3685,40 +3685,40 @@
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>27</v>
+        <v>269</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>87</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
@@ -3732,45 +3732,45 @@
         <v>1</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>28</v>
+        <v>270</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>87</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B51" s="2">
         <v>3</v>
@@ -3779,45 +3779,45 @@
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>11</v>
+        <v>271</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B52" s="2">
         <v>3</v>
@@ -3826,45 +3826,45 @@
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>12</v>
+        <v>275</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B53" s="2">
         <v>3</v>
@@ -3873,45 +3873,45 @@
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>13</v>
+        <v>276</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B54" s="2">
         <v>3</v>
@@ -3920,45 +3920,45 @@
         <v>1</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>14</v>
+        <v>277</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>15</v>
+        <v>272</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>88</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B55" s="2">
         <v>3</v>
@@ -3967,45 +3967,45 @@
         <v>1</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>31</v>
+        <v>278</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>89</v>
+        <v>281</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B56" s="2">
         <v>3</v>
@@ -4014,45 +4014,45 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>32</v>
+        <v>282</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>89</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B57" s="2">
         <v>3</v>
@@ -4061,45 +4061,45 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>89</v>
+        <v>281</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B58" s="2">
         <v>3</v>
@@ -4108,45 +4108,45 @@
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>35</v>
+        <v>279</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>36</v>
+        <v>280</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>89</v>
+        <v>281</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B59" s="2">
         <v>3</v>
@@ -4155,45 +4155,45 @@
         <v>1</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>39</v>
+        <v>285</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>41</v>
+        <v>286</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
       <c r="O59" s="1" t="s">
-        <v>44</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B60" s="2">
         <v>3</v>
@@ -4202,45 +4202,45 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>40</v>
+        <v>289</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>41</v>
+        <v>286</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>42</v>
+        <v>287</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>45</v>
+        <v>290</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B61" s="2">
         <v>3</v>
@@ -4249,45 +4249,45 @@
         <v>1</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B62" s="2">
         <v>3</v>
@@ -4296,45 +4296,45 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="B63" s="2">
         <v>3</v>
@@ -4343,45 +4343,45 @@
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="B64" s="2">
         <v>3</v>
@@ -4390,45 +4390,45 @@
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="B65" s="2">
         <v>3</v>
@@ -4437,45 +4437,45 @@
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="B66" s="2">
         <v>3</v>
@@ -4484,45 +4484,45 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B67" s="2">
         <v>3</v>
@@ -4531,45 +4531,45 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="B68" s="2">
         <v>3</v>
@@ -4578,45 +4578,45 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="B69" s="2">
         <v>3</v>
@@ -4625,45 +4625,45 @@
         <v>1</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="B70" s="2">
         <v>3</v>
@@ -4672,45 +4672,45 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="B71" s="3">
         <v>3</v>
@@ -4719,45 +4719,45 @@
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L71" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="M71" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="N71" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B72" s="3">
         <v>2</v>
@@ -4766,45 +4766,45 @@
         <v>1</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L72" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="M72" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="N72" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="B73" s="3">
         <v>2</v>
@@ -4813,45 +4813,45 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L73" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
       <c r="M73" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="N73" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="B74" s="3">
         <v>2</v>
@@ -4860,186 +4860,186 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="L74" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="M74" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="N74" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
+        <v>233</v>
+      </c>
+      <c r="B75" s="3">
+        <v>2</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L75" t="s">
         <v>260</v>
       </c>
-      <c r="B75" s="3">
-        <v>2</v>
-      </c>
-      <c r="C75" s="3">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L75" t="s">
-        <v>287</v>
-      </c>
       <c r="M75" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="N75" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>234</v>
+      </c>
+      <c r="B76" s="3">
+        <v>2</v>
+      </c>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L76" t="s">
         <v>261</v>
       </c>
-      <c r="B76" s="3">
-        <v>2</v>
-      </c>
-      <c r="C76" s="3">
-        <v>1</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L76" t="s">
-        <v>288</v>
-      </c>
       <c r="M76" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="N76" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
+        <v>235</v>
+      </c>
+      <c r="B77" s="3">
+        <v>2</v>
+      </c>
+      <c r="C77" s="3">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L77" t="s">
         <v>262</v>
       </c>
-      <c r="B77" s="3">
-        <v>2</v>
-      </c>
-      <c r="C77" s="3">
-        <v>1</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L77" t="s">
-        <v>289</v>
-      </c>
       <c r="M77" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="N77" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="B78" s="3">
         <v>2</v>
@@ -5048,36 +5048,36 @@
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="B79" s="3">
         <v>2</v>
@@ -5086,36 +5086,36 @@
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="B80" s="3">
         <v>2</v>
@@ -5124,36 +5124,36 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="B81" s="3">
         <v>2</v>
@@ -5162,36 +5162,36 @@
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -5200,36 +5200,36 @@
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="B83" s="3">
         <v>2</v>
@@ -5238,36 +5238,36 @@
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="B84" s="3">
         <v>2</v>
@@ -5276,36 +5276,36 @@
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="B85" s="3">
         <v>2</v>
@@ -5314,36 +5314,36 @@
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>271</v>
+        <v>244</v>
       </c>
       <c r="B86" s="3">
         <v>2</v>
@@ -5352,36 +5352,36 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="B87" s="3">
         <v>2</v>
@@ -5390,36 +5390,36 @@
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>273</v>
+        <v>246</v>
       </c>
       <c r="B88" s="3">
         <v>2</v>
@@ -5428,36 +5428,36 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>274</v>
+        <v>247</v>
       </c>
       <c r="B89" s="3">
         <v>2</v>
@@ -5466,36 +5466,36 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>275</v>
+        <v>248</v>
       </c>
       <c r="B90" s="3">
         <v>2</v>
@@ -5504,36 +5504,36 @@
         <v>1</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="B91" s="3">
         <v>2</v>
@@ -5542,36 +5542,36 @@
         <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="B92" s="3">
         <v>2</v>
@@ -5580,36 +5580,36 @@
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="B93" s="3">
         <v>2</v>
@@ -5618,36 +5618,36 @@
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B94" s="3">
         <v>2</v>
@@ -5656,31 +5656,31 @@
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F279F08B-E9DB-41DD-931A-5190DAA273F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A9B926-C133-474B-9A8C-A996E209341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="3930" windowWidth="23550" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="1920" windowWidth="23550" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="358">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,9 +54,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\train.txt</t>
-  </si>
-  <si>
     <t>SimuBeads3D-128-31-0-0-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -125,29 +122,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\raw_128x128_0</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\gt_128x128_0</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\train_128x128_0.txt</t>
-  </si>
-  <si>
     <t>none</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\raw_1024x1024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule\train_1024x1024.txt</t>
-  </si>
-  <si>
     <t>Microtubule2-3d-512</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,24 +134,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\raw_512x512</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\gt_512x512</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\train_512x512.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Microtubule2\train_1024x1024.txt</t>
-  </si>
-  <si>
     <t>Nuclear-pore-complex-128-0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -190,42 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_128x128_0</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_128x128_0</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\train_128x128_0.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\train_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_512x512</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_512x512</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\train_512x512.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\train_1024x1024.txt</t>
-  </si>
-  <si>
     <t>ZeroShotDeconvNet-642</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -234,24 +158,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw\PSF_odd.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw\PSF_odd.tif</t>
-  </si>
-  <si>
     <t>Microtubules2-9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -272,10 +178,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(31,25,25)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>scale_factor</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -328,10 +230,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\Microtubules2\train.txt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>id_sample_val</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -378,82 +276,6 @@
     <t>F-actin-nonlinear-2</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_9_sf_1\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin_Nonlinear\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_9_sf_1\gt</t>
-  </si>
-  <si>
     <t>Microtubules2-8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -483,80 +305,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\Microtubules2\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-9</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\raw</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_9_sf_1\gt</t>
-  </si>
-  <si>
     <t>None</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -565,301 +317,85 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-7</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-6</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-5</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-4</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-3</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-2</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CCPs-1</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_12_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-11</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_11_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-10</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_10_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-9</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_9_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-8</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_8_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-7</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_7_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-6</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_6_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-5</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-4</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-3</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-2</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>F-actin-1</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ER-6</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_6_sf_1\gt</t>
-  </si>
-  <si>
     <t>ER-5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_5_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ER-4</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_4_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ER-3</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_3_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ER-2</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_2_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ER-1</t>
   </si>
   <si>
-    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\raw</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\noise_1_sf_1\gt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\CCPs\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\F-actin\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioSR\ER\train.txt</t>
-  </si>
-  <si>
     <t>F-actin-nonlinear-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -868,15 +404,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\train_1024x1024.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
-  </si>
-  <si>
     <t>biotisr-ccps-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -935,142 +462,745 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sim-actin-3d</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vmsim3-mito</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vmsim5-mito</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vmsim488-patch-512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vmsim568-patch-512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vmsim647-patch-512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>I:\Datasets\BioTISR\transformed\CCPs\SIM_2d-dn-rb_rescale_100.0_avepool_2_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\CCPs\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\CCPs\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\F-actin\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\F-actin\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>I:\Datasets\BioTISR\transformed\F-actin\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\PSF_31.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\gt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\train.txt</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
-  </si>
-  <si>
-    <t>I:\Datasets\RLN\unzip\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuBeads3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\raw_psf_31_gauss_0_poiss_0_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\PSF_31.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.3</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_256\raw_psf_31_gauss_0.5_poiss_1_sf_1_ratio_0.1</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_560\PSF.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_382\raw_psf_101_gauss_0.5_poiss_1_sf_1_ratio_1_lambda_642\PSF.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\raw_128x128_0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\gt_128x128_0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\train_128x128_0.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\raw_512x512</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\gt_512x512</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\train_512x512.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Microtubule2\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_128x128_0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_128x128_0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\train_128x128_0.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_512x512</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_512x512</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\train_512x512.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\Nuclear_Pore_complex2\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_H2B\642\raw\PSF_odd.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\ZeroShotDeconvNet\3D time-lapsing data_LLSM_Mitosis_Mito\560\raw\PSF_odd.tif</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\SirDNA\raw_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\SirDNA\gt_1024x1024</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RCAN3D\Confocal_2_STED\SirDNA\train_1024x1024.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\CCPs\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\CCPs\SIM_2d-dn-rb_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\CCPs\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\CCPs\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\CCPs\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_8_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_8_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_7_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_7_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_6_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_5_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_5_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_4_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_4_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_3_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_3_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_2_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_2_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_1_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_1_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_8_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_8_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_7_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_7_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_6_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_5_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_5_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_4_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_4_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_3_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_3_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_2_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_2_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_1_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_1_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_8_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_8_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_7_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_7_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_6_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_5_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_5_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_4_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_4_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_3_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_3_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_2_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_2_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_1_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_1_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_12_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_12_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_11_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_11_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_10_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_10_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_9_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_9_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_8_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_8_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_7_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_7_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_6_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_5_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_5_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_4_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_4_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_3_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_3_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_2_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_2_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_1_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_1_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_6_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_6_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_5_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_5_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_4_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_4_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_3_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_3_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_2_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_2_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\raw</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\gt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\WF_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\SIM_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\WF_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\SIM_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\train.txt</t>
+  </si>
+  <si>
+    <t>deepbacs-ecoli-ave2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deepbacs-saureus-ave2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\SIM_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\WF_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\WF_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\SIM_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>biotisr-lysosomes-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-lysosomes-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-lysosomes-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin\train.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Lysosomes\SIM_2d_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Lysosomes\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Lysosomes\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Lysosomes\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Lysosomes\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin_nonlinear\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin_nonlinear\WF_noise_level_1_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin_nonlinear\WF_noise_level_2_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin_nonlinear\WF_noise_level_3_2d_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin_nonlinear\SIM_2d_rescale_100.0_avepool_3_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>(1,5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-0-sim-ave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-0-wf-ave-400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-1-sim-ave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-1-wf-ave-400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-2-sim-ave</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w2s-2-wf-ave-400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_0\SIM_rescale_100.0_avepool_2_bkgsub_1100</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_1\SIM_rescale_100.0_avepool_2_bkgsub_1100</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_2\SIM_rescale_100.0_avepool_2_bkgsub_1100</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_0\SIM_ave_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_0\WF_ave_400_rescale_100.0_bkgsub_auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_1\SIM_ave_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_1\WF_ave_400_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_2\SIM_ave_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\channle_2\WF_ave_400_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\W2S\transformed\train.txt</t>
+  </si>
+  <si>
+    <t>biotisr-3d-factin-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-3d-factin-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-3d-mt-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-3d-mt-2</t>
+  </si>
+  <si>
+    <t>biotisr-3d-mito-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>biotisr-3d-mito-2</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin-3D\SIM_remove_last_t0_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin-3D\WF_noise_level_1_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin-3D\WF_noise_level_2_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules-3D\SIM_remove_last_t0_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules-3D\WF_noise_level_1_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules-3D\WF_noise_level_2_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria-3D\SIM_remove_last_t0_rescale_100.0_avepool_2_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria-3D\WF_noise_level_1_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria-3D\WF_noise_level_2_remove_last_t0_rescale_100.0_bkgsub_100.0</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\F-actin-3D\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Microtubules-3D\train.txt</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria-3D\train.txt</t>
+  </si>
+  <si>
+    <t>biotisr-3d-mito-2-k5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5,31,31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimuMix3D-128-31-05-1-01-31x31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1101,7 +1231,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1109,11 +1239,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1122,6 +1261,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1402,7 +1552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -1413,56 +1563,56 @@
     <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="47.625" customWidth="1"/>
-    <col min="13" max="13" width="9.125" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="13" width="17.125" customWidth="1"/>
     <col min="14" max="14" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>21</v>
+      <c r="O1" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -1476,45 +1626,45 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1523,45 +1673,45 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -1570,45 +1720,45 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>107</v>
+        <v>195</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -1617,45 +1767,45 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>100</v>
+        <v>196</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1664,45 +1814,45 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>101</v>
+        <v>198</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>109</v>
+        <v>199</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -1711,45 +1861,45 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>102</v>
+        <v>200</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -1758,45 +1908,45 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>111</v>
+        <v>203</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -1805,45 +1955,45 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>104</v>
+        <v>204</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>112</v>
+        <v>205</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -1852,45 +2002,45 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>113</v>
+        <v>207</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>6</v>
+        <v>191</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="B11" s="2">
         <v>2</v>
@@ -1899,45 +2049,45 @@
         <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>114</v>
+        <v>208</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>115</v>
+        <v>209</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1946,45 +2096,45 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1993,45 +2143,45 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
@@ -2040,45 +2190,45 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -2087,45 +2237,45 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>127</v>
+        <v>217</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2134,45 +2284,45 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>128</v>
+        <v>219</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>136</v>
+        <v>220</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2181,45 +2331,45 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>129</v>
+        <v>221</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2228,45 +2378,45 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>130</v>
+        <v>223</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>138</v>
+        <v>224</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
@@ -2275,45 +2425,45 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>131</v>
+        <v>225</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>139</v>
+        <v>226</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>82</v>
+        <v>210</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>140</v>
+        <v>71</v>
       </c>
       <c r="B20" s="3">
         <v>2</v>
@@ -2325,42 +2475,42 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L20" t="s">
-        <v>141</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O20" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>144</v>
+        <v>73</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
@@ -2372,42 +2522,42 @@
         <v>1</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s">
-        <v>146</v>
+        <v>231</v>
       </c>
       <c r="N21" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O21" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -2419,42 +2569,42 @@
         <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s">
-        <v>149</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O22" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="B23" s="3">
         <v>2</v>
@@ -2466,42 +2616,42 @@
         <v>1</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L23" t="s">
-        <v>151</v>
+        <v>234</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>235</v>
       </c>
       <c r="N23" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O23" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>153</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
@@ -2513,42 +2663,42 @@
         <v>1</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L24" t="s">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O24" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -2560,42 +2710,42 @@
         <v>1</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L25" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="N25" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O25" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
@@ -2607,42 +2757,42 @@
         <v>1</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L26" t="s">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="M26" t="s">
-        <v>161</v>
+        <v>241</v>
       </c>
       <c r="N26" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O26" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="B27" s="3">
         <v>2</v>
@@ -2654,42 +2804,42 @@
         <v>1</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L27" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O27" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -2701,42 +2851,42 @@
         <v>1</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="M28" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="N28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="O28" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>168</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3">
         <v>2</v>
@@ -2748,42 +2898,42 @@
         <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L29" t="s">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s">
-        <v>170</v>
+        <v>247</v>
       </c>
       <c r="N29" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O29" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="B30" s="3">
         <v>2</v>
@@ -2795,42 +2945,42 @@
         <v>1</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L30" t="s">
-        <v>172</v>
+        <v>249</v>
       </c>
       <c r="M30" t="s">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="N30" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O30" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="B31" s="3">
         <v>2</v>
@@ -2842,42 +2992,42 @@
         <v>1</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L31" t="s">
-        <v>175</v>
+        <v>251</v>
       </c>
       <c r="M31" t="s">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="N31" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O31" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="B32" s="3">
         <v>2</v>
@@ -2889,42 +3039,42 @@
         <v>1</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L32" t="s">
-        <v>178</v>
+        <v>253</v>
       </c>
       <c r="M32" t="s">
-        <v>179</v>
+        <v>254</v>
       </c>
       <c r="N32" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O32" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
@@ -2936,42 +3086,42 @@
         <v>1</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L33" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="M33" t="s">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="N33" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O33" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>86</v>
       </c>
       <c r="B34" s="3">
         <v>2</v>
@@ -2983,42 +3133,42 @@
         <v>1</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L34" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s">
-        <v>185</v>
+        <v>258</v>
       </c>
       <c r="N34" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O34" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>87</v>
       </c>
       <c r="B35" s="3">
         <v>2</v>
@@ -3030,42 +3180,42 @@
         <v>1</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L35" t="s">
-        <v>187</v>
+        <v>259</v>
       </c>
       <c r="M35" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="N35" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O35" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="B36" s="3">
         <v>2</v>
@@ -3077,42 +3227,42 @@
         <v>1</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L36" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="M36" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="N36" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O36" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="B37" s="3">
         <v>2</v>
@@ -3124,42 +3274,42 @@
         <v>1</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L37" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="M37" t="s">
-        <v>194</v>
+        <v>264</v>
       </c>
       <c r="N37" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O37" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>195</v>
+        <v>90</v>
       </c>
       <c r="B38" s="3">
         <v>2</v>
@@ -3171,42 +3321,42 @@
         <v>1</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
       <c r="M38" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
       <c r="N38" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O38" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="B39" s="3">
         <v>2</v>
@@ -3218,42 +3368,42 @@
         <v>1</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L39" t="s">
-        <v>199</v>
+        <v>267</v>
       </c>
       <c r="M39" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="N39" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O39" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="B40" s="3">
         <v>2</v>
@@ -3265,42 +3415,42 @@
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L40" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
       <c r="N40" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="O40" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>204</v>
+        <v>93</v>
       </c>
       <c r="B41" s="3">
         <v>2</v>
@@ -3312,42 +3462,42 @@
         <v>1</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L41" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="M41" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="N41" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O41" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>94</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
@@ -3359,42 +3509,42 @@
         <v>1</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O42" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>210</v>
+        <v>95</v>
       </c>
       <c r="B43" s="3">
         <v>2</v>
@@ -3406,42 +3556,42 @@
         <v>1</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L43" t="s">
-        <v>211</v>
+        <v>276</v>
       </c>
       <c r="M43" t="s">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="N43" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O43" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>96</v>
       </c>
       <c r="B44" s="3">
         <v>2</v>
@@ -3453,42 +3603,42 @@
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L44" t="s">
-        <v>214</v>
+        <v>278</v>
       </c>
       <c r="M44" t="s">
-        <v>215</v>
+        <v>279</v>
       </c>
       <c r="N44" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O44" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="B45" s="3">
         <v>2</v>
@@ -3500,89 +3650,89 @@
         <v>1</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L45" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="M45" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="N45" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="O45" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>219</v>
-      </c>
-      <c r="B46" s="3">
-        <v>2</v>
-      </c>
-      <c r="C46" s="3">
-        <v>1</v>
-      </c>
-      <c r="D46" s="2">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L46" t="s">
-        <v>220</v>
-      </c>
-      <c r="M46" t="s">
-        <v>221</v>
-      </c>
-      <c r="N46" t="s">
-        <v>224</v>
-      </c>
-      <c r="O46" t="s">
-        <v>143</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B46" s="5">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>1</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="M46" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2">
         <v>3</v>
@@ -3591,45 +3741,45 @@
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>264</v>
+        <v>119</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B48" s="2">
         <v>3</v>
@@ -3638,45 +3788,45 @@
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>268</v>
+        <v>123</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>267</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B49" s="2">
         <v>3</v>
@@ -3685,92 +3835,92 @@
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>265</v>
+        <v>120</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>266</v>
+        <v>121</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="6">
         <v>3</v>
       </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="O50" s="1" t="s">
-        <v>267</v>
+      <c r="C50" s="6">
+        <v>1</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L50" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="O50" s="7" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" s="2">
         <v>3</v>
@@ -3779,45 +3929,45 @@
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>271</v>
+        <v>126</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>272</v>
+        <v>127</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>274</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" s="2">
         <v>3</v>
@@ -3826,45 +3976,45 @@
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>275</v>
+        <v>130</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>272</v>
+        <v>127</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>274</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="2">
         <v>3</v>
@@ -3873,139 +4023,139 @@
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>276</v>
+        <v>131</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>272</v>
+        <v>127</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>273</v>
+        <v>128</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B54" s="6">
         <v>3</v>
       </c>
-      <c r="C54" s="2">
-        <v>1</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" s="2">
+      <c r="C54" s="6">
+        <v>1</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J54" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L54" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="O54" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B55" s="6">
         <v>3</v>
       </c>
-      <c r="C55" s="2">
-        <v>1</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>281</v>
+      <c r="C55" s="6">
+        <v>1</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J55" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B56" s="2">
         <v>3</v>
@@ -4014,45 +4164,45 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>282</v>
+        <v>133</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B57" s="2">
         <v>3</v>
@@ -4061,45 +4211,45 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>283</v>
+        <v>137</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>281</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B58" s="2">
         <v>3</v>
@@ -4108,92 +4258,92 @@
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>284</v>
+        <v>138</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>279</v>
+        <v>134</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>280</v>
+        <v>135</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59" s="6">
         <v>3</v>
       </c>
-      <c r="C59" s="2">
-        <v>1</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>288</v>
+      <c r="C59" s="6">
+        <v>1</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B60" s="2">
         <v>3</v>
@@ -4202,92 +4352,92 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>289</v>
+        <v>140</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>286</v>
+        <v>141</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>287</v>
+        <v>142</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B61" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" s="6">
         <v>3</v>
       </c>
-      <c r="C61" s="2">
-        <v>1</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>27</v>
+      <c r="C61" s="6">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B62" s="2">
         <v>3</v>
@@ -4296,45 +4446,45 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>29</v>
+        <v>147</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B63" s="2">
         <v>3</v>
@@ -4343,45 +4493,45 @@
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>33</v>
+        <v>149</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B64" s="2">
         <v>3</v>
@@ -4390,45 +4540,45 @@
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>36</v>
+        <v>153</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B65" s="2">
         <v>3</v>
@@ -4437,45 +4587,45 @@
         <v>1</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>43</v>
+        <v>155</v>
       </c>
       <c r="M65" s="1" t="s">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B66" s="2">
         <v>3</v>
@@ -4484,45 +4634,45 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B67" s="2">
         <v>3</v>
@@ -4531,45 +4681,45 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B68" s="2">
         <v>3</v>
@@ -4578,92 +4728,92 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="6">
         <v>3</v>
       </c>
-      <c r="C69" s="2">
-        <v>1</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>62</v>
+      <c r="C69" s="6">
+        <v>1</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I69" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B70" s="2">
         <v>3</v>
@@ -4672,139 +4822,139 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="B71" s="3">
+        <v>31</v>
+      </c>
+      <c r="B71" s="2">
         <v>3</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="2">
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L71" t="s">
-        <v>228</v>
-      </c>
-      <c r="M71" t="s">
-        <v>229</v>
-      </c>
-      <c r="N71" t="s">
-        <v>227</v>
+        <v>46</v>
+      </c>
+      <c r="L71" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>174</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>230</v>
-      </c>
-      <c r="B72" s="3">
-        <v>2</v>
-      </c>
-      <c r="C72" s="3">
-        <v>1</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L72" t="s">
-        <v>256</v>
-      </c>
-      <c r="M72" t="s">
-        <v>254</v>
-      </c>
-      <c r="N72" t="s">
-        <v>255</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>27</v>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B72" s="5">
+        <v>3</v>
+      </c>
+      <c r="C72" s="5">
+        <v>1</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="O72" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>231</v>
+        <v>101</v>
       </c>
       <c r="B73" s="3">
         <v>2</v>
@@ -4813,45 +4963,45 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>253</v>
+        <v>53</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L73" t="s">
-        <v>257</v>
+        <v>179</v>
       </c>
       <c r="M73" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="N73" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>232</v>
+        <v>102</v>
       </c>
       <c r="B74" s="3">
         <v>2</v>
@@ -4860,45 +5010,45 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L74" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="M74" t="s">
-        <v>254</v>
+        <v>180</v>
       </c>
       <c r="N74" t="s">
-        <v>255</v>
+        <v>181</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>233</v>
+        <v>103</v>
       </c>
       <c r="B75" s="3">
         <v>2</v>
@@ -4907,45 +5057,45 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L75" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="M75" t="s">
-        <v>259</v>
+        <v>180</v>
       </c>
       <c r="N75" t="s">
-        <v>263</v>
+        <v>181</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>234</v>
+        <v>104</v>
       </c>
       <c r="B76" s="3">
         <v>2</v>
@@ -4954,45 +5104,45 @@
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>261</v>
+        <v>184</v>
       </c>
       <c r="M76" t="s">
-        <v>259</v>
+        <v>185</v>
       </c>
       <c r="N76" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="B77" s="3">
         <v>2</v>
@@ -5001,45 +5151,45 @@
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="L77" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="M77" t="s">
-        <v>259</v>
+        <v>185</v>
       </c>
       <c r="N77" t="s">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>236</v>
+        <v>106</v>
       </c>
       <c r="B78" s="3">
         <v>2</v>
@@ -5048,36 +5198,45 @@
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L78" t="s">
+        <v>188</v>
+      </c>
+      <c r="M78" t="s">
+        <v>185</v>
+      </c>
+      <c r="N78" t="s">
+        <v>186</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>107</v>
       </c>
       <c r="B79" s="3">
         <v>2</v>
@@ -5086,36 +5245,45 @@
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L79" t="s">
+        <v>316</v>
+      </c>
+      <c r="M79" t="s">
+        <v>319</v>
+      </c>
+      <c r="N79" t="s">
+        <v>315</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="B80" s="3">
         <v>2</v>
@@ -5124,36 +5292,45 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L80" t="s">
+        <v>317</v>
+      </c>
+      <c r="M80" t="s">
+        <v>319</v>
+      </c>
+      <c r="N80" t="s">
+        <v>315</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>239</v>
+        <v>109</v>
       </c>
       <c r="B81" s="3">
         <v>2</v>
@@ -5162,36 +5339,45 @@
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L81" t="s">
+        <v>318</v>
+      </c>
+      <c r="M81" t="s">
+        <v>319</v>
+      </c>
+      <c r="N81" t="s">
+        <v>315</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -5200,36 +5386,45 @@
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H82" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L82" t="s">
+        <v>311</v>
+      </c>
+      <c r="M82" t="s">
+        <v>310</v>
+      </c>
+      <c r="N82" t="s">
+        <v>314</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="B83" s="3">
         <v>2</v>
@@ -5238,36 +5433,45 @@
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L83" t="s">
+        <v>312</v>
+      </c>
+      <c r="M83" t="s">
+        <v>310</v>
+      </c>
+      <c r="N83" t="s">
+        <v>314</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>242</v>
+        <v>298</v>
       </c>
       <c r="B84" s="3">
         <v>2</v>
@@ -5276,36 +5480,45 @@
         <v>1</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L84" t="s">
+        <v>313</v>
+      </c>
+      <c r="M84" t="s">
+        <v>310</v>
+      </c>
+      <c r="N84" t="s">
+        <v>314</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>243</v>
+        <v>110</v>
       </c>
       <c r="B85" s="3">
         <v>2</v>
@@ -5314,36 +5527,45 @@
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L85" t="s">
+        <v>299</v>
+      </c>
+      <c r="M85" t="s">
+        <v>302</v>
+      </c>
+      <c r="N85" t="s">
+        <v>303</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="B86" s="3">
         <v>2</v>
@@ -5352,36 +5574,45 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L86" t="s">
+        <v>300</v>
+      </c>
+      <c r="M86" t="s">
+        <v>302</v>
+      </c>
+      <c r="N86" t="s">
+        <v>303</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>245</v>
+        <v>112</v>
       </c>
       <c r="B87" s="3">
         <v>2</v>
@@ -5390,36 +5621,45 @@
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L87" t="s">
+        <v>301</v>
+      </c>
+      <c r="M87" t="s">
+        <v>302</v>
+      </c>
+      <c r="N87" t="s">
+        <v>303</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>246</v>
+        <v>113</v>
       </c>
       <c r="B88" s="3">
         <v>2</v>
@@ -5428,36 +5668,45 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L88" t="s">
+        <v>305</v>
+      </c>
+      <c r="M88" t="s">
+        <v>304</v>
+      </c>
+      <c r="N88" t="s">
+        <v>308</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>247</v>
+        <v>114</v>
       </c>
       <c r="B89" s="3">
         <v>2</v>
@@ -5466,74 +5715,92 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L89" t="s">
+        <v>306</v>
+      </c>
+      <c r="M89" t="s">
+        <v>304</v>
+      </c>
+      <c r="N89" t="s">
+        <v>308</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>248</v>
-      </c>
-      <c r="B90" s="3">
-        <v>2</v>
-      </c>
-      <c r="C90" s="3">
-        <v>1</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B90" s="5">
+        <v>2</v>
+      </c>
+      <c r="C90" s="5">
+        <v>1</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H90" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I90" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J90" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>27</v>
+        <v>320</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H90" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K90" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="M90" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="N90" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="O90" s="7" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>249</v>
+        <v>116</v>
       </c>
       <c r="B91" s="3">
         <v>2</v>
@@ -5542,36 +5809,45 @@
         <v>1</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L91" t="s">
+        <v>284</v>
+      </c>
+      <c r="M91" t="s">
+        <v>286</v>
+      </c>
+      <c r="N91" t="s">
+        <v>285</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="B92" s="3">
         <v>2</v>
@@ -5580,36 +5856,45 @@
         <v>1</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L92" t="s">
+        <v>293</v>
+      </c>
+      <c r="M92" t="s">
+        <v>292</v>
+      </c>
+      <c r="N92" t="s">
+        <v>285</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>251</v>
+        <v>117</v>
       </c>
       <c r="B93" s="3">
         <v>2</v>
@@ -5618,69 +5903,698 @@
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
+      </c>
+      <c r="L93" t="s">
+        <v>287</v>
+      </c>
+      <c r="M93" t="s">
+        <v>288</v>
+      </c>
+      <c r="N93" t="s">
+        <v>289</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>252</v>
-      </c>
-      <c r="B94" s="3">
-        <v>2</v>
-      </c>
-      <c r="C94" s="3">
-        <v>1</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G94" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B94" s="5">
+        <v>2</v>
+      </c>
+      <c r="C94" s="5">
+        <v>1</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J94" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K94" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L94" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="M94" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="N94" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="O94" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A95" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B95" s="3">
+        <v>2</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L95" t="s">
+        <v>330</v>
+      </c>
+      <c r="M95" t="s">
+        <v>327</v>
+      </c>
+      <c r="N95" t="s">
+        <v>336</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A96" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B96" s="3">
+        <v>2</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L96" t="s">
+        <v>331</v>
+      </c>
+      <c r="M96" t="s">
+        <v>327</v>
+      </c>
+      <c r="N96" t="s">
+        <v>336</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A97" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B97" s="3">
+        <v>2</v>
+      </c>
+      <c r="C97" s="3">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L97" t="s">
+        <v>332</v>
+      </c>
+      <c r="M97" t="s">
+        <v>328</v>
+      </c>
+      <c r="N97" t="s">
+        <v>336</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A98" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B98" s="3">
+        <v>2</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L98" t="s">
+        <v>333</v>
+      </c>
+      <c r="M98" t="s">
+        <v>328</v>
+      </c>
+      <c r="N98" t="s">
+        <v>336</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A99" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="B99" s="3">
+        <v>2</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L99" t="s">
+        <v>334</v>
+      </c>
+      <c r="M99" t="s">
+        <v>329</v>
+      </c>
+      <c r="N99" t="s">
+        <v>336</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B100" s="5">
+        <v>2</v>
+      </c>
+      <c r="C100" s="5">
+        <v>1</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H100" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I100" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J100" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K100" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L100" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="N100" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="O100" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>337</v>
+      </c>
+      <c r="B101" s="3">
+        <v>3</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I101" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J101" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K101" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L101" t="s">
+        <v>344</v>
+      </c>
+      <c r="M101" t="s">
+        <v>343</v>
+      </c>
+      <c r="N101" t="s">
+        <v>352</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>338</v>
+      </c>
+      <c r="B102" s="3">
+        <v>3</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I102" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J102" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L102" t="s">
+        <v>345</v>
+      </c>
+      <c r="M102" t="s">
+        <v>343</v>
+      </c>
+      <c r="N102" t="s">
+        <v>352</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>339</v>
+      </c>
+      <c r="B103" s="3">
+        <v>3</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I103" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J103" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K103" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L103" t="s">
+        <v>347</v>
+      </c>
+      <c r="M103" t="s">
+        <v>346</v>
+      </c>
+      <c r="N103" t="s">
+        <v>353</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>340</v>
+      </c>
+      <c r="B104" s="3">
+        <v>3</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I104" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J104" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K104" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L104" t="s">
+        <v>348</v>
+      </c>
+      <c r="M104" t="s">
+        <v>346</v>
+      </c>
+      <c r="N104" t="s">
+        <v>353</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>341</v>
+      </c>
+      <c r="B105" s="3">
+        <v>3</v>
+      </c>
+      <c r="C105" s="3">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I105" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J105" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K105" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L105" t="s">
+        <v>350</v>
+      </c>
+      <c r="M105" t="s">
+        <v>349</v>
+      </c>
+      <c r="N105" t="s">
+        <v>354</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>342</v>
+      </c>
+      <c r="B106" s="3">
+        <v>3</v>
+      </c>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J106" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K106" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L106" t="s">
+        <v>351</v>
+      </c>
+      <c r="M106" t="s">
+        <v>349</v>
+      </c>
+      <c r="N106" t="s">
+        <v>354</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>355</v>
+      </c>
+      <c r="B107" s="3">
+        <v>3</v>
+      </c>
+      <c r="C107" s="3">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J107" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K107" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L107" t="s">
+        <v>351</v>
+      </c>
+      <c r="M107" t="s">
+        <v>349</v>
+      </c>
+      <c r="N107" t="s">
+        <v>354</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A9B926-C133-474B-9A8C-A996E209341F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2785B7E5-8A56-475A-8548-CA68D0FF0475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="1920" windowWidth="23550" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19515" yWindow="525" windowWidth="19185" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="359">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1200,6 +1200,10 @@
   </si>
   <si>
     <t>SimuMix3D-128-31-05-1-01-31x31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\train.txt</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1207,7 +1211,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1217,6 +1221,21 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -1252,7 +1271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1272,6 +1291,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4012,50 +4036,50 @@
         <v>129</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+    <row r="53" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="12">
         <v>3</v>
       </c>
-      <c r="C53" s="2">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="C53" s="12">
+        <v>1</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G53" s="1" t="s">
+      <c r="E53" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G53" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L53" s="1" t="s">
+      <c r="J53" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L53" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="N53" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O53" s="1" t="s">
+      <c r="N53" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="O53" s="11" t="s">
         <v>129</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2785B7E5-8A56-475A-8548-CA68D0FF0475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD26C54-E142-441E-8E08-2DB49BA8C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19515" yWindow="525" windowWidth="19185" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="401">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -454,14 +454,6 @@
     <t>biotisr-mito-3</t>
   </si>
   <si>
-    <t>deepbacs-ecoli</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>deepbacs-saureus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -960,21 +952,9 @@
     <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\gt</t>
   </si>
   <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\WF_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
     <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\train.txt</t>
   </si>
   <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Ecoli\SIM_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\WF_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
-    <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\SIM_rescale_100.0_bkgsub_auto</t>
-  </si>
-  <si>
     <t>E:\qiqilu\datasets_2\DeepBacs\Saureus\train.txt</t>
   </si>
   <si>
@@ -1204,6 +1184,152 @@
   </si>
   <si>
     <t>E:\qiqilu\datasets_2\RLN\unzip\kldeconv\SimuMix3D_128\train.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin_Nonlinear\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\Microtubules2\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\CCPs\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_12_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_11_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_10_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_9_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_8_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_7_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\F-actin\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_6_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_5_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_4_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_3_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_2_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>E:\qiqilu\datasets_2\BioSR\transformed\ER\noise_1_sf_1\raw_rescale_100.0_bkgsub_auto</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>path_lr_net</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1576,7 +1702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O107"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
@@ -1587,12 +1713,13 @@
     <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="20.375" customWidth="1"/>
-    <col min="13" max="13" width="17.125" customWidth="1"/>
-    <col min="14" max="14" width="11.875" customWidth="1"/>
+    <col min="12" max="12" width="12.875" customWidth="1"/>
+    <col min="13" max="13" width="65.125" customWidth="1"/>
+    <col min="14" max="14" width="12.5" customWidth="1"/>
+    <col min="15" max="15" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1630,16 +1757,19 @@
         <v>2</v>
       </c>
       <c r="M1" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1668,25 +1798,28 @@
         <v>41</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>56</v>
       </c>
@@ -1715,25 +1848,28 @@
         <v>41</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>192</v>
+        <v>354</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>191</v>
       </c>
       <c r="O3" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>57</v>
       </c>
@@ -1762,25 +1898,28 @@
         <v>41</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>194</v>
+        <v>355</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>58</v>
       </c>
@@ -1809,25 +1948,28 @@
         <v>41</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>196</v>
+        <v>356</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O5" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>59</v>
       </c>
@@ -1856,25 +1998,28 @@
         <v>41</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>198</v>
+        <v>357</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>60</v>
       </c>
@@ -1903,25 +2048,28 @@
         <v>41</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>200</v>
+        <v>358</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="O7" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
@@ -1950,25 +2098,28 @@
         <v>41</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>202</v>
+        <v>359</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="O8" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>62</v>
       </c>
@@ -1997,25 +2148,28 @@
         <v>41</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>204</v>
+        <v>360</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="O9" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>99</v>
       </c>
@@ -2044,25 +2198,28 @@
         <v>41</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>206</v>
+        <v>361</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="O10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -2091,25 +2248,28 @@
         <v>41</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="O11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>63</v>
       </c>
@@ -2138,25 +2298,28 @@
         <v>41</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>211</v>
+        <v>363</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>210</v>
       </c>
       <c r="O12" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>67</v>
       </c>
@@ -2185,25 +2348,28 @@
         <v>41</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>213</v>
+        <v>364</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>68</v>
       </c>
@@ -2232,25 +2398,28 @@
         <v>41</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="O14" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>69</v>
       </c>
@@ -2279,25 +2448,28 @@
         <v>41</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>217</v>
+        <v>366</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="O15" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>70</v>
       </c>
@@ -2326,25 +2498,28 @@
         <v>41</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>219</v>
+        <v>367</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="O16" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>64</v>
       </c>
@@ -2373,25 +2548,28 @@
         <v>41</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>221</v>
+        <v>368</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>65</v>
       </c>
@@ -2420,25 +2598,28 @@
         <v>41</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>223</v>
+        <v>369</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="O18" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>66</v>
       </c>
@@ -2467,25 +2648,28 @@
         <v>41</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="O19" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>71</v>
       </c>
@@ -2514,25 +2698,28 @@
         <v>41</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L20" t="s">
+        <v>371</v>
+      </c>
+      <c r="M20" t="s">
+        <v>225</v>
+      </c>
+      <c r="N20" t="s">
+        <v>226</v>
+      </c>
+      <c r="O20" t="s">
         <v>227</v>
       </c>
-      <c r="M20" t="s">
-        <v>228</v>
-      </c>
-      <c r="N20" t="s">
-        <v>229</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>73</v>
       </c>
@@ -2561,25 +2748,28 @@
         <v>41</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L21" t="s">
-        <v>230</v>
+        <v>372</v>
       </c>
       <c r="M21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N21" t="s">
         <v>229</v>
       </c>
       <c r="O21" t="s">
+        <v>227</v>
+      </c>
+      <c r="P21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -2608,25 +2798,28 @@
         <v>41</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L22" t="s">
-        <v>232</v>
+        <v>373</v>
       </c>
       <c r="M22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N22" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O22" t="s">
+        <v>227</v>
+      </c>
+      <c r="P22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -2655,25 +2848,28 @@
         <v>41</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L23" t="s">
-        <v>234</v>
+        <v>374</v>
       </c>
       <c r="M23" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="O23" t="s">
+        <v>227</v>
+      </c>
+      <c r="P23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -2702,25 +2898,28 @@
         <v>41</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L24" t="s">
-        <v>236</v>
+        <v>375</v>
       </c>
       <c r="M24" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="O24" t="s">
+        <v>227</v>
+      </c>
+      <c r="P24" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -2749,25 +2948,28 @@
         <v>41</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L25" t="s">
-        <v>238</v>
+        <v>376</v>
       </c>
       <c r="M25" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N25" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="O25" t="s">
+        <v>227</v>
+      </c>
+      <c r="P25" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -2796,25 +2998,28 @@
         <v>41</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L26" t="s">
-        <v>240</v>
+        <v>377</v>
       </c>
       <c r="M26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="N26" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="O26" t="s">
+        <v>227</v>
+      </c>
+      <c r="P26" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -2843,25 +3048,28 @@
         <v>41</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L27" t="s">
-        <v>242</v>
+        <v>378</v>
       </c>
       <c r="M27" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="O27" t="s">
+        <v>227</v>
+      </c>
+      <c r="P27" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -2890,25 +3098,28 @@
         <v>41</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L28" t="s">
-        <v>244</v>
+        <v>379</v>
       </c>
       <c r="M28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N28" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="O28" t="s">
+        <v>227</v>
+      </c>
+      <c r="P28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -2937,25 +3148,28 @@
         <v>41</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L29" t="s">
+        <v>380</v>
+      </c>
+      <c r="M29" t="s">
+        <v>244</v>
+      </c>
+      <c r="N29" t="s">
+        <v>245</v>
+      </c>
+      <c r="O29" t="s">
         <v>246</v>
       </c>
-      <c r="M29" t="s">
-        <v>247</v>
-      </c>
-      <c r="N29" t="s">
-        <v>248</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -2984,25 +3198,28 @@
         <v>41</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L30" t="s">
-        <v>249</v>
+        <v>381</v>
       </c>
       <c r="M30" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N30" t="s">
         <v>248</v>
       </c>
       <c r="O30" t="s">
+        <v>246</v>
+      </c>
+      <c r="P30" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -3031,25 +3248,28 @@
         <v>41</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L31" t="s">
-        <v>251</v>
+        <v>382</v>
       </c>
       <c r="M31" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="N31" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O31" t="s">
+        <v>246</v>
+      </c>
+      <c r="P31" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>84</v>
       </c>
@@ -3078,25 +3298,28 @@
         <v>41</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L32" t="s">
-        <v>253</v>
+        <v>383</v>
       </c>
       <c r="M32" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="N32" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O32" t="s">
+        <v>246</v>
+      </c>
+      <c r="P32" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -3125,25 +3348,28 @@
         <v>41</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L33" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
       <c r="M33" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N33" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="O33" t="s">
+        <v>246</v>
+      </c>
+      <c r="P33" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -3172,25 +3398,28 @@
         <v>41</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L34" t="s">
-        <v>257</v>
+        <v>385</v>
       </c>
       <c r="M34" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="N34" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="O34" t="s">
+        <v>246</v>
+      </c>
+      <c r="P34" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -3219,25 +3448,28 @@
         <v>41</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L35" t="s">
-        <v>259</v>
+        <v>386</v>
       </c>
       <c r="M35" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="N35" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="O35" t="s">
+        <v>246</v>
+      </c>
+      <c r="P35" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -3266,25 +3498,28 @@
         <v>41</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L36" t="s">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="M36" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N36" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="O36" t="s">
+        <v>246</v>
+      </c>
+      <c r="P36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -3313,25 +3548,28 @@
         <v>41</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L37" t="s">
-        <v>263</v>
+        <v>388</v>
       </c>
       <c r="M37" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="N37" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="O37" t="s">
+        <v>246</v>
+      </c>
+      <c r="P37" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -3360,25 +3598,28 @@
         <v>41</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>43</v>
+        <v>399</v>
       </c>
       <c r="K38" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L38" t="s">
-        <v>265</v>
+        <v>389</v>
       </c>
       <c r="M38" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N38" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="O38" t="s">
+        <v>246</v>
+      </c>
+      <c r="P38" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>91</v>
       </c>
@@ -3407,25 +3648,28 @@
         <v>41</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L39" t="s">
-        <v>267</v>
+        <v>390</v>
       </c>
       <c r="M39" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N39" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="O39" t="s">
+        <v>246</v>
+      </c>
+      <c r="P39" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>92</v>
       </c>
@@ -3454,25 +3698,28 @@
         <v>41</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L40" t="s">
-        <v>269</v>
+        <v>391</v>
       </c>
       <c r="M40" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="N40" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="O40" t="s">
+        <v>246</v>
+      </c>
+      <c r="P40" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>93</v>
       </c>
@@ -3501,25 +3748,28 @@
         <v>41</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K41" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L41" t="s">
+        <v>392</v>
+      </c>
+      <c r="M41" t="s">
+        <v>269</v>
+      </c>
+      <c r="N41" t="s">
+        <v>270</v>
+      </c>
+      <c r="O41" t="s">
         <v>271</v>
       </c>
-      <c r="M41" t="s">
-        <v>272</v>
-      </c>
-      <c r="N41" t="s">
-        <v>273</v>
-      </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -3548,25 +3798,28 @@
         <v>41</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L42" t="s">
-        <v>274</v>
+        <v>393</v>
       </c>
       <c r="M42" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="N42" t="s">
         <v>273</v>
       </c>
       <c r="O42" t="s">
+        <v>271</v>
+      </c>
+      <c r="P42" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -3595,25 +3848,28 @@
         <v>41</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L43" t="s">
-        <v>276</v>
+        <v>394</v>
       </c>
       <c r="M43" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N43" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O43" t="s">
+        <v>271</v>
+      </c>
+      <c r="P43" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -3642,25 +3898,28 @@
         <v>41</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L44" t="s">
-        <v>278</v>
+        <v>395</v>
       </c>
       <c r="M44" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N44" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="O44" t="s">
+        <v>271</v>
+      </c>
+      <c r="P44" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -3689,25 +3948,28 @@
         <v>41</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>43</v>
+        <v>398</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="L45" t="s">
-        <v>280</v>
+        <v>396</v>
       </c>
       <c r="M45" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="N45" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="O45" t="s">
+        <v>271</v>
+      </c>
+      <c r="P45" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>98</v>
       </c>
@@ -3735,26 +3997,29 @@
       <c r="I46" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J46" s="7" t="s">
-        <v>43</v>
+      <c r="J46" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>46</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>282</v>
+        <v>397</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="O46" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="P46" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -3789,19 +4054,22 @@
         <v>46</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O47" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="P47" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N47" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -3836,19 +4104,22 @@
         <v>46</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M48" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N48" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="O48" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -3883,19 +4154,22 @@
         <v>46</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M49" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="N49" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>9</v>
       </c>
@@ -3930,19 +4204,22 @@
         <v>46</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M50" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="O50" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="P50" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="N50" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="O50" s="7" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>10</v>
       </c>
@@ -3977,19 +4254,22 @@
         <v>46</v>
       </c>
       <c r="L51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="P51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4024,19 +4304,22 @@
         <v>46</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M52" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N52" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="O52" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
@@ -4071,21 +4354,24 @@
         <v>46</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M53" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="P53" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="N53" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="O53" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B54" s="6">
         <v>3</v>
@@ -4118,19 +4404,22 @@
         <v>46</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M54" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O54" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="P54" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="N54" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="O54" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>13</v>
       </c>
@@ -4165,19 +4454,22 @@
         <v>46</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M55" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="P55" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="N55" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="O55" s="7" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>14</v>
       </c>
@@ -4212,19 +4504,22 @@
         <v>46</v>
       </c>
       <c r="L56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O56" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="P56" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -4259,19 +4554,22 @@
         <v>46</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M57" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P57" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -4306,19 +4604,22 @@
         <v>46</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M58" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P58" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="N58" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>17</v>
       </c>
@@ -4353,19 +4654,22 @@
         <v>46</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M59" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="P59" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="N59" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="O59" s="7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>18</v>
       </c>
@@ -4400,19 +4704,22 @@
         <v>46</v>
       </c>
       <c r="L60" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O60" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="P60" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="N60" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>19</v>
       </c>
@@ -4447,19 +4754,22 @@
         <v>46</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N61" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="O61" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="P61" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -4494,19 +4804,22 @@
         <v>46</v>
       </c>
       <c r="L62" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O62" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="M62" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="O62" s="1" t="s">
+      <c r="P62" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
@@ -4541,19 +4854,22 @@
         <v>46</v>
       </c>
       <c r="L63" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O63" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="O63" s="1" t="s">
+      <c r="P63" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>24</v>
       </c>
@@ -4588,19 +4904,22 @@
         <v>46</v>
       </c>
       <c r="L64" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O64" s="1" t="s">
+      <c r="P64" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>25</v>
       </c>
@@ -4635,19 +4954,22 @@
         <v>46</v>
       </c>
       <c r="L65" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="O65" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="O65" s="1" t="s">
+      <c r="P65" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
@@ -4682,19 +5004,22 @@
         <v>46</v>
       </c>
       <c r="L66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="O66" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="O66" s="1" t="s">
+      <c r="P66" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -4729,19 +5054,22 @@
         <v>46</v>
       </c>
       <c r="L67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="O67" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="M67" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="O67" s="1" t="s">
+      <c r="P67" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>28</v>
       </c>
@@ -4776,19 +5104,22 @@
         <v>46</v>
       </c>
       <c r="L68" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="O68" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="M68" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="O68" s="1" t="s">
+      <c r="P68" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="s">
         <v>29</v>
       </c>
@@ -4823,19 +5154,22 @@
         <v>46</v>
       </c>
       <c r="L69" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="O69" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="M69" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="N69" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="O69" s="7" t="s">
+      <c r="P69" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
@@ -4870,19 +5204,22 @@
         <v>46</v>
       </c>
       <c r="L70" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>31</v>
       </c>
@@ -4917,19 +5254,22 @@
         <v>46</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P71" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>100</v>
       </c>
@@ -4964,19 +5304,22 @@
         <v>46</v>
       </c>
       <c r="L72" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="M72" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O72" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="M72" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="O72" s="7" t="s">
+      <c r="P72" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -4993,7 +5336,7 @@
         <v>48</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>35</v>
@@ -5011,19 +5354,22 @@
         <v>46</v>
       </c>
       <c r="L73" t="s">
+        <v>177</v>
+      </c>
+      <c r="M73" t="s">
+        <v>177</v>
+      </c>
+      <c r="N73" t="s">
+        <v>178</v>
+      </c>
+      <c r="O73" t="s">
         <v>179</v>
       </c>
-      <c r="M73" t="s">
-        <v>180</v>
-      </c>
-      <c r="N73" t="s">
-        <v>181</v>
-      </c>
-      <c r="O73" s="1" t="s">
+      <c r="P73" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -5034,13 +5380,13 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>35</v>
@@ -5058,19 +5404,22 @@
         <v>46</v>
       </c>
       <c r="L74" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="M74" t="s">
         <v>180</v>
       </c>
       <c r="N74" t="s">
-        <v>181</v>
-      </c>
-      <c r="O74" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O74" t="s">
+        <v>179</v>
+      </c>
+      <c r="P74" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -5081,13 +5430,13 @@
         <v>1</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>35</v>
@@ -5105,19 +5454,22 @@
         <v>46</v>
       </c>
       <c r="L75" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M75" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N75" t="s">
-        <v>181</v>
-      </c>
-      <c r="O75" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="O75" t="s">
+        <v>179</v>
+      </c>
+      <c r="P75" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -5128,13 +5480,13 @@
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>35</v>
@@ -5152,19 +5504,22 @@
         <v>46</v>
       </c>
       <c r="L76" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="M76" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N76" t="s">
-        <v>309</v>
-      </c>
-      <c r="O76" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O76" t="s">
+        <v>303</v>
+      </c>
+      <c r="P76" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -5175,13 +5530,13 @@
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>35</v>
@@ -5199,19 +5554,22 @@
         <v>46</v>
       </c>
       <c r="L77" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M77" t="s">
         <v>185</v>
       </c>
       <c r="N77" t="s">
-        <v>186</v>
-      </c>
-      <c r="O77" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O77" t="s">
+        <v>184</v>
+      </c>
+      <c r="P77" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -5222,13 +5580,13 @@
         <v>1</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>35</v>
@@ -5246,19 +5604,22 @@
         <v>46</v>
       </c>
       <c r="L78" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M78" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N78" t="s">
-        <v>186</v>
-      </c>
-      <c r="O78" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="O78" t="s">
+        <v>184</v>
+      </c>
+      <c r="P78" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -5269,13 +5630,13 @@
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>35</v>
@@ -5293,19 +5654,22 @@
         <v>46</v>
       </c>
       <c r="L79" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="M79" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="N79" t="s">
-        <v>315</v>
-      </c>
-      <c r="O79" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="O79" t="s">
+        <v>309</v>
+      </c>
+      <c r="P79" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -5316,13 +5680,13 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>35</v>
@@ -5340,19 +5704,22 @@
         <v>46</v>
       </c>
       <c r="L80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M80" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N80" t="s">
-        <v>315</v>
-      </c>
-      <c r="O80" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="O80" t="s">
+        <v>309</v>
+      </c>
+      <c r="P80" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -5363,13 +5730,13 @@
         <v>1</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>35</v>
@@ -5387,21 +5754,24 @@
         <v>46</v>
       </c>
       <c r="L81" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="M81" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="N81" t="s">
-        <v>315</v>
-      </c>
-      <c r="O81" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="O81" t="s">
+        <v>309</v>
+      </c>
+      <c r="P81" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -5410,13 +5780,13 @@
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>35</v>
@@ -5434,36 +5804,39 @@
         <v>46</v>
       </c>
       <c r="L82" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M82" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="N82" t="s">
+        <v>304</v>
+      </c>
+      <c r="O82" t="s">
+        <v>308</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>291</v>
+      </c>
+      <c r="B83" s="3">
+        <v>2</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>297</v>
-      </c>
-      <c r="B83" s="3">
-        <v>2</v>
-      </c>
-      <c r="C83" s="3">
-        <v>1</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>35</v>
@@ -5481,36 +5854,39 @@
         <v>46</v>
       </c>
       <c r="L83" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="M83" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="N83" t="s">
+        <v>304</v>
+      </c>
+      <c r="O83" t="s">
+        <v>308</v>
+      </c>
+      <c r="P83" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>292</v>
+      </c>
+      <c r="B84" s="3">
+        <v>2</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>298</v>
-      </c>
-      <c r="B84" s="3">
-        <v>2</v>
-      </c>
-      <c r="C84" s="3">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>320</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>35</v>
@@ -5528,19 +5904,22 @@
         <v>46</v>
       </c>
       <c r="L84" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M84" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="N84" t="s">
-        <v>314</v>
-      </c>
-      <c r="O84" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O84" t="s">
+        <v>308</v>
+      </c>
+      <c r="P84" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>110</v>
       </c>
@@ -5551,13 +5930,13 @@
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>35</v>
@@ -5575,19 +5954,22 @@
         <v>46</v>
       </c>
       <c r="L85" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="M85" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="N85" t="s">
-        <v>303</v>
-      </c>
-      <c r="O85" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O85" t="s">
+        <v>297</v>
+      </c>
+      <c r="P85" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>111</v>
       </c>
@@ -5598,13 +5980,13 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>35</v>
@@ -5622,19 +6004,22 @@
         <v>46</v>
       </c>
       <c r="L86" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M86" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="N86" t="s">
-        <v>303</v>
-      </c>
-      <c r="O86" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O86" t="s">
+        <v>297</v>
+      </c>
+      <c r="P86" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>112</v>
       </c>
@@ -5645,13 +6030,13 @@
         <v>1</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>35</v>
@@ -5669,19 +6054,22 @@
         <v>46</v>
       </c>
       <c r="L87" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="M87" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="N87" t="s">
-        <v>303</v>
-      </c>
-      <c r="O87" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O87" t="s">
+        <v>297</v>
+      </c>
+      <c r="P87" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>113</v>
       </c>
@@ -5692,13 +6080,13 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>35</v>
@@ -5716,19 +6104,22 @@
         <v>46</v>
       </c>
       <c r="L88" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="M88" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N88" t="s">
-        <v>308</v>
-      </c>
-      <c r="O88" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O88" t="s">
+        <v>302</v>
+      </c>
+      <c r="P88" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -5739,13 +6130,13 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>48</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>35</v>
@@ -5763,19 +6154,22 @@
         <v>46</v>
       </c>
       <c r="L89" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="M89" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="N89" t="s">
-        <v>308</v>
-      </c>
-      <c r="O89" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="O89" t="s">
+        <v>302</v>
+      </c>
+      <c r="P89" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>115</v>
       </c>
@@ -5786,13 +6180,13 @@
         <v>1</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>48</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>35</v>
@@ -5810,30 +6204,33 @@
         <v>46</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="M90" s="4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="N90" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="O90" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="P90" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
+        <v>284</v>
+      </c>
+      <c r="B91" s="3">
+        <v>2</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="B91" s="3">
-        <v>2</v>
-      </c>
-      <c r="C91" s="3">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>48</v>
@@ -5857,68 +6254,74 @@
         <v>46</v>
       </c>
       <c r="L91" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M91" t="s">
+        <v>287</v>
+      </c>
+      <c r="N91" t="s">
         <v>286</v>
       </c>
-      <c r="N91" t="s">
+      <c r="O91" t="s">
+        <v>282</v>
+      </c>
+      <c r="P91" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="O91" s="1" t="s">
+      <c r="B92" s="5">
+        <v>2</v>
+      </c>
+      <c r="C92" s="5">
+        <v>1</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H92" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J92" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="M92" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="N92" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="P92" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>290</v>
-      </c>
-      <c r="B92" s="3">
-        <v>2</v>
-      </c>
-      <c r="C92" s="3">
-        <v>1</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H92" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L92" t="s">
-        <v>293</v>
-      </c>
-      <c r="M92" t="s">
-        <v>292</v>
-      </c>
-      <c r="N92" t="s">
-        <v>285</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>117</v>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A93" s="8" t="s">
+        <v>315</v>
       </c>
       <c r="B93" s="3">
         <v>2</v>
@@ -5927,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>48</v>
@@ -5951,68 +6354,74 @@
         <v>46</v>
       </c>
       <c r="L93" t="s">
-        <v>287</v>
+        <v>324</v>
       </c>
       <c r="M93" t="s">
-        <v>288</v>
+        <v>324</v>
       </c>
       <c r="N93" t="s">
-        <v>289</v>
-      </c>
-      <c r="O93" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="O93" t="s">
+        <v>330</v>
+      </c>
+      <c r="P93" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="B94" s="5">
-        <v>2</v>
-      </c>
-      <c r="C94" s="5">
-        <v>1</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J94" s="7" t="s">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A94" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B94" s="3">
+        <v>2</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K94" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="M94" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="N94" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="O94" s="7" t="s">
+      <c r="K94" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L94" t="s">
+        <v>325</v>
+      </c>
+      <c r="M94" t="s">
+        <v>325</v>
+      </c>
+      <c r="N94" t="s">
+        <v>321</v>
+      </c>
+      <c r="O94" t="s">
+        <v>330</v>
+      </c>
+      <c r="P94" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95" s="8" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B95" s="3">
         <v>2</v>
@@ -6045,21 +6454,24 @@
         <v>46</v>
       </c>
       <c r="L95" t="s">
+        <v>326</v>
+      </c>
+      <c r="M95" t="s">
+        <v>326</v>
+      </c>
+      <c r="N95" t="s">
+        <v>322</v>
+      </c>
+      <c r="O95" t="s">
         <v>330</v>
       </c>
-      <c r="M95" t="s">
-        <v>327</v>
-      </c>
-      <c r="N95" t="s">
-        <v>336</v>
-      </c>
-      <c r="O95" s="1" t="s">
+      <c r="P95" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B96" s="3">
         <v>2</v>
@@ -6092,21 +6504,24 @@
         <v>46</v>
       </c>
       <c r="L96" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="M96" t="s">
         <v>327</v>
       </c>
       <c r="N96" t="s">
-        <v>336</v>
-      </c>
-      <c r="O96" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O96" t="s">
+        <v>330</v>
+      </c>
+      <c r="P96" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B97" s="3">
         <v>2</v>
@@ -6139,71 +6554,77 @@
         <v>46</v>
       </c>
       <c r="L97" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M97" t="s">
         <v>328</v>
       </c>
       <c r="N97" t="s">
-        <v>336</v>
-      </c>
-      <c r="O97" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O97" t="s">
+        <v>330</v>
+      </c>
+      <c r="P97" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A98" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B98" s="3">
-        <v>2</v>
-      </c>
-      <c r="C98" s="3">
-        <v>1</v>
-      </c>
-      <c r="D98" s="2" t="s">
+    <row r="98" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="B98" s="5">
+        <v>2</v>
+      </c>
+      <c r="C98" s="5">
+        <v>1</v>
+      </c>
+      <c r="D98" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J98" s="1" t="s">
+      <c r="E98" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I98" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J98" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K98" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L98" t="s">
-        <v>333</v>
-      </c>
-      <c r="M98" t="s">
-        <v>328</v>
-      </c>
-      <c r="N98" t="s">
-        <v>336</v>
-      </c>
-      <c r="O98" s="1" t="s">
+      <c r="K98" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="M98" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="N98" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="O98" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="P98" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A99" s="8" t="s">
-        <v>325</v>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>331</v>
       </c>
       <c r="B99" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99" s="3">
         <v>1</v>
@@ -6211,90 +6632,96 @@
       <c r="D99" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J99" s="1" t="s">
+      <c r="E99" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I99" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J99" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K99" s="10" t="s">
         <v>46</v>
       </c>
       <c r="L99" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M99" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="N99" t="s">
-        <v>336</v>
-      </c>
-      <c r="O99" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="O99" t="s">
+        <v>346</v>
+      </c>
+      <c r="P99" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="B100" s="5">
-        <v>2</v>
-      </c>
-      <c r="C100" s="5">
-        <v>1</v>
-      </c>
-      <c r="D100" s="6" t="s">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>332</v>
+      </c>
+      <c r="B100" s="3">
+        <v>3</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E100" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G100" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I100" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="J100" s="7" t="s">
+      <c r="E100" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I100" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J100" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K100" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="M100" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="N100" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="O100" s="7" t="s">
+      <c r="K100" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="L100" t="s">
+        <v>339</v>
+      </c>
+      <c r="M100" t="s">
+        <v>339</v>
+      </c>
+      <c r="N100" t="s">
+        <v>337</v>
+      </c>
+      <c r="O100" t="s">
+        <v>346</v>
+      </c>
+      <c r="P100" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B101" s="3">
         <v>3</v>
@@ -6327,21 +6754,24 @@
         <v>46</v>
       </c>
       <c r="L101" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="M101" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="N101" t="s">
-        <v>352</v>
-      </c>
-      <c r="O101" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="O101" t="s">
+        <v>347</v>
+      </c>
+      <c r="P101" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B102" s="3">
         <v>3</v>
@@ -6374,21 +6804,24 @@
         <v>46</v>
       </c>
       <c r="L102" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="M102" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="N102" t="s">
-        <v>352</v>
-      </c>
-      <c r="O102" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="O102" t="s">
+        <v>347</v>
+      </c>
+      <c r="P102" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B103" s="3">
         <v>3</v>
@@ -6421,21 +6854,24 @@
         <v>46</v>
       </c>
       <c r="L103" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="M103" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="N103" t="s">
-        <v>353</v>
-      </c>
-      <c r="O103" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="O103" t="s">
+        <v>348</v>
+      </c>
+      <c r="P103" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B104" s="3">
         <v>3</v>
@@ -6468,21 +6904,24 @@
         <v>46</v>
       </c>
       <c r="L104" t="s">
+        <v>345</v>
+      </c>
+      <c r="M104" t="s">
+        <v>345</v>
+      </c>
+      <c r="N104" t="s">
+        <v>343</v>
+      </c>
+      <c r="O104" t="s">
         <v>348</v>
       </c>
-      <c r="M104" t="s">
-        <v>346</v>
-      </c>
-      <c r="N104" t="s">
-        <v>353</v>
-      </c>
-      <c r="O104" s="1" t="s">
+      <c r="P104" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B105" s="3">
         <v>3</v>
@@ -6500,10 +6939,10 @@
         <v>51</v>
       </c>
       <c r="G105" s="10" t="s">
-        <v>39</v>
+        <v>350</v>
       </c>
       <c r="H105" s="10" t="s">
-        <v>39</v>
+        <v>350</v>
       </c>
       <c r="I105" s="10" t="s">
         <v>42</v>
@@ -6515,109 +6954,18 @@
         <v>46</v>
       </c>
       <c r="L105" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M105" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="N105" t="s">
-        <v>354</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>342</v>
-      </c>
-      <c r="B106" s="3">
-        <v>3</v>
-      </c>
-      <c r="C106" s="3">
-        <v>1</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E106" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F106" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="H106" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J106" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K106" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L106" t="s">
-        <v>351</v>
-      </c>
-      <c r="M106" t="s">
-        <v>349</v>
-      </c>
-      <c r="N106" t="s">
-        <v>354</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>355</v>
-      </c>
-      <c r="B107" s="3">
-        <v>3</v>
-      </c>
-      <c r="C107" s="3">
-        <v>1</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E107" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="I107" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J107" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K107" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L107" t="s">
-        <v>351</v>
-      </c>
-      <c r="M107" t="s">
-        <v>349</v>
-      </c>
-      <c r="N107" t="s">
-        <v>354</v>
-      </c>
-      <c r="O107" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="O105" t="s">
+        <v>348</v>
+      </c>
+      <c r="P105" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD26C54-E142-441E-8E08-2DB49BA8C731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB39B33-F6B6-4B5F-BB4A-72A76C4EEE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1740" yWindow="2700" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="404">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -202,18 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>epoch_fp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>epoch_bp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1171,10 +1159,6 @@
     <t>E:\qiqilu\datasets_2\BioTISR\transformed\Mitochondria-3D\train.txt</t>
   </si>
   <si>
-    <t>biotisr-3d-mito-2-k5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(5,31,31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1330,6 +1314,34 @@
   </si>
   <si>
     <t>path_lr_net</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>median_filter</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5,10)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_iter_bp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>num_iter_fp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(7,31,31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(9,31,31)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1397,7 +1409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1422,6 +1434,28 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1702,24 +1736,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
     <col min="2" max="3" width="5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="5" style="2" customWidth="1"/>
-    <col min="5" max="6" width="9.125" customWidth="1"/>
-    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
-    <col min="8" max="9" width="10.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="9.625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.875" customWidth="1"/>
-    <col min="13" max="13" width="65.125" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
-    <col min="15" max="15" width="11.875" customWidth="1"/>
+    <col min="4" max="5" width="5" style="2" customWidth="1"/>
+    <col min="6" max="7" width="9.125" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="10" width="10.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="42.625" customWidth="1"/>
+    <col min="14" max="14" width="99.625" customWidth="1"/>
+    <col min="15" max="15" width="111.125" customWidth="1"/>
+    <col min="16" max="16" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1730,46 +1764,49 @@
         <v>37</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>44</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>45</v>
+        <v>401</v>
       </c>
       <c r="L1" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>400</v>
-      </c>
       <c r="N1" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="O1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1780,48 +1817,51 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -1830,48 +1870,51 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>354</v>
+        <v>43</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>190</v>
+        <v>350</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B4" s="2">
         <v>2</v>
@@ -1880,48 +1923,51 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K4" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>355</v>
+        <v>43</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2">
         <v>2</v>
@@ -1930,48 +1976,51 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K5" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>356</v>
+        <v>43</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>194</v>
+        <v>352</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P5" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -1980,48 +2029,51 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E6" s="14">
+        <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>357</v>
+        <v>43</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>196</v>
+        <v>353</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2">
         <v>2</v>
@@ -2030,48 +2082,51 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K7" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>358</v>
+        <v>43</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>198</v>
+        <v>354</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="P7" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2">
         <v>2</v>
@@ -2080,48 +2135,51 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E8" s="14">
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K8" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>359</v>
+        <v>43</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="P8" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2">
         <v>2</v>
@@ -2130,48 +2188,51 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K9" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>360</v>
+        <v>43</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>202</v>
+        <v>356</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2">
         <v>2</v>
@@ -2180,98 +2241,104 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K10" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>361</v>
+        <v>43</v>
       </c>
       <c r="M10" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="12">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="O11" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="P11" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q11" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -2280,48 +2347,51 @@
         <v>1</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>363</v>
+        <v>43</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>209</v>
+        <v>359</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="P12" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -2330,98 +2400,104 @@
         <v>1</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>364</v>
+        <v>43</v>
       </c>
       <c r="M13" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="12">
+        <v>2</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="O14" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="N13" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P13" s="1" t="s">
+      <c r="P14" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q14" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
@@ -2430,48 +2506,51 @@
         <v>1</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K15" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>366</v>
+        <v>43</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>215</v>
+        <v>362</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="P15" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
@@ -2480,48 +2559,51 @@
         <v>1</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K16" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>367</v>
+        <v>43</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>217</v>
+        <v>363</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="P16" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2530,48 +2612,51 @@
         <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K17" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>368</v>
+        <v>43</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>219</v>
+        <v>364</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P17" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2">
         <v>2</v>
@@ -2580,48 +2665,51 @@
         <v>1</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K18" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>369</v>
+        <v>43</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>221</v>
+        <v>365</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="P18" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2">
         <v>2</v>
@@ -2630,98 +2718,104 @@
         <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K19" s="1" t="s">
-        <v>46</v>
+        <v>395</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>370</v>
+        <v>43</v>
       </c>
       <c r="M19" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="22">
+        <v>2</v>
+      </c>
+      <c r="C20" s="22">
+        <v>1</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="O20" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="P20" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="3">
-        <v>2</v>
-      </c>
-      <c r="C20" s="3">
-        <v>1</v>
-      </c>
-      <c r="D20" s="2">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L20" t="s">
-        <v>371</v>
-      </c>
-      <c r="M20" t="s">
-        <v>225</v>
-      </c>
-      <c r="N20" t="s">
-        <v>226</v>
-      </c>
-      <c r="O20" t="s">
-        <v>227</v>
-      </c>
-      <c r="P20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B21" s="3">
         <v>2</v>
@@ -2732,46 +2826,49 @@
       <c r="D21" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>48</v>
+      <c r="E21" s="14">
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L21" t="s">
-        <v>372</v>
+        <v>395</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M21" t="s">
-        <v>228</v>
+        <v>368</v>
       </c>
       <c r="N21" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="O21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="P21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -2782,96 +2879,102 @@
       <c r="D22" s="2">
         <v>1</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>48</v>
+      <c r="E22" s="14">
+        <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K22" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" t="s">
-        <v>373</v>
+        <v>395</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M22" t="s">
+        <v>369</v>
+      </c>
+      <c r="N22" t="s">
+        <v>227</v>
+      </c>
+      <c r="O22" t="s">
+        <v>228</v>
+      </c>
+      <c r="P22" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="22">
+        <v>2</v>
+      </c>
+      <c r="C23" s="22">
+        <v>1</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>0</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="O23" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="N22" t="s">
-        <v>231</v>
-      </c>
-      <c r="O22" t="s">
-        <v>227</v>
-      </c>
-      <c r="P22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>75</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2</v>
-      </c>
-      <c r="C23" s="3">
-        <v>1</v>
-      </c>
-      <c r="D23" s="2">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L23" t="s">
-        <v>374</v>
-      </c>
-      <c r="M23" t="s">
-        <v>232</v>
-      </c>
-      <c r="N23" t="s">
-        <v>233</v>
-      </c>
-      <c r="O23" t="s">
-        <v>227</v>
-      </c>
-      <c r="P23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q23" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B24" s="3">
         <v>2</v>
@@ -2882,46 +2985,49 @@
       <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>48</v>
+      <c r="E24" s="14">
+        <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L24" t="s">
-        <v>375</v>
+        <v>395</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M24" t="s">
-        <v>234</v>
+        <v>371</v>
       </c>
       <c r="N24" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="O24" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="P24" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B25" s="3">
         <v>2</v>
@@ -2932,46 +3038,49 @@
       <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>48</v>
+      <c r="E25" s="14">
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" t="s">
-        <v>376</v>
+        <v>395</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M25" t="s">
-        <v>236</v>
+        <v>372</v>
       </c>
       <c r="N25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="O25" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="P25" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B26" s="3">
         <v>2</v>
@@ -2982,46 +3091,49 @@
       <c r="D26" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>48</v>
+      <c r="E26" s="14">
+        <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L26" t="s">
-        <v>377</v>
+        <v>395</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M26" t="s">
-        <v>238</v>
+        <v>373</v>
       </c>
       <c r="N26" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="O26" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="P26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B27" s="3">
         <v>2</v>
@@ -3032,46 +3144,49 @@
       <c r="D27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>48</v>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L27" t="s">
-        <v>378</v>
+        <v>395</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>240</v>
+        <v>374</v>
       </c>
       <c r="N27" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O27" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="P27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B28" s="3">
         <v>2</v>
@@ -3082,46 +3197,49 @@
       <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>48</v>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L28" t="s">
-        <v>379</v>
+        <v>395</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M28" t="s">
-        <v>242</v>
+        <v>375</v>
       </c>
       <c r="N28" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O28" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="P28" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B29" s="3">
         <v>2</v>
@@ -3132,46 +3250,49 @@
       <c r="D29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>48</v>
+      <c r="E29" s="14">
+        <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K29" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L29" t="s">
-        <v>380</v>
+        <v>395</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M29" t="s">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="N29" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="O29" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B30" s="3">
         <v>2</v>
@@ -3182,46 +3303,49 @@
       <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>48</v>
+      <c r="E30" s="14">
+        <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K30" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L30" t="s">
-        <v>381</v>
+        <v>395</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M30" t="s">
-        <v>247</v>
+        <v>377</v>
       </c>
       <c r="N30" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="O30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P30" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B31" s="3">
         <v>2</v>
@@ -3232,96 +3356,102 @@
       <c r="D31" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>48</v>
+      <c r="E31" s="14">
+        <v>0</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L31" t="s">
-        <v>382</v>
+        <v>395</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M31" t="s">
+        <v>378</v>
+      </c>
+      <c r="N31" t="s">
+        <v>246</v>
+      </c>
+      <c r="O31" t="s">
+        <v>247</v>
+      </c>
+      <c r="P31" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" s="22">
+        <v>2</v>
+      </c>
+      <c r="C32" s="22">
+        <v>1</v>
+      </c>
+      <c r="D32" s="12">
+        <v>1</v>
+      </c>
+      <c r="E32" s="15">
+        <v>0</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M32" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="N32" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="O32" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="N31" t="s">
-        <v>250</v>
-      </c>
-      <c r="O31" t="s">
-        <v>246</v>
-      </c>
-      <c r="P31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" s="3">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3">
-        <v>1</v>
-      </c>
-      <c r="D32" s="2">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L32" t="s">
-        <v>383</v>
-      </c>
-      <c r="M32" t="s">
-        <v>251</v>
-      </c>
-      <c r="N32" t="s">
-        <v>252</v>
-      </c>
-      <c r="O32" t="s">
-        <v>246</v>
-      </c>
-      <c r="P32" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q32" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3">
         <v>2</v>
@@ -3332,46 +3462,49 @@
       <c r="D33" s="2">
         <v>1</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>48</v>
+      <c r="E33" s="14">
+        <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K33" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L33" t="s">
-        <v>384</v>
+        <v>395</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M33" t="s">
-        <v>253</v>
+        <v>380</v>
       </c>
       <c r="N33" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="O33" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="P33" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B34" s="3">
         <v>2</v>
@@ -3382,96 +3515,102 @@
       <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>48</v>
+      <c r="E34" s="14">
+        <v>0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K34" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L34" t="s">
-        <v>385</v>
+        <v>395</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M34" t="s">
+        <v>381</v>
+      </c>
+      <c r="N34" t="s">
+        <v>252</v>
+      </c>
+      <c r="O34" t="s">
+        <v>253</v>
+      </c>
+      <c r="P34" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="22">
+        <v>2</v>
+      </c>
+      <c r="C35" s="22">
+        <v>1</v>
+      </c>
+      <c r="D35" s="12">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M35" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="N35" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="O35" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="N34" t="s">
-        <v>256</v>
-      </c>
-      <c r="O34" t="s">
-        <v>246</v>
-      </c>
-      <c r="P34" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="3">
-        <v>2</v>
-      </c>
-      <c r="C35" s="3">
-        <v>1</v>
-      </c>
-      <c r="D35" s="2">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L35" t="s">
-        <v>386</v>
-      </c>
-      <c r="M35" t="s">
-        <v>257</v>
-      </c>
-      <c r="N35" t="s">
-        <v>258</v>
-      </c>
-      <c r="O35" t="s">
-        <v>246</v>
-      </c>
-      <c r="P35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q35" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B36" s="3">
         <v>2</v>
@@ -3482,46 +3621,49 @@
       <c r="D36" s="2">
         <v>1</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>48</v>
+      <c r="E36" s="14">
+        <v>0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L36" t="s">
-        <v>387</v>
+        <v>395</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M36" t="s">
-        <v>259</v>
+        <v>383</v>
       </c>
       <c r="N36" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="O36" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="P36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3">
         <v>2</v>
@@ -3532,46 +3674,49 @@
       <c r="D37" s="2">
         <v>1</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>48</v>
+      <c r="E37" s="14">
+        <v>0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L37" t="s">
-        <v>388</v>
+        <v>395</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M37" t="s">
-        <v>261</v>
+        <v>384</v>
       </c>
       <c r="N37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="O37" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="P37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B38" s="3">
         <v>2</v>
@@ -3582,46 +3727,49 @@
       <c r="D38" s="2">
         <v>1</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>48</v>
+      <c r="E38" s="14">
+        <v>0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>399</v>
-      </c>
       <c r="K38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L38" t="s">
-        <v>389</v>
+        <v>395</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M38" t="s">
-        <v>263</v>
+        <v>385</v>
       </c>
       <c r="N38" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="O38" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="P38" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3">
         <v>2</v>
@@ -3632,46 +3780,49 @@
       <c r="D39" s="2">
         <v>1</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>48</v>
+      <c r="E39" s="14">
+        <v>0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L39" t="s">
-        <v>390</v>
+        <v>394</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M39" t="s">
-        <v>265</v>
+        <v>386</v>
       </c>
       <c r="N39" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="O39" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="P39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B40" s="3">
         <v>2</v>
@@ -3682,96 +3833,102 @@
       <c r="D40" s="2">
         <v>1</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>48</v>
+      <c r="E40" s="14">
+        <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L40" t="s">
-        <v>391</v>
+        <v>394</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M40" t="s">
+        <v>387</v>
+      </c>
+      <c r="N40" t="s">
+        <v>264</v>
+      </c>
+      <c r="O40" t="s">
+        <v>265</v>
+      </c>
+      <c r="P40" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" s="22">
+        <v>2</v>
+      </c>
+      <c r="C41" s="22">
+        <v>1</v>
+      </c>
+      <c r="D41" s="12">
+        <v>1</v>
+      </c>
+      <c r="E41" s="15">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J41" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K41" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M41" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="N41" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="O41" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="N40" t="s">
+      <c r="P41" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="O40" t="s">
-        <v>246</v>
-      </c>
-      <c r="P40" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>93</v>
-      </c>
-      <c r="B41" s="3">
-        <v>2</v>
-      </c>
-      <c r="C41" s="3">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" t="s">
-        <v>392</v>
-      </c>
-      <c r="M41" t="s">
-        <v>269</v>
-      </c>
-      <c r="N41" t="s">
-        <v>270</v>
-      </c>
-      <c r="O41" t="s">
-        <v>271</v>
-      </c>
-      <c r="P41" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B42" s="3">
         <v>2</v>
@@ -3782,46 +3939,49 @@
       <c r="D42" s="2">
         <v>1</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>48</v>
+      <c r="E42" s="14">
+        <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K42" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L42" t="s">
-        <v>393</v>
+        <v>394</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M42" t="s">
-        <v>272</v>
+        <v>389</v>
       </c>
       <c r="N42" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="O42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P42" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3">
         <v>2</v>
@@ -3832,46 +3992,49 @@
       <c r="D43" s="2">
         <v>1</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>48</v>
+      <c r="E43" s="14">
+        <v>0</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K43" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L43" t="s">
         <v>394</v>
       </c>
+      <c r="L43" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="M43" t="s">
-        <v>274</v>
+        <v>390</v>
       </c>
       <c r="N43" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O43" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P43" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B44" s="3">
         <v>2</v>
@@ -3882,46 +4045,49 @@
       <c r="D44" s="2">
         <v>1</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>48</v>
+      <c r="E44" s="14">
+        <v>0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K44" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L44" t="s">
-        <v>395</v>
+        <v>394</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M44" t="s">
-        <v>276</v>
+        <v>391</v>
       </c>
       <c r="N44" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="O44" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P44" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3">
         <v>2</v>
@@ -3932,46 +4098,49 @@
       <c r="D45" s="2">
         <v>1</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>48</v>
+      <c r="E45" s="14">
+        <v>0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="K45" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L45" t="s">
-        <v>396</v>
+        <v>394</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M45" t="s">
-        <v>278</v>
+        <v>392</v>
       </c>
       <c r="N45" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="O45" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="P45" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B46" s="5">
         <v>2</v>
@@ -3982,44 +4151,47 @@
       <c r="D46" s="6">
         <v>1</v>
       </c>
-      <c r="E46" s="7" t="s">
-        <v>48</v>
+      <c r="E46" s="14">
+        <v>0</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I46" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J46" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="K46" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>397</v>
+      <c r="K46" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L46" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>280</v>
+        <v>393</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+      <c r="Q46" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -4030,46 +4202,49 @@
         <v>1</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K47" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="O47" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q47" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -4080,46 +4255,49 @@
         <v>1</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K48" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>118</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -4130,46 +4308,49 @@
         <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K49" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>9</v>
       </c>
@@ -4180,46 +4361,49 @@
         <v>1</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J50" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K50" s="7" t="s">
-        <v>46</v>
+      <c r="K50" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>123</v>
+        <v>43</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N50" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O50" s="7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P50" s="7" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>10</v>
       </c>
@@ -4230,46 +4414,49 @@
         <v>1</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E51" s="14">
+        <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K51" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L51" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q51" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4280,46 +4467,49 @@
         <v>1</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K52" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>125</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
@@ -4330,48 +4520,51 @@
         <v>1</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H53" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I53" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="J53" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>46</v>
+      <c r="K53" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L53" s="11" t="s">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="M53" s="11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>352</v>
+        <v>122</v>
       </c>
       <c r="P53" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+      <c r="Q53" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B54" s="6">
         <v>3</v>
@@ -4380,46 +4573,49 @@
         <v>1</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="E54" s="14">
+        <v>0</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J54" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J54" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K54" s="7" t="s">
-        <v>46</v>
+      <c r="K54" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="M54" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O54" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P54" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>13</v>
       </c>
@@ -4430,46 +4626,49 @@
         <v>1</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="E55" s="14">
+        <v>1</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J55" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K55" s="7" t="s">
-        <v>46</v>
+      <c r="K55" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>14</v>
       </c>
@@ -4480,46 +4679,49 @@
         <v>1</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K56" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q56" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="M56" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -4530,46 +4732,49 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K57" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>132</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -4580,46 +4785,49 @@
         <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="I58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K58" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>17</v>
       </c>
@@ -4630,46 +4838,49 @@
         <v>1</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="I59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>46</v>
+      <c r="K59" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>137</v>
+        <v>43</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N59" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O59" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="P59" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="Q59" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>18</v>
       </c>
@@ -4680,46 +4891,49 @@
         <v>1</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K60" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q60" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="M60" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>19</v>
       </c>
@@ -4730,46 +4944,49 @@
         <v>1</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>38</v>
       </c>
       <c r="I61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="J61" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J61" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>46</v>
+      <c r="K61" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>142</v>
+        <v>43</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>139</v>
       </c>
       <c r="O61" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="P61" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q61" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="P61" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -4780,46 +4997,49 @@
         <v>1</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I62" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K62" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q62" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
@@ -4830,46 +5050,49 @@
         <v>1</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K63" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="M63" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P63" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q63" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>24</v>
       </c>
@@ -4880,96 +5103,102 @@
         <v>1</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E64" s="14">
+        <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K64" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" s="12">
+        <v>3</v>
+      </c>
+      <c r="C65" s="12">
+        <v>1</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" s="14">
+        <v>1</v>
+      </c>
+      <c r="F65" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="G65" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="J65" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L65" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="M65" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="N65" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="N64" s="1" t="s">
+      <c r="O65" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="O64" s="1" t="s">
+      <c r="P65" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="P64" s="1" t="s">
+      <c r="Q65" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B65" s="2">
-        <v>3</v>
-      </c>
-      <c r="C65" s="2">
-        <v>1</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
@@ -4980,46 +5209,49 @@
         <v>1</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E66" s="14">
+        <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K66" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="M66" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q66" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -5030,46 +5262,49 @@
         <v>1</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K67" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="P67" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q67" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>28</v>
       </c>
@@ -5080,96 +5315,102 @@
         <v>1</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>398</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>39</v>
       </c>
       <c r="I68" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K68" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="18">
+        <v>3</v>
+      </c>
+      <c r="C69" s="18">
+        <v>1</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="14">
+        <v>1</v>
+      </c>
+      <c r="F69" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="G69" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="J69" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L69" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="M69" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="N69" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="N68" s="1" t="s">
+      <c r="O69" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="O68" s="1" t="s">
+      <c r="P69" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="P68" s="1" t="s">
+      <c r="Q69" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B69" s="6">
-        <v>3</v>
-      </c>
-      <c r="C69" s="6">
-        <v>1</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="M69" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="N69" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="O69" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="P69" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
@@ -5180,46 +5421,49 @@
         <v>1</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E70" s="14">
+        <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K70" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N70" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="O70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="P70" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>31</v>
       </c>
@@ -5230,48 +5474,51 @@
         <v>1</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>38</v>
       </c>
       <c r="I71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J71" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K71" s="1" t="s">
-        <v>46</v>
+        <v>394</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>171</v>
+        <v>43</v>
       </c>
       <c r="M71" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N71" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="O71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="P71" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>169</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B72" s="5">
         <v>3</v>
@@ -5280,48 +5527,51 @@
         <v>1</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H72" s="7" t="s">
         <v>39</v>
       </c>
       <c r="I72" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J72" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J72" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>174</v>
+      <c r="K72" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="P72" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q72" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B73" s="3">
         <v>2</v>
@@ -5330,48 +5580,51 @@
         <v>1</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K73" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L73" t="s">
-        <v>177</v>
+        <v>394</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M73" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N73" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="O73" t="s">
-        <v>179</v>
-      </c>
-      <c r="P73" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="P73" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q73" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B74" s="3">
         <v>2</v>
@@ -5380,98 +5633,104 @@
         <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E74" s="14">
+        <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K74" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L74" t="s">
-        <v>180</v>
+        <v>394</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M74" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N74" t="s">
+        <v>177</v>
+      </c>
+      <c r="O74" t="s">
+        <v>175</v>
+      </c>
+      <c r="P74" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="22">
+        <v>2</v>
+      </c>
+      <c r="C75" s="22">
+        <v>1</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E75" s="15">
+        <v>0</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J75" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K75" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L75" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M75" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="O74" t="s">
-        <v>179</v>
-      </c>
-      <c r="P74" s="1" t="s">
+      <c r="N75" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="O75" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="P75" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q75" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>103</v>
-      </c>
-      <c r="B75" s="3">
-        <v>2</v>
-      </c>
-      <c r="C75" s="3">
-        <v>1</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L75" t="s">
-        <v>181</v>
-      </c>
-      <c r="M75" t="s">
-        <v>181</v>
-      </c>
-      <c r="N75" t="s">
-        <v>178</v>
-      </c>
-      <c r="O75" t="s">
-        <v>179</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B76" s="3">
         <v>2</v>
@@ -5480,48 +5739,51 @@
         <v>1</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E76" s="14">
+        <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K76" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L76" t="s">
-        <v>182</v>
+        <v>394</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M76" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="N76" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O76" t="s">
-        <v>303</v>
-      </c>
-      <c r="P76" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="P76" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q76" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B77" s="3">
         <v>2</v>
@@ -5530,98 +5792,104 @@
         <v>1</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E77" s="14">
+        <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K77" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L77" t="s">
-        <v>185</v>
+        <v>394</v>
+      </c>
+      <c r="L77" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M77" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="N77" t="s">
+        <v>182</v>
+      </c>
+      <c r="O77" t="s">
+        <v>180</v>
+      </c>
+      <c r="P77" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="22">
+        <v>2</v>
+      </c>
+      <c r="C78" s="22">
+        <v>1</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E78" s="15">
+        <v>0</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G78" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H78" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J78" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K78" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L78" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M78" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="O77" t="s">
-        <v>184</v>
-      </c>
-      <c r="P77" s="1" t="s">
+      <c r="N78" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="O78" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="P78" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q78" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>106</v>
-      </c>
-      <c r="B78" s="3">
-        <v>2</v>
-      </c>
-      <c r="C78" s="3">
-        <v>1</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L78" t="s">
-        <v>186</v>
-      </c>
-      <c r="M78" t="s">
-        <v>186</v>
-      </c>
-      <c r="N78" t="s">
-        <v>183</v>
-      </c>
-      <c r="O78" t="s">
-        <v>184</v>
-      </c>
-      <c r="P78" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B79" s="3">
         <v>2</v>
@@ -5630,48 +5898,51 @@
         <v>1</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E79" s="14">
+        <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J79" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K79" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L79" t="s">
+        <v>394</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M79" t="s">
+        <v>307</v>
+      </c>
+      <c r="N79" t="s">
+        <v>307</v>
+      </c>
+      <c r="O79" t="s">
         <v>310</v>
       </c>
-      <c r="M79" t="s">
-        <v>310</v>
-      </c>
-      <c r="N79" t="s">
-        <v>313</v>
-      </c>
-      <c r="O79" t="s">
-        <v>309</v>
-      </c>
-      <c r="P79" s="1" t="s">
+      <c r="P79" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q79" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B80" s="3">
         <v>2</v>
@@ -5680,98 +5951,104 @@
         <v>1</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E80" s="14">
+        <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K80" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L80" t="s">
+        <v>394</v>
+      </c>
+      <c r="L80" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M80" t="s">
+        <v>308</v>
+      </c>
+      <c r="N80" t="s">
+        <v>308</v>
+      </c>
+      <c r="O80" t="s">
+        <v>310</v>
+      </c>
+      <c r="P80" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B81" s="22">
+        <v>2</v>
+      </c>
+      <c r="C81" s="22">
+        <v>1</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E81" s="15">
+        <v>0</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G81" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="M80" t="s">
-        <v>311</v>
-      </c>
-      <c r="N80" t="s">
-        <v>313</v>
-      </c>
-      <c r="O80" t="s">
+      <c r="H81" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J81" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K81" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L81" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M81" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="P80" s="1" t="s">
+      <c r="N81" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="O81" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="P81" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q81" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>109</v>
-      </c>
-      <c r="B81" s="3">
-        <v>2</v>
-      </c>
-      <c r="C81" s="3">
-        <v>1</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L81" t="s">
-        <v>312</v>
-      </c>
-      <c r="M81" t="s">
-        <v>312</v>
-      </c>
-      <c r="N81" t="s">
-        <v>313</v>
-      </c>
-      <c r="O81" t="s">
-        <v>309</v>
-      </c>
-      <c r="P81" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B82" s="3">
         <v>2</v>
@@ -5780,48 +6057,51 @@
         <v>1</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E82" s="14">
+        <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K82" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L82" t="s">
+        <v>394</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M82" t="s">
+        <v>302</v>
+      </c>
+      <c r="N82" t="s">
+        <v>302</v>
+      </c>
+      <c r="O82" t="s">
+        <v>301</v>
+      </c>
+      <c r="P82" t="s">
         <v>305</v>
       </c>
-      <c r="M82" t="s">
-        <v>305</v>
-      </c>
-      <c r="N82" t="s">
-        <v>304</v>
-      </c>
-      <c r="O82" t="s">
-        <v>308</v>
-      </c>
-      <c r="P82" s="1" t="s">
+      <c r="Q82" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B83" s="3">
         <v>2</v>
@@ -5830,98 +6110,104 @@
         <v>1</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E83" s="14">
+        <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K83" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L83" t="s">
-        <v>306</v>
+        <v>394</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M83" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="N83" t="s">
+        <v>303</v>
+      </c>
+      <c r="O83" t="s">
+        <v>301</v>
+      </c>
+      <c r="P83" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="B84" s="22">
+        <v>2</v>
+      </c>
+      <c r="C84" s="22">
+        <v>1</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E84" s="15">
+        <v>0</v>
+      </c>
+      <c r="F84" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G84" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H84" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J84" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K84" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L84" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M84" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="O83" t="s">
-        <v>308</v>
-      </c>
-      <c r="P83" s="1" t="s">
+      <c r="N84" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="O84" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="P84" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q84" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>292</v>
-      </c>
-      <c r="B84" s="3">
-        <v>2</v>
-      </c>
-      <c r="C84" s="3">
-        <v>1</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L84" t="s">
-        <v>307</v>
-      </c>
-      <c r="M84" t="s">
-        <v>307</v>
-      </c>
-      <c r="N84" t="s">
-        <v>304</v>
-      </c>
-      <c r="O84" t="s">
-        <v>308</v>
-      </c>
-      <c r="P84" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B85" s="3">
         <v>2</v>
@@ -5930,48 +6216,51 @@
         <v>1</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E85" s="14">
+        <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I85" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J85" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J85" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K85" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L85" t="s">
+        <v>394</v>
+      </c>
+      <c r="L85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M85" t="s">
+        <v>290</v>
+      </c>
+      <c r="N85" t="s">
+        <v>290</v>
+      </c>
+      <c r="O85" t="s">
         <v>293</v>
       </c>
-      <c r="M85" t="s">
-        <v>293</v>
-      </c>
-      <c r="N85" t="s">
-        <v>296</v>
-      </c>
-      <c r="O85" t="s">
-        <v>297</v>
-      </c>
-      <c r="P85" s="1" t="s">
+      <c r="P85" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q85" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B86" s="3">
         <v>2</v>
@@ -5980,98 +6269,104 @@
         <v>1</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E86" s="14">
+        <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K86" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L86" t="s">
+        <v>394</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M86" t="s">
+        <v>291</v>
+      </c>
+      <c r="N86" t="s">
+        <v>291</v>
+      </c>
+      <c r="O86" t="s">
+        <v>293</v>
+      </c>
+      <c r="P86" t="s">
         <v>294</v>
       </c>
-      <c r="M86" t="s">
+      <c r="Q86" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B87" s="22">
+        <v>2</v>
+      </c>
+      <c r="C87" s="22">
+        <v>1</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" s="15">
+        <v>0</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G87" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J87" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K87" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L87" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M87" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="N87" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="O87" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="P87" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="N86" t="s">
-        <v>296</v>
-      </c>
-      <c r="O86" t="s">
-        <v>297</v>
-      </c>
-      <c r="P86" s="1" t="s">
+      <c r="Q87" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>112</v>
-      </c>
-      <c r="B87" s="3">
-        <v>2</v>
-      </c>
-      <c r="C87" s="3">
-        <v>1</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H87" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L87" t="s">
-        <v>295</v>
-      </c>
-      <c r="M87" t="s">
-        <v>295</v>
-      </c>
-      <c r="N87" t="s">
-        <v>296</v>
-      </c>
-      <c r="O87" t="s">
-        <v>297</v>
-      </c>
-      <c r="P87" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B88" s="3">
         <v>2</v>
@@ -6080,48 +6375,51 @@
         <v>1</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E88" s="14">
+        <v>0</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K88" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L88" t="s">
+        <v>394</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M88" t="s">
+        <v>296</v>
+      </c>
+      <c r="N88" t="s">
+        <v>296</v>
+      </c>
+      <c r="O88" t="s">
+        <v>295</v>
+      </c>
+      <c r="P88" t="s">
         <v>299</v>
       </c>
-      <c r="M88" t="s">
-        <v>299</v>
-      </c>
-      <c r="N88" t="s">
-        <v>298</v>
-      </c>
-      <c r="O88" t="s">
-        <v>302</v>
-      </c>
-      <c r="P88" s="1" t="s">
+      <c r="Q88" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B89" s="3">
         <v>2</v>
@@ -6130,248 +6428,263 @@
         <v>1</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>48</v>
+        <v>113</v>
+      </c>
+      <c r="E89" s="14">
+        <v>0</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>314</v>
+        <v>45</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K89" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L89" t="s">
-        <v>300</v>
+        <v>394</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M89" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="N89" t="s">
+        <v>297</v>
+      </c>
+      <c r="O89" t="s">
+        <v>295</v>
+      </c>
+      <c r="P89" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="B90" s="24">
+        <v>2</v>
+      </c>
+      <c r="C90" s="24">
+        <v>1</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" s="15">
+        <v>0</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G90" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I90" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J90" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K90" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L90" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M90" s="23" t="s">
         <v>298</v>
       </c>
-      <c r="O89" t="s">
-        <v>302</v>
-      </c>
-      <c r="P89" s="1" t="s">
+      <c r="N90" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="O90" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="P90" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q90" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B90" s="5">
+    <row r="91" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="B91" s="22">
         <v>2</v>
       </c>
-      <c r="C90" s="5">
-        <v>1</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H90" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I90" s="7" t="s">
+      <c r="C91" s="22">
+        <v>1</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" s="15">
+        <v>0</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G91" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H91" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I91" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J91" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J90" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K90" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="M90" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="N90" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="O90" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="P90" s="7" t="s">
+      <c r="K91" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L91" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M91" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="N91" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="O91" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="P91" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="Q91" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>284</v>
-      </c>
-      <c r="B91" s="3">
+    <row r="92" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B92" s="24">
         <v>2</v>
       </c>
-      <c r="C91" s="3">
-        <v>1</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H91" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I91" s="1" t="s">
+      <c r="C92" s="24">
+        <v>1</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" s="15">
+        <v>0</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J92" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="J91" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L91" t="s">
-        <v>287</v>
-      </c>
-      <c r="M91" t="s">
-        <v>287</v>
-      </c>
-      <c r="N91" t="s">
+      <c r="K92" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L92" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="M92" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="N92" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="O92" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="O91" t="s">
-        <v>282</v>
-      </c>
-      <c r="P91" s="1" t="s">
+      <c r="P92" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q92" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="B92" s="5">
+    <row r="93" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B93" s="22">
         <v>2</v>
       </c>
-      <c r="C92" s="5">
-        <v>1</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H92" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I92" s="7" t="s">
+      <c r="C93" s="22">
+        <v>1</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E93" s="15">
+        <v>0</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G93" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H93" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I93" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J93" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J92" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="M92" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="N92" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="O92" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="P92" s="7" t="s">
+      <c r="K93" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L93" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M93" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="N93" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="O93" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="P93" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q93" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A93" s="8" t="s">
-        <v>315</v>
-      </c>
-      <c r="B93" s="3">
-        <v>2</v>
-      </c>
-      <c r="C93" s="3">
-        <v>1</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J93" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L93" t="s">
-        <v>324</v>
-      </c>
-      <c r="M93" t="s">
-        <v>324</v>
-      </c>
-      <c r="N93" t="s">
-        <v>321</v>
-      </c>
-      <c r="O93" t="s">
-        <v>330</v>
-      </c>
-      <c r="P93" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B94" s="3">
         <v>2</v>
@@ -6380,98 +6693,104 @@
         <v>1</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E94" s="14">
+        <v>0</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J94" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K94" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L94" t="s">
-        <v>325</v>
+        <v>394</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="M94" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="N94" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O94" t="s">
-        <v>330</v>
-      </c>
-      <c r="P94" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P94" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q94" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A95" s="8" t="s">
-        <v>317</v>
-      </c>
-      <c r="B95" s="3">
+    <row r="95" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B95" s="22">
         <v>2</v>
       </c>
-      <c r="C95" s="3">
-        <v>1</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G95" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I95" s="1" t="s">
+      <c r="C95" s="22">
+        <v>1</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E95" s="15">
+        <v>0</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G95" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H95" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I95" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J95" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="J95" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L95" t="s">
-        <v>326</v>
-      </c>
-      <c r="M95" t="s">
-        <v>326</v>
-      </c>
-      <c r="N95" t="s">
-        <v>322</v>
-      </c>
-      <c r="O95" t="s">
-        <v>330</v>
-      </c>
-      <c r="P95" s="1" t="s">
+      <c r="K95" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L95" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M95" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="N95" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="O95" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="P95" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q95" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B96" s="3">
         <v>2</v>
@@ -6480,98 +6799,104 @@
         <v>1</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E96" s="14">
+        <v>0</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>35</v>
       </c>
       <c r="I96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J96" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J96" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="K96" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L96" t="s">
+        <v>394</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M96" t="s">
+        <v>324</v>
+      </c>
+      <c r="N96" t="s">
+        <v>324</v>
+      </c>
+      <c r="O96" t="s">
+        <v>319</v>
+      </c>
+      <c r="P96" t="s">
         <v>327</v>
       </c>
-      <c r="M96" t="s">
+      <c r="Q96" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B97" s="22">
+        <v>2</v>
+      </c>
+      <c r="C97" s="22">
+        <v>1</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="15">
+        <v>0</v>
+      </c>
+      <c r="F97" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="G97" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H97" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I97" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J97" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="K97" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="L97" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="M97" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="N97" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="O97" s="13" t="s">
+        <v>320</v>
+      </c>
+      <c r="P97" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="N96" t="s">
-        <v>322</v>
-      </c>
-      <c r="O96" t="s">
-        <v>330</v>
-      </c>
-      <c r="P96" s="1" t="s">
+      <c r="Q97" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A97" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="B97" s="3">
-        <v>2</v>
-      </c>
-      <c r="C97" s="3">
-        <v>1</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L97" t="s">
-        <v>328</v>
-      </c>
-      <c r="M97" t="s">
-        <v>328</v>
-      </c>
-      <c r="N97" t="s">
-        <v>323</v>
-      </c>
-      <c r="O97" t="s">
-        <v>330</v>
-      </c>
-      <c r="P97" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
         <v>2</v>
@@ -6580,48 +6905,51 @@
         <v>1</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E98" s="14">
+        <v>0</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>35</v>
       </c>
       <c r="I98" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J98" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="J98" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>329</v>
+      <c r="K98" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="N98" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="P98" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="P98" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q98" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B99" s="3">
         <v>3</v>
@@ -6630,48 +6958,51 @@
         <v>1</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E99" s="14">
+        <v>0</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>39</v>
+        <v>346</v>
       </c>
       <c r="I99" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="J99" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J99" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K99" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L99" t="s">
-        <v>338</v>
+      <c r="K99" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L99" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="M99" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="N99" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="O99" t="s">
-        <v>346</v>
-      </c>
-      <c r="P99" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="P99" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q99" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B100" s="3">
         <v>3</v>
@@ -6680,48 +7011,51 @@
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E100" s="14">
+        <v>0</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>39</v>
+        <v>346</v>
       </c>
       <c r="I100" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="J100" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J100" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K100" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L100" t="s">
-        <v>339</v>
+      <c r="K100" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L100" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="M100" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="N100" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="O100" t="s">
-        <v>346</v>
-      </c>
-      <c r="P100" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="P100" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q100" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B101" s="3">
         <v>3</v>
@@ -6730,48 +7064,51 @@
         <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E101" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E101" s="14">
+        <v>0</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="I101" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="J101" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J101" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K101" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L101" t="s">
-        <v>341</v>
+      <c r="K101" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L101" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="M101" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="N101" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="O101" t="s">
-        <v>347</v>
-      </c>
-      <c r="P101" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="P101" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q101" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B102" s="3">
         <v>3</v>
@@ -6780,48 +7117,51 @@
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E102" s="14">
+        <v>0</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="I102" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="J102" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J102" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L102" t="s">
-        <v>342</v>
+      <c r="K102" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L102" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="M102" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="N102" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O102" t="s">
-        <v>347</v>
-      </c>
-      <c r="P102" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="P102" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q102" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B103" s="3">
         <v>3</v>
@@ -6830,48 +7170,51 @@
         <v>1</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E103" s="14">
+        <v>0</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>39</v>
+        <v>403</v>
       </c>
       <c r="I103" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="J103" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J103" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K103" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L103" t="s">
-        <v>344</v>
+      <c r="K103" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L103" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="M103" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="N103" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="O103" t="s">
-        <v>348</v>
-      </c>
-      <c r="P103" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="P103" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q103" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B104" s="3">
         <v>3</v>
@@ -6880,92 +7223,45 @@
         <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="E104" s="14">
+        <v>0</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>39</v>
+        <v>403</v>
       </c>
       <c r="I104" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="J104" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J104" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K104" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L104" t="s">
+      <c r="K104" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="L104" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M104" t="s">
+        <v>342</v>
+      </c>
+      <c r="N104" t="s">
+        <v>342</v>
+      </c>
+      <c r="O104" t="s">
+        <v>340</v>
+      </c>
+      <c r="P104" t="s">
         <v>345</v>
       </c>
-      <c r="M104" t="s">
-        <v>345</v>
-      </c>
-      <c r="N104" t="s">
-        <v>343</v>
-      </c>
-      <c r="O104" t="s">
-        <v>348</v>
-      </c>
-      <c r="P104" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>349</v>
-      </c>
-      <c r="B105" s="3">
-        <v>3</v>
-      </c>
-      <c r="C105" s="3">
-        <v>1</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E105" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G105" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="I105" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J105" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="K105" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L105" t="s">
-        <v>345</v>
-      </c>
-      <c r="M105" t="s">
-        <v>345</v>
-      </c>
-      <c r="N105" t="s">
-        <v>343</v>
-      </c>
-      <c r="O105" t="s">
-        <v>348</v>
-      </c>
-      <c r="P105" s="1" t="s">
+      <c r="Q104" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB39B33-F6B6-4B5F-BB4A-72A76C4EEE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58673F7A-C9FC-4E2A-A02C-A09169844A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="2700" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1575" yWindow="5025" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="405">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1342,6 +1342,10 @@
   </si>
   <si>
     <t>(9,31,31)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dark</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1736,24 +1740,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="33.25" customWidth="1"/>
     <col min="2" max="3" width="5" style="3" customWidth="1"/>
-    <col min="4" max="5" width="5" style="2" customWidth="1"/>
-    <col min="6" max="7" width="9.125" customWidth="1"/>
-    <col min="8" max="8" width="12.25" style="1" customWidth="1"/>
-    <col min="9" max="10" width="10.25" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="42.625" customWidth="1"/>
-    <col min="14" max="14" width="99.625" customWidth="1"/>
-    <col min="15" max="15" width="111.125" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
+    <col min="4" max="6" width="5" style="2" customWidth="1"/>
+    <col min="7" max="8" width="9.125" customWidth="1"/>
+    <col min="9" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="11" width="10.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9.625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="42.625" customWidth="1"/>
+    <col min="15" max="15" width="99.625" customWidth="1"/>
+    <col min="16" max="16" width="111.125" customWidth="1"/>
+    <col min="17" max="17" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1769,44 +1773,47 @@
       <c r="E1" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1822,44 +1829,47 @@
       <c r="E2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>45</v>
+      <c r="F2" s="14">
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -1875,44 +1885,47 @@
       <c r="E3" s="14">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>45</v>
+      <c r="F3" s="14">
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L3" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>54</v>
       </c>
@@ -1928,44 +1941,47 @@
       <c r="E4" s="14">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>45</v>
+      <c r="F4" s="14">
+        <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>55</v>
       </c>
@@ -1981,44 +1997,47 @@
       <c r="E5" s="14">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>45</v>
+      <c r="F5" s="14">
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L5" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="R5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>56</v>
       </c>
@@ -2034,44 +2053,47 @@
       <c r="E6" s="14">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>45</v>
+      <c r="F6" s="14">
+        <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>57</v>
       </c>
@@ -2087,44 +2109,47 @@
       <c r="E7" s="14">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>45</v>
+      <c r="F7" s="14">
+        <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>58</v>
       </c>
@@ -2140,44 +2165,47 @@
       <c r="E8" s="14">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>45</v>
+      <c r="F8" s="14">
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
@@ -2193,44 +2221,47 @@
       <c r="E9" s="14">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>45</v>
+      <c r="F9" s="14">
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>96</v>
       </c>
@@ -2246,44 +2277,47 @@
       <c r="E10" s="14">
         <v>0</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>45</v>
+      <c r="F10" s="14">
+        <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
         <v>32</v>
       </c>
@@ -2299,44 +2333,47 @@
       <c r="E11" s="15">
         <v>0</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>45</v>
+      <c r="F11" s="14">
+        <v>0</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="M11" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N11" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="N11" s="11" t="s">
+      <c r="O11" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="O11" s="11" t="s">
+      <c r="P11" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="P11" s="11" t="s">
+      <c r="Q11" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="Q11" s="11" t="s">
+      <c r="R11" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -2352,44 +2389,47 @@
       <c r="E12" s="14">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>45</v>
+      <c r="F12" s="14">
+        <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N12" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
@@ -2405,44 +2445,47 @@
       <c r="E13" s="14">
         <v>0</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>45</v>
+      <c r="F13" s="14">
+        <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>65</v>
       </c>
@@ -2458,44 +2501,47 @@
       <c r="E14" s="15">
         <v>0</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>45</v>
+      <c r="F14" s="14">
+        <v>0</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="L14" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="M14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="N14" s="11" t="s">
+      <c r="O14" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="P14" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="P14" s="11" t="s">
+      <c r="Q14" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="Q14" s="11" t="s">
+      <c r="R14" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>66</v>
       </c>
@@ -2511,44 +2557,47 @@
       <c r="E15" s="14">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>45</v>
+      <c r="F15" s="14">
+        <v>0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q15" s="1" t="s">
+      <c r="R15" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -2564,44 +2613,47 @@
       <c r="E16" s="14">
         <v>0</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>45</v>
+      <c r="F16" s="14">
+        <v>0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M16" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N16" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>61</v>
       </c>
@@ -2617,44 +2669,47 @@
       <c r="E17" s="14">
         <v>0</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>45</v>
+      <c r="F17" s="14">
+        <v>0</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>62</v>
       </c>
@@ -2670,44 +2725,47 @@
       <c r="E18" s="14">
         <v>0</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>45</v>
+      <c r="F18" s="14">
+        <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N18" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="O18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>63</v>
       </c>
@@ -2723,44 +2781,47 @@
       <c r="E19" s="14">
         <v>0</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>45</v>
+      <c r="F19" s="14">
+        <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
         <v>68</v>
       </c>
@@ -2776,44 +2837,47 @@
       <c r="E20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="19" t="s">
-        <v>45</v>
+      <c r="F20" s="14">
+        <v>0</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I20" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J20" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K20" s="19" t="s">
+      <c r="L20" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="L20" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="N20" s="21" t="s">
+      <c r="O20" s="21" t="s">
         <v>222</v>
       </c>
-      <c r="O20" s="21" t="s">
+      <c r="P20" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="P20" s="21" t="s">
+      <c r="Q20" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="Q20" s="21" t="s">
+      <c r="R20" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -2829,44 +2893,47 @@
       <c r="E21" s="14">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>45</v>
+      <c r="F21" s="14">
+        <v>0</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" t="s">
+      <c r="M21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" t="s">
         <v>368</v>
       </c>
-      <c r="N21" t="s">
+      <c r="O21" t="s">
         <v>225</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>226</v>
       </c>
-      <c r="P21" t="s">
+      <c r="Q21" t="s">
         <v>224</v>
       </c>
-      <c r="Q21" t="s">
+      <c r="R21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -2882,44 +2949,47 @@
       <c r="E22" s="14">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>45</v>
+      <c r="F22" s="14">
+        <v>0</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" t="s">
+      <c r="M22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" t="s">
         <v>369</v>
       </c>
-      <c r="N22" t="s">
+      <c r="O22" t="s">
         <v>227</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>228</v>
       </c>
-      <c r="P22" t="s">
+      <c r="Q22" t="s">
         <v>224</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="R22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
         <v>72</v>
       </c>
@@ -2935,44 +3005,47 @@
       <c r="E23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="19" t="s">
-        <v>45</v>
+      <c r="F23" s="14">
+        <v>0</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I23" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J23" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="L23" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="L23" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M23" s="21" t="s">
+      <c r="M23" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N23" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="N23" s="21" t="s">
+      <c r="O23" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="O23" s="21" t="s">
+      <c r="P23" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="P23" s="21" t="s">
+      <c r="Q23" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="Q23" s="21" t="s">
+      <c r="R23" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -2988,44 +3061,47 @@
       <c r="E24" s="14">
         <v>0</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>45</v>
+      <c r="F24" s="14">
+        <v>0</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="M24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N24" t="s">
         <v>371</v>
       </c>
-      <c r="N24" t="s">
+      <c r="O24" t="s">
         <v>231</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>232</v>
       </c>
-      <c r="P24" t="s">
+      <c r="Q24" t="s">
         <v>224</v>
       </c>
-      <c r="Q24" t="s">
+      <c r="R24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>74</v>
       </c>
@@ -3041,44 +3117,47 @@
       <c r="E25" s="14">
         <v>0</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>45</v>
+      <c r="F25" s="14">
+        <v>0</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="M25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" t="s">
         <v>372</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
         <v>233</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>234</v>
       </c>
-      <c r="P25" t="s">
+      <c r="Q25" t="s">
         <v>224</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="R25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -3094,44 +3173,47 @@
       <c r="E26" s="14">
         <v>0</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>45</v>
+      <c r="F26" s="14">
+        <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M26" t="s">
+      <c r="M26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N26" t="s">
         <v>373</v>
       </c>
-      <c r="N26" t="s">
+      <c r="O26" t="s">
         <v>235</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>236</v>
       </c>
-      <c r="P26" t="s">
+      <c r="Q26" t="s">
         <v>224</v>
       </c>
-      <c r="Q26" t="s">
+      <c r="R26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>76</v>
       </c>
@@ -3147,44 +3229,47 @@
       <c r="E27" s="14">
         <v>0</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>45</v>
+      <c r="F27" s="14">
+        <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M27" t="s">
+      <c r="M27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N27" t="s">
         <v>374</v>
       </c>
-      <c r="N27" t="s">
+      <c r="O27" t="s">
         <v>237</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>238</v>
       </c>
-      <c r="P27" t="s">
+      <c r="Q27" t="s">
         <v>224</v>
       </c>
-      <c r="Q27" t="s">
+      <c r="R27" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>77</v>
       </c>
@@ -3200,44 +3285,47 @@
       <c r="E28" s="14">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>45</v>
+      <c r="F28" s="14">
+        <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M28" t="s">
+      <c r="M28" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N28" t="s">
         <v>375</v>
       </c>
-      <c r="N28" t="s">
+      <c r="O28" t="s">
         <v>239</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>240</v>
       </c>
-      <c r="P28" t="s">
+      <c r="Q28" t="s">
         <v>224</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="R28" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>78</v>
       </c>
@@ -3253,44 +3341,47 @@
       <c r="E29" s="14">
         <v>0</v>
       </c>
-      <c r="F29" s="1" t="s">
-        <v>45</v>
+      <c r="F29" s="14">
+        <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M29" t="s">
+      <c r="M29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" t="s">
         <v>376</v>
       </c>
-      <c r="N29" t="s">
+      <c r="O29" t="s">
         <v>241</v>
       </c>
-      <c r="O29" t="s">
+      <c r="P29" t="s">
         <v>242</v>
       </c>
-      <c r="P29" t="s">
+      <c r="Q29" t="s">
         <v>243</v>
       </c>
-      <c r="Q29" t="s">
+      <c r="R29" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>79</v>
       </c>
@@ -3306,44 +3397,47 @@
       <c r="E30" s="14">
         <v>0</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>45</v>
+      <c r="F30" s="14">
+        <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M30" t="s">
+      <c r="M30" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N30" t="s">
         <v>377</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
         <v>244</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>245</v>
       </c>
-      <c r="P30" t="s">
+      <c r="Q30" t="s">
         <v>243</v>
       </c>
-      <c r="Q30" t="s">
+      <c r="R30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>80</v>
       </c>
@@ -3359,44 +3453,47 @@
       <c r="E31" s="14">
         <v>0</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>45</v>
+      <c r="F31" s="14">
+        <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M31" t="s">
+      <c r="M31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N31" t="s">
         <v>378</v>
       </c>
-      <c r="N31" t="s">
+      <c r="O31" t="s">
         <v>246</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>247</v>
       </c>
-      <c r="P31" t="s">
+      <c r="Q31" t="s">
         <v>243</v>
       </c>
-      <c r="Q31" t="s">
+      <c r="R31" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="21" t="s">
         <v>81</v>
       </c>
@@ -3412,44 +3509,47 @@
       <c r="E32" s="15">
         <v>0</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>45</v>
+      <c r="F32" s="14">
+        <v>0</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I32" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J32" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K32" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="19" t="s">
+      <c r="L32" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="L32" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M32" s="21" t="s">
+      <c r="M32" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N32" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="N32" s="21" t="s">
+      <c r="O32" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="O32" s="21" t="s">
+      <c r="P32" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="P32" s="21" t="s">
+      <c r="Q32" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="Q32" s="21" t="s">
+      <c r="R32" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>82</v>
       </c>
@@ -3465,44 +3565,47 @@
       <c r="E33" s="14">
         <v>0</v>
       </c>
-      <c r="F33" s="1" t="s">
-        <v>45</v>
+      <c r="F33" s="14">
+        <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M33" t="s">
+      <c r="M33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N33" t="s">
         <v>380</v>
       </c>
-      <c r="N33" t="s">
+      <c r="O33" t="s">
         <v>250</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>251</v>
       </c>
-      <c r="P33" t="s">
+      <c r="Q33" t="s">
         <v>243</v>
       </c>
-      <c r="Q33" t="s">
+      <c r="R33" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -3518,44 +3621,47 @@
       <c r="E34" s="14">
         <v>0</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>45</v>
+      <c r="F34" s="14">
+        <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J34" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M34" t="s">
+      <c r="M34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N34" t="s">
         <v>381</v>
       </c>
-      <c r="N34" t="s">
+      <c r="O34" t="s">
         <v>252</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>253</v>
       </c>
-      <c r="P34" t="s">
+      <c r="Q34" t="s">
         <v>243</v>
       </c>
-      <c r="Q34" t="s">
+      <c r="R34" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="21" t="s">
         <v>84</v>
       </c>
@@ -3571,44 +3677,47 @@
       <c r="E35" s="15">
         <v>0</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>45</v>
+      <c r="F35" s="14">
+        <v>0</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I35" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J35" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K35" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K35" s="19" t="s">
+      <c r="L35" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="L35" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M35" s="21" t="s">
+      <c r="M35" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N35" s="21" t="s">
         <v>382</v>
       </c>
-      <c r="N35" s="21" t="s">
+      <c r="O35" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="O35" s="21" t="s">
+      <c r="P35" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="P35" s="21" t="s">
+      <c r="Q35" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="Q35" s="21" t="s">
+      <c r="R35" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>85</v>
       </c>
@@ -3624,44 +3733,47 @@
       <c r="E36" s="14">
         <v>0</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>45</v>
+      <c r="F36" s="14">
+        <v>0</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M36" t="s">
+      <c r="M36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N36" t="s">
         <v>383</v>
       </c>
-      <c r="N36" t="s">
+      <c r="O36" t="s">
         <v>256</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>257</v>
       </c>
-      <c r="P36" t="s">
+      <c r="Q36" t="s">
         <v>243</v>
       </c>
-      <c r="Q36" t="s">
+      <c r="R36" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>86</v>
       </c>
@@ -3677,44 +3789,47 @@
       <c r="E37" s="14">
         <v>0</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>45</v>
+      <c r="F37" s="14">
+        <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M37" t="s">
+      <c r="M37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N37" t="s">
         <v>384</v>
       </c>
-      <c r="N37" t="s">
+      <c r="O37" t="s">
         <v>258</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>259</v>
       </c>
-      <c r="P37" t="s">
+      <c r="Q37" t="s">
         <v>243</v>
       </c>
-      <c r="Q37" t="s">
+      <c r="R37" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -3730,44 +3845,47 @@
       <c r="E38" s="14">
         <v>0</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>45</v>
+      <c r="F38" s="14">
+        <v>0</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="M38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N38" t="s">
         <v>385</v>
       </c>
-      <c r="N38" t="s">
+      <c r="O38" t="s">
         <v>260</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>261</v>
       </c>
-      <c r="P38" t="s">
+      <c r="Q38" t="s">
         <v>243</v>
       </c>
-      <c r="Q38" t="s">
+      <c r="R38" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -3783,44 +3901,47 @@
       <c r="E39" s="14">
         <v>0</v>
       </c>
-      <c r="F39" s="1" t="s">
-        <v>45</v>
+      <c r="F39" s="14">
+        <v>0</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J39" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M39" t="s">
+      <c r="M39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N39" t="s">
         <v>386</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" t="s">
         <v>262</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>263</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>243</v>
       </c>
-      <c r="Q39" t="s">
+      <c r="R39" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -3836,44 +3957,47 @@
       <c r="E40" s="14">
         <v>0</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>45</v>
+      <c r="F40" s="14">
+        <v>0</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M40" t="s">
+      <c r="M40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N40" t="s">
         <v>387</v>
       </c>
-      <c r="N40" t="s">
+      <c r="O40" t="s">
         <v>264</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>265</v>
       </c>
-      <c r="P40" t="s">
+      <c r="Q40" t="s">
         <v>243</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="21" t="s">
         <v>90</v>
       </c>
@@ -3889,44 +4013,47 @@
       <c r="E41" s="15">
         <v>0</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>45</v>
+      <c r="F41" s="14">
+        <v>0</v>
       </c>
       <c r="G41" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I41" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J41" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K41" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K41" s="19" t="s">
+      <c r="L41" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L41" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M41" s="21" t="s">
+      <c r="M41" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="N41" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="N41" s="21" t="s">
+      <c r="O41" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="O41" s="21" t="s">
+      <c r="P41" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="P41" s="21" t="s">
+      <c r="Q41" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="Q41" s="21" t="s">
+      <c r="R41" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -3942,44 +4069,47 @@
       <c r="E42" s="14">
         <v>0</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>45</v>
+      <c r="F42" s="14">
+        <v>0</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M42" t="s">
+      <c r="M42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" t="s">
         <v>389</v>
       </c>
-      <c r="N42" t="s">
+      <c r="O42" t="s">
         <v>269</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>270</v>
       </c>
-      <c r="P42" t="s">
+      <c r="Q42" t="s">
         <v>268</v>
       </c>
-      <c r="Q42" t="s">
+      <c r="R42" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -3995,44 +4125,47 @@
       <c r="E43" s="14">
         <v>0</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>45</v>
+      <c r="F43" s="14">
+        <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M43" t="s">
+      <c r="M43" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N43" t="s">
         <v>390</v>
       </c>
-      <c r="N43" t="s">
+      <c r="O43" t="s">
         <v>271</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>272</v>
       </c>
-      <c r="P43" t="s">
+      <c r="Q43" t="s">
         <v>268</v>
       </c>
-      <c r="Q43" t="s">
+      <c r="R43" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>93</v>
       </c>
@@ -4048,44 +4181,47 @@
       <c r="E44" s="14">
         <v>0</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>45</v>
+      <c r="F44" s="14">
+        <v>0</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J44" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M44" t="s">
+      <c r="M44" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N44" t="s">
         <v>391</v>
       </c>
-      <c r="N44" t="s">
+      <c r="O44" t="s">
         <v>273</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>274</v>
       </c>
-      <c r="P44" t="s">
+      <c r="Q44" t="s">
         <v>268</v>
       </c>
-      <c r="Q44" t="s">
+      <c r="R44" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>94</v>
       </c>
@@ -4101,44 +4237,47 @@
       <c r="E45" s="14">
         <v>0</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>45</v>
+      <c r="F45" s="14">
+        <v>0</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M45" t="s">
+      <c r="M45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N45" t="s">
         <v>392</v>
       </c>
-      <c r="N45" t="s">
+      <c r="O45" t="s">
         <v>275</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>276</v>
       </c>
-      <c r="P45" t="s">
+      <c r="Q45" t="s">
         <v>268</v>
       </c>
-      <c r="Q45" t="s">
+      <c r="R45" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>95</v>
       </c>
@@ -4154,44 +4293,47 @@
       <c r="E46" s="14">
         <v>0</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>45</v>
+      <c r="F46" s="14">
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J46" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L46" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M46" s="4" t="s">
+      <c r="M46" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="N46" s="4" t="s">
+      <c r="O46" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="O46" s="4" t="s">
+      <c r="P46" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="P46" s="4" t="s">
+      <c r="Q46" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="Q46" s="4" t="s">
+      <c r="R46" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
@@ -4207,44 +4349,47 @@
       <c r="E47" s="14">
         <v>0</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>45</v>
+      <c r="F47" s="14">
+        <v>0</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J47" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M47" s="1" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>114</v>
       </c>
       <c r="O47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P47" s="1" t="s">
+      <c r="Q47" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Q47" s="1" t="s">
+      <c r="R47" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
@@ -4260,44 +4405,47 @@
       <c r="E48" s="14">
         <v>0</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>45</v>
+      <c r="F48" s="14">
+        <v>0</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J48" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M48" s="1" t="s">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>118</v>
       </c>
       <c r="O48" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="P48" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P48" s="1" t="s">
+      <c r="Q48" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Q48" s="1" t="s">
+      <c r="R48" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>8</v>
       </c>
@@ -4313,44 +4461,47 @@
       <c r="E49" s="14">
         <v>0</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>45</v>
+      <c r="F49" s="14">
+        <v>0</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M49" s="1" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>119</v>
       </c>
       <c r="O49" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="P49" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="P49" s="1" t="s">
+      <c r="Q49" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="Q49" s="1" t="s">
+      <c r="R49" s="1" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="s">
         <v>9</v>
       </c>
@@ -4366,44 +4517,47 @@
       <c r="E50" s="14">
         <v>0</v>
       </c>
-      <c r="F50" s="7" t="s">
-        <v>45</v>
+      <c r="F50" s="14">
+        <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J50" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K50" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L50" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="M50" s="7" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>120</v>
       </c>
       <c r="O50" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="P50" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="P50" s="7" t="s">
+      <c r="Q50" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="Q50" s="7" t="s">
+      <c r="R50" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>10</v>
       </c>
@@ -4419,44 +4573,47 @@
       <c r="E51" s="14">
         <v>0</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>45</v>
+      <c r="F51" s="14">
+        <v>0</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J51" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M51" s="1" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="N51" s="1" t="s">
         <v>121</v>
       </c>
       <c r="O51" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P51" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P51" s="1" t="s">
+      <c r="Q51" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q51" s="1" t="s">
+      <c r="R51" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>11</v>
       </c>
@@ -4472,44 +4629,47 @@
       <c r="E52" s="14">
         <v>0</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>45</v>
+      <c r="F52" s="14">
+        <v>0</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M52" s="1" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>125</v>
       </c>
       <c r="O52" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P52" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="P52" s="1" t="s">
+      <c r="Q52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="Q52" s="1" t="s">
+      <c r="R52" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
         <v>12</v>
       </c>
@@ -4525,44 +4685,47 @@
       <c r="E53" s="14">
         <v>0</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>45</v>
+      <c r="F53" s="14">
+        <v>0</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I53" s="11" t="s">
         <v>36</v>
       </c>
       <c r="J53" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="K53" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K53" s="1" t="s">
+      <c r="L53" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L53" s="11" t="s">
-        <v>43</v>
-      </c>
       <c r="M53" s="11" t="s">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="N53" s="11" t="s">
         <v>126</v>
       </c>
       <c r="O53" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="P53" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="P53" s="11" t="s">
+      <c r="Q53" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="Q53" s="11" t="s">
+      <c r="R53" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="s">
         <v>347</v>
       </c>
@@ -4578,44 +4741,47 @@
       <c r="E54" s="14">
         <v>0</v>
       </c>
-      <c r="F54" s="7" t="s">
-        <v>45</v>
+      <c r="F54" s="14">
+        <v>0</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J54" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K54" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K54" s="1" t="s">
+      <c r="L54" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L54" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="M54" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="N54" s="7" t="s">
         <v>127</v>
       </c>
       <c r="O54" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="P54" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="P54" s="7" t="s">
+      <c r="Q54" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Q54" s="7" t="s">
+      <c r="R54" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="s">
         <v>13</v>
       </c>
@@ -4631,44 +4797,47 @@
       <c r="E55" s="14">
         <v>1</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>45</v>
+      <c r="F55" s="14">
+        <v>0</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J55" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K55" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K55" s="1" t="s">
+      <c r="L55" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L55" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="M55" s="7" t="s">
-        <v>127</v>
+        <v>43</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>127</v>
       </c>
       <c r="O55" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="P55" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="P55" s="7" t="s">
+      <c r="Q55" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="Q55" s="7" t="s">
+      <c r="R55" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>14</v>
       </c>
@@ -4684,44 +4853,47 @@
       <c r="E56" s="14">
         <v>0</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>45</v>
+      <c r="F56" s="14">
+        <v>0</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J56" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K56" s="1" t="s">
+      <c r="L56" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L56" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M56" s="1" t="s">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="N56" s="1" t="s">
         <v>128</v>
       </c>
       <c r="O56" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="P56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P56" s="1" t="s">
+      <c r="Q56" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Q56" s="1" t="s">
+      <c r="R56" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>15</v>
       </c>
@@ -4737,44 +4909,47 @@
       <c r="E57" s="14">
         <v>0</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>45</v>
+      <c r="F57" s="14">
+        <v>0</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M57" s="1" t="s">
-        <v>132</v>
+        <v>43</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>132</v>
       </c>
       <c r="O57" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="P57" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P57" s="1" t="s">
+      <c r="Q57" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Q57" s="1" t="s">
+      <c r="R57" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>16</v>
       </c>
@@ -4790,44 +4965,47 @@
       <c r="E58" s="14">
         <v>0</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>45</v>
+      <c r="F58" s="14">
+        <v>0</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J58" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K58" s="1" t="s">
+      <c r="L58" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L58" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M58" s="1" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>133</v>
       </c>
       <c r="O58" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P58" s="1" t="s">
+      <c r="Q58" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Q58" s="1" t="s">
+      <c r="R58" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="7" t="s">
         <v>17</v>
       </c>
@@ -4843,44 +5021,47 @@
       <c r="E59" s="14">
         <v>0</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>45</v>
+      <c r="F59" s="14">
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J59" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="K59" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K59" s="1" t="s">
+      <c r="L59" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="M59" s="7" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="N59" s="7" t="s">
         <v>134</v>
       </c>
       <c r="O59" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="P59" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="P59" s="7" t="s">
+      <c r="Q59" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="Q59" s="7" t="s">
+      <c r="R59" s="7" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>18</v>
       </c>
@@ -4896,44 +5077,47 @@
       <c r="E60" s="14">
         <v>0</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>45</v>
+      <c r="F60" s="14">
+        <v>0</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K60" s="1" t="s">
+      <c r="L60" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L60" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M60" s="1" t="s">
-        <v>135</v>
+        <v>43</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>135</v>
       </c>
       <c r="O60" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P60" s="1" t="s">
+      <c r="Q60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="Q60" s="1" t="s">
+      <c r="R60" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A61" s="7" t="s">
         <v>19</v>
       </c>
@@ -4949,44 +5133,47 @@
       <c r="E61" s="14">
         <v>0</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>45</v>
+      <c r="F61" s="14">
+        <v>0</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>38</v>
       </c>
       <c r="J61" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K61" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L61" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="M61" s="7" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>139</v>
       </c>
       <c r="O61" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="P61" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="P61" s="7" t="s">
+      <c r="Q61" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="Q61" s="7" t="s">
+      <c r="R61" s="7" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>21</v>
       </c>
@@ -5002,44 +5189,47 @@
       <c r="E62" s="14">
         <v>0</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G62" s="7" t="s">
+      <c r="H62" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J62" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="L62" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L62" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M62" s="1" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="N62" s="1" t="s">
         <v>141</v>
       </c>
       <c r="O62" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="P62" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="P62" s="1" t="s">
+      <c r="Q62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="Q62" s="1" t="s">
+      <c r="R62" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
@@ -5055,44 +5245,47 @@
       <c r="E63" s="14">
         <v>0</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="H63" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K63" s="1" t="s">
+      <c r="L63" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L63" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M63" s="1" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>144</v>
       </c>
       <c r="O63" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="P63" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="P63" s="1" t="s">
+      <c r="Q63" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="Q63" s="1" t="s">
+      <c r="R63" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>24</v>
       </c>
@@ -5108,44 +5301,47 @@
       <c r="E64" s="14">
         <v>0</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="H64" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J64" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K64" s="1" t="s">
+      <c r="L64" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L64" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M64" s="1" t="s">
-        <v>147</v>
+        <v>43</v>
       </c>
       <c r="N64" s="1" t="s">
         <v>147</v>
       </c>
       <c r="O64" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="P64" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="P64" s="1" t="s">
+      <c r="Q64" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Q64" s="1" t="s">
+      <c r="R64" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
         <v>25</v>
       </c>
@@ -5161,44 +5357,47 @@
       <c r="E65" s="14">
         <v>1</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G65" s="16" t="s">
+      <c r="H65" s="16" t="s">
         <v>398</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="I65" s="11" t="s">
         <v>346</v>
       </c>
       <c r="J65" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="K65" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="L65" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L65" s="11" t="s">
+      <c r="M65" s="11" t="s">
         <v>399</v>
-      </c>
-      <c r="M65" s="11" t="s">
-        <v>150</v>
       </c>
       <c r="N65" s="11" t="s">
         <v>150</v>
       </c>
       <c r="O65" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="P65" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="P65" s="11" t="s">
+      <c r="Q65" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="Q65" s="11" t="s">
+      <c r="R65" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>26</v>
       </c>
@@ -5214,44 +5413,47 @@
       <c r="E66" s="14">
         <v>0</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="H66" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J66" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K66" s="1" t="s">
+      <c r="L66" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L66" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M66" s="1" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>153</v>
       </c>
       <c r="O66" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="P66" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="P66" s="1" t="s">
+      <c r="Q66" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="Q66" s="1" t="s">
+      <c r="R66" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>27</v>
       </c>
@@ -5267,44 +5469,47 @@
       <c r="E67" s="14">
         <v>0</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="H67" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J67" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K67" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K67" s="1" t="s">
+      <c r="L67" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L67" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M67" s="1" t="s">
-        <v>156</v>
+        <v>43</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>156</v>
       </c>
       <c r="O67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="P67" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="P67" s="1" t="s">
+      <c r="Q67" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="Q67" s="1" t="s">
+      <c r="R67" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>28</v>
       </c>
@@ -5320,44 +5525,47 @@
       <c r="E68" s="14">
         <v>0</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G68" s="7" t="s">
+      <c r="H68" s="7" t="s">
         <v>398</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J68" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K68" s="1" t="s">
+      <c r="L68" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L68" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M68" s="1" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>159</v>
       </c>
       <c r="O68" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="P68" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="P68" s="1" t="s">
+      <c r="Q68" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="Q68" s="1" t="s">
+      <c r="R68" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
         <v>29</v>
       </c>
@@ -5373,44 +5581,47 @@
       <c r="E69" s="14">
         <v>1</v>
       </c>
-      <c r="F69" s="17" t="s">
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="H69" s="17" t="s">
         <v>398</v>
-      </c>
-      <c r="H69" s="11" t="s">
-        <v>346</v>
       </c>
       <c r="I69" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="J69" s="17" t="s">
+      <c r="J69" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="K69" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="K69" s="1" t="s">
+      <c r="L69" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L69" s="17" t="s">
+      <c r="M69" s="17" t="s">
         <v>399</v>
-      </c>
-      <c r="M69" s="17" t="s">
-        <v>162</v>
       </c>
       <c r="N69" s="17" t="s">
         <v>162</v>
       </c>
       <c r="O69" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="P69" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="P69" s="17" t="s">
+      <c r="Q69" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="Q69" s="17" t="s">
+      <c r="R69" s="17" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>30</v>
       </c>
@@ -5426,44 +5637,47 @@
       <c r="E70" s="14">
         <v>0</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>45</v>
+      <c r="F70" s="14">
+        <v>0</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J70" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K70" s="1" t="s">
+      <c r="L70" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L70" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M70" s="1" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>165</v>
       </c>
       <c r="O70" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="P70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P70" s="1" t="s">
+      <c r="Q70" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="Q70" s="1" t="s">
+      <c r="R70" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>31</v>
       </c>
@@ -5479,44 +5693,47 @@
       <c r="E71" s="14">
         <v>0</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>45</v>
+      <c r="F71" s="14">
+        <v>0</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>38</v>
       </c>
       <c r="J71" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K71" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K71" s="1" t="s">
+      <c r="L71" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L71" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="M71" s="1" t="s">
-        <v>168</v>
+        <v>43</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>168</v>
       </c>
       <c r="O71" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="P71" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P71" s="1" t="s">
+      <c r="Q71" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="Q71" s="1" t="s">
+      <c r="R71" s="1" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="s">
         <v>97</v>
       </c>
@@ -5532,44 +5749,47 @@
       <c r="E72" s="14">
         <v>0</v>
       </c>
-      <c r="F72" s="7" t="s">
-        <v>45</v>
+      <c r="F72" s="14">
+        <v>0</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H72" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J72" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K72" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="K72" s="1" t="s">
+      <c r="L72" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L72" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>171</v>
+      <c r="M72" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="N72" s="4" t="s">
         <v>171</v>
       </c>
       <c r="O72" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="P72" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="P72" s="4" t="s">
+      <c r="Q72" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="Q72" s="7" t="s">
+      <c r="R72" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>98</v>
       </c>
@@ -5585,44 +5805,47 @@
       <c r="E73" s="14">
         <v>0</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>45</v>
+      <c r="F73" s="14">
+        <v>0</v>
       </c>
       <c r="G73" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I73" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K73" s="1" t="s">
+      <c r="L73" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L73" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M73" t="s">
-        <v>174</v>
+      <c r="M73" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N73" t="s">
         <v>174</v>
       </c>
       <c r="O73" t="s">
+        <v>174</v>
+      </c>
+      <c r="P73" t="s">
         <v>175</v>
       </c>
-      <c r="P73" t="s">
+      <c r="Q73" t="s">
         <v>176</v>
       </c>
-      <c r="Q73" s="1" t="s">
+      <c r="R73" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>99</v>
       </c>
@@ -5638,44 +5861,47 @@
       <c r="E74" s="14">
         <v>0</v>
       </c>
-      <c r="F74" s="1" t="s">
-        <v>45</v>
+      <c r="F74" s="14">
+        <v>0</v>
       </c>
       <c r="G74" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I74" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J74" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="L74" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L74" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M74" t="s">
-        <v>177</v>
+      <c r="M74" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N74" t="s">
         <v>177</v>
       </c>
       <c r="O74" t="s">
+        <v>177</v>
+      </c>
+      <c r="P74" t="s">
         <v>175</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q74" t="s">
         <v>176</v>
       </c>
-      <c r="Q74" s="1" t="s">
+      <c r="R74" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="21" t="s">
         <v>100</v>
       </c>
@@ -5691,44 +5917,47 @@
       <c r="E75" s="15">
         <v>0</v>
       </c>
-      <c r="F75" s="19" t="s">
-        <v>45</v>
+      <c r="F75" s="14">
+        <v>0</v>
       </c>
       <c r="G75" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H75" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H75" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="I75" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J75" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K75" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K75" s="19" t="s">
+      <c r="L75" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L75" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M75" s="21" t="s">
-        <v>178</v>
+      <c r="M75" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N75" s="21" t="s">
         <v>178</v>
       </c>
       <c r="O75" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="P75" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="P75" s="21" t="s">
+      <c r="Q75" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="Q75" s="19" t="s">
+      <c r="R75" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>101</v>
       </c>
@@ -5744,44 +5973,47 @@
       <c r="E76" s="14">
         <v>0</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>45</v>
+      <c r="F76" s="14">
+        <v>0</v>
       </c>
       <c r="G76" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I76" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J76" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K76" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K76" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L76" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M76" t="s">
-        <v>179</v>
+      <c r="M76" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N76" t="s">
         <v>179</v>
       </c>
       <c r="O76" t="s">
+        <v>179</v>
+      </c>
+      <c r="P76" t="s">
         <v>180</v>
       </c>
-      <c r="P76" t="s">
+      <c r="Q76" t="s">
         <v>300</v>
       </c>
-      <c r="Q76" s="1" t="s">
+      <c r="R76" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -5797,44 +6029,47 @@
       <c r="E77" s="14">
         <v>0</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>45</v>
+      <c r="F77" s="14">
+        <v>0</v>
       </c>
       <c r="G77" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H77" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I77" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J77" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K77" s="1" t="s">
+      <c r="L77" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M77" t="s">
-        <v>182</v>
+      <c r="M77" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N77" t="s">
         <v>182</v>
       </c>
       <c r="O77" t="s">
+        <v>182</v>
+      </c>
+      <c r="P77" t="s">
         <v>180</v>
       </c>
-      <c r="P77" t="s">
+      <c r="Q77" t="s">
         <v>181</v>
       </c>
-      <c r="Q77" s="1" t="s">
+      <c r="R77" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="21" t="s">
         <v>103</v>
       </c>
@@ -5850,44 +6085,47 @@
       <c r="E78" s="15">
         <v>0</v>
       </c>
-      <c r="F78" s="19" t="s">
-        <v>45</v>
+      <c r="F78" s="14">
+        <v>0</v>
       </c>
       <c r="G78" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H78" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H78" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="I78" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J78" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K78" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K78" s="19" t="s">
+      <c r="L78" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L78" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M78" s="21" t="s">
-        <v>183</v>
+      <c r="M78" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N78" s="21" t="s">
         <v>183</v>
       </c>
       <c r="O78" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="P78" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="P78" s="21" t="s">
+      <c r="Q78" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="Q78" s="19" t="s">
+      <c r="R78" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>104</v>
       </c>
@@ -5903,44 +6141,47 @@
       <c r="E79" s="14">
         <v>0</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>45</v>
+      <c r="F79" s="14">
+        <v>0</v>
       </c>
       <c r="G79" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H79" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I79" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J79" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="L79" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L79" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M79" t="s">
-        <v>307</v>
+      <c r="M79" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N79" t="s">
         <v>307</v>
       </c>
       <c r="O79" t="s">
+        <v>307</v>
+      </c>
+      <c r="P79" t="s">
         <v>310</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q79" t="s">
         <v>306</v>
       </c>
-      <c r="Q79" s="1" t="s">
+      <c r="R79" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>105</v>
       </c>
@@ -5956,44 +6197,47 @@
       <c r="E80" s="14">
         <v>0</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>45</v>
+      <c r="F80" s="14">
+        <v>0</v>
       </c>
       <c r="G80" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H80" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H80" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I80" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J80" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K80" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K80" s="1" t="s">
+      <c r="L80" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L80" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M80" t="s">
-        <v>308</v>
+      <c r="M80" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N80" t="s">
         <v>308</v>
       </c>
       <c r="O80" t="s">
+        <v>308</v>
+      </c>
+      <c r="P80" t="s">
         <v>310</v>
       </c>
-      <c r="P80" t="s">
+      <c r="Q80" t="s">
         <v>306</v>
       </c>
-      <c r="Q80" s="1" t="s">
+      <c r="R80" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>106</v>
       </c>
@@ -6009,44 +6253,47 @@
       <c r="E81" s="15">
         <v>0</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>45</v>
+      <c r="F81" s="14">
+        <v>0</v>
       </c>
       <c r="G81" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H81" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H81" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="I81" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J81" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K81" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K81" s="19" t="s">
+      <c r="L81" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L81" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M81" s="21" t="s">
-        <v>309</v>
+      <c r="M81" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N81" s="21" t="s">
         <v>309</v>
       </c>
       <c r="O81" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="P81" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="P81" s="21" t="s">
+      <c r="Q81" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="Q81" s="19" t="s">
+      <c r="R81" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>287</v>
       </c>
@@ -6062,44 +6309,47 @@
       <c r="E82" s="14">
         <v>0</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>45</v>
+      <c r="F82" s="14">
+        <v>0</v>
       </c>
       <c r="G82" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H82" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H82" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I82" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K82" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K82" s="1" t="s">
+      <c r="L82" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L82" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M82" t="s">
-        <v>302</v>
+      <c r="M82" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N82" t="s">
         <v>302</v>
       </c>
       <c r="O82" t="s">
+        <v>302</v>
+      </c>
+      <c r="P82" t="s">
         <v>301</v>
       </c>
-      <c r="P82" t="s">
+      <c r="Q82" t="s">
         <v>305</v>
       </c>
-      <c r="Q82" s="1" t="s">
+      <c r="R82" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>288</v>
       </c>
@@ -6115,44 +6365,47 @@
       <c r="E83" s="14">
         <v>0</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>45</v>
+      <c r="F83" s="14">
+        <v>0</v>
       </c>
       <c r="G83" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H83" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H83" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I83" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J83" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K83" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K83" s="1" t="s">
+      <c r="L83" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L83" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M83" t="s">
-        <v>303</v>
+      <c r="M83" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N83" t="s">
         <v>303</v>
       </c>
       <c r="O83" t="s">
+        <v>303</v>
+      </c>
+      <c r="P83" t="s">
         <v>301</v>
       </c>
-      <c r="P83" t="s">
+      <c r="Q83" t="s">
         <v>305</v>
       </c>
-      <c r="Q83" s="1" t="s">
+      <c r="R83" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="21" t="s">
         <v>289</v>
       </c>
@@ -6168,44 +6421,47 @@
       <c r="E84" s="15">
         <v>0</v>
       </c>
-      <c r="F84" s="19" t="s">
-        <v>45</v>
+      <c r="F84" s="14">
+        <v>0</v>
       </c>
       <c r="G84" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H84" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H84" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="I84" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J84" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K84" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K84" s="19" t="s">
+      <c r="L84" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L84" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M84" s="21" t="s">
-        <v>304</v>
+      <c r="M84" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N84" s="21" t="s">
         <v>304</v>
       </c>
       <c r="O84" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="P84" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="P84" s="21" t="s">
+      <c r="Q84" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="Q84" s="19" t="s">
+      <c r="R84" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>107</v>
       </c>
@@ -6221,44 +6477,47 @@
       <c r="E85" s="14">
         <v>0</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>45</v>
+      <c r="F85" s="14">
+        <v>0</v>
       </c>
       <c r="G85" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H85" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I85" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K85" s="1" t="s">
+      <c r="L85" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L85" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M85" t="s">
-        <v>290</v>
+      <c r="M85" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N85" t="s">
         <v>290</v>
       </c>
       <c r="O85" t="s">
+        <v>290</v>
+      </c>
+      <c r="P85" t="s">
         <v>293</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q85" t="s">
         <v>294</v>
       </c>
-      <c r="Q85" s="1" t="s">
+      <c r="R85" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>108</v>
       </c>
@@ -6274,44 +6533,47 @@
       <c r="E86" s="14">
         <v>0</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>45</v>
+      <c r="F86" s="14">
+        <v>0</v>
       </c>
       <c r="G86" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H86" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I86" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J86" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K86" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K86" s="1" t="s">
+      <c r="L86" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L86" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M86" t="s">
-        <v>291</v>
+      <c r="M86" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N86" t="s">
         <v>291</v>
       </c>
       <c r="O86" t="s">
+        <v>291</v>
+      </c>
+      <c r="P86" t="s">
         <v>293</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q86" t="s">
         <v>294</v>
       </c>
-      <c r="Q86" s="1" t="s">
+      <c r="R86" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="21" t="s">
         <v>109</v>
       </c>
@@ -6327,44 +6589,47 @@
       <c r="E87" s="15">
         <v>0</v>
       </c>
-      <c r="F87" s="19" t="s">
-        <v>45</v>
+      <c r="F87" s="14">
+        <v>0</v>
       </c>
       <c r="G87" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H87" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I87" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J87" s="19" t="s">
+      <c r="J87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K87" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K87" s="19" t="s">
+      <c r="L87" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L87" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M87" s="21" t="s">
-        <v>292</v>
+      <c r="M87" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N87" s="21" t="s">
         <v>292</v>
       </c>
       <c r="O87" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="P87" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="P87" s="21" t="s">
+      <c r="Q87" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="Q87" s="19" t="s">
+      <c r="R87" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>110</v>
       </c>
@@ -6380,44 +6645,47 @@
       <c r="E88" s="14">
         <v>0</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>45</v>
+      <c r="F88" s="14">
+        <v>0</v>
       </c>
       <c r="G88" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H88" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I88" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J88" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K88" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K88" s="1" t="s">
+      <c r="L88" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L88" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M88" t="s">
-        <v>296</v>
+      <c r="M88" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N88" t="s">
         <v>296</v>
       </c>
       <c r="O88" t="s">
+        <v>296</v>
+      </c>
+      <c r="P88" t="s">
         <v>295</v>
       </c>
-      <c r="P88" t="s">
+      <c r="Q88" t="s">
         <v>299</v>
       </c>
-      <c r="Q88" s="1" t="s">
+      <c r="R88" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>111</v>
       </c>
@@ -6433,44 +6701,47 @@
       <c r="E89" s="14">
         <v>0</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>45</v>
+      <c r="F89" s="14">
+        <v>0</v>
       </c>
       <c r="G89" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="I89" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K89" s="1" t="s">
+      <c r="L89" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L89" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M89" t="s">
-        <v>297</v>
+      <c r="M89" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N89" t="s">
         <v>297</v>
       </c>
       <c r="O89" t="s">
+        <v>297</v>
+      </c>
+      <c r="P89" t="s">
         <v>295</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q89" t="s">
         <v>299</v>
       </c>
-      <c r="Q89" s="1" t="s">
+      <c r="R89" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" s="23" t="s">
         <v>112</v>
       </c>
@@ -6486,44 +6757,47 @@
       <c r="E90" s="15">
         <v>0</v>
       </c>
-      <c r="F90" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G90" s="19" t="s">
+      <c r="F90" s="14">
+        <v>0</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H90" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="H90" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="I90" s="16" t="s">
+      <c r="I90" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J90" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K90" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="K90" s="19" t="s">
+      <c r="L90" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L90" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M90" s="23" t="s">
-        <v>298</v>
+      <c r="M90" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="N90" s="23" t="s">
         <v>298</v>
       </c>
       <c r="O90" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="P90" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="P90" s="23" t="s">
+      <c r="Q90" s="23" t="s">
         <v>299</v>
       </c>
-      <c r="Q90" s="16" t="s">
+      <c r="R90" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="21" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" s="21" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="21" t="s">
         <v>281</v>
       </c>
@@ -6539,44 +6813,47 @@
       <c r="E91" s="15">
         <v>0</v>
       </c>
-      <c r="F91" s="19" t="s">
-        <v>45</v>
+      <c r="F91" s="14">
+        <v>0</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I91" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J91" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K91" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K91" s="19" t="s">
+      <c r="L91" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L91" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M91" s="21" t="s">
-        <v>284</v>
+      <c r="M91" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N91" s="21" t="s">
         <v>284</v>
       </c>
       <c r="O91" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="P91" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="P91" s="21" t="s">
+      <c r="Q91" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="Q91" s="19" t="s">
+      <c r="R91" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="20" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" s="20" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="20" t="s">
         <v>282</v>
       </c>
@@ -6592,44 +6869,47 @@
       <c r="E92" s="15">
         <v>0</v>
       </c>
-      <c r="F92" s="16" t="s">
-        <v>45</v>
+      <c r="F92" s="14">
+        <v>0</v>
       </c>
       <c r="G92" s="16" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H92" s="16" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I92" s="16" t="s">
         <v>35</v>
       </c>
       <c r="J92" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K92" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="K92" s="19" t="s">
+      <c r="L92" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L92" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="M92" s="20" t="s">
-        <v>285</v>
+      <c r="M92" s="16" t="s">
+        <v>43</v>
       </c>
       <c r="N92" s="20" t="s">
         <v>285</v>
       </c>
       <c r="O92" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="P92" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="P92" s="20" t="s">
+      <c r="Q92" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="Q92" s="16" t="s">
+      <c r="R92" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" s="25" t="s">
         <v>312</v>
       </c>
@@ -6645,44 +6925,47 @@
       <c r="E93" s="15">
         <v>0</v>
       </c>
-      <c r="F93" s="19" t="s">
-        <v>45</v>
+      <c r="F93" s="14">
+        <v>0</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I93" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J93" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K93" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K93" s="19" t="s">
+      <c r="L93" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L93" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M93" s="13" t="s">
-        <v>321</v>
+      <c r="M93" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N93" s="13" t="s">
         <v>321</v>
       </c>
       <c r="O93" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="P93" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="P93" s="13" t="s">
+      <c r="Q93" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="Q93" s="19" t="s">
+      <c r="R93" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="8" t="s">
         <v>313</v>
       </c>
@@ -6698,44 +6981,47 @@
       <c r="E94" s="14">
         <v>0</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>45</v>
+      <c r="F94" s="14">
+        <v>0</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J94" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K94" s="1" t="s">
+      <c r="L94" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L94" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M94" t="s">
-        <v>322</v>
+      <c r="M94" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N94" t="s">
         <v>322</v>
       </c>
       <c r="O94" t="s">
+        <v>322</v>
+      </c>
+      <c r="P94" t="s">
         <v>318</v>
       </c>
-      <c r="P94" t="s">
+      <c r="Q94" t="s">
         <v>327</v>
       </c>
-      <c r="Q94" s="1" t="s">
+      <c r="R94" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A95" s="25" t="s">
         <v>314</v>
       </c>
@@ -6751,44 +7037,47 @@
       <c r="E95" s="15">
         <v>0</v>
       </c>
-      <c r="F95" s="19" t="s">
-        <v>45</v>
+      <c r="F95" s="14">
+        <v>0</v>
       </c>
       <c r="G95" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H95" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I95" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J95" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K95" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K95" s="19" t="s">
+      <c r="L95" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L95" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M95" s="13" t="s">
-        <v>323</v>
+      <c r="M95" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N95" s="13" t="s">
         <v>323</v>
       </c>
       <c r="O95" s="13" t="s">
+        <v>323</v>
+      </c>
+      <c r="P95" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="P95" s="13" t="s">
+      <c r="Q95" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="Q95" s="19" t="s">
+      <c r="R95" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="8" t="s">
         <v>315</v>
       </c>
@@ -6804,44 +7093,47 @@
       <c r="E96" s="14">
         <v>0</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>45</v>
+      <c r="F96" s="14">
+        <v>0</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H96" s="1" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J96" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K96" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K96" s="1" t="s">
+      <c r="L96" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L96" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M96" t="s">
-        <v>324</v>
+      <c r="M96" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="N96" t="s">
         <v>324</v>
       </c>
       <c r="O96" t="s">
+        <v>324</v>
+      </c>
+      <c r="P96" t="s">
         <v>319</v>
       </c>
-      <c r="P96" t="s">
+      <c r="Q96" t="s">
         <v>327</v>
       </c>
-      <c r="Q96" s="1" t="s">
+      <c r="R96" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="25" t="s">
         <v>316</v>
       </c>
@@ -6857,44 +7149,47 @@
       <c r="E97" s="15">
         <v>0</v>
       </c>
-      <c r="F97" s="19" t="s">
-        <v>45</v>
+      <c r="F97" s="14">
+        <v>0</v>
       </c>
       <c r="G97" s="19" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H97" s="19" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I97" s="19" t="s">
         <v>35</v>
       </c>
       <c r="J97" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K97" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="K97" s="19" t="s">
+      <c r="L97" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="L97" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="M97" s="13" t="s">
-        <v>325</v>
+      <c r="M97" s="19" t="s">
+        <v>43</v>
       </c>
       <c r="N97" s="13" t="s">
         <v>325</v>
       </c>
       <c r="O97" s="13" t="s">
+        <v>325</v>
+      </c>
+      <c r="P97" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="P97" s="13" t="s">
+      <c r="Q97" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="Q97" s="19" t="s">
+      <c r="R97" s="19" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" s="9" t="s">
         <v>317</v>
       </c>
@@ -6910,44 +7205,47 @@
       <c r="E98" s="14">
         <v>0</v>
       </c>
-      <c r="F98" s="7" t="s">
-        <v>45</v>
+      <c r="F98" s="14">
+        <v>0</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>35</v>
       </c>
       <c r="J98" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K98" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="L98" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L98" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M98" s="4" t="s">
-        <v>326</v>
+      <c r="M98" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="N98" s="4" t="s">
         <v>326</v>
       </c>
       <c r="O98" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="P98" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="P98" s="4" t="s">
+      <c r="Q98" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="Q98" s="7" t="s">
+      <c r="R98" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>328</v>
       </c>
@@ -6963,44 +7261,47 @@
       <c r="E99" s="14">
         <v>0</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>45</v>
+      <c r="F99" s="14">
+        <v>0</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>346</v>
+        <v>48</v>
       </c>
       <c r="I99" s="10" t="s">
         <v>346</v>
       </c>
       <c r="J99" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="K99" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="L99" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L99" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M99" t="s">
-        <v>335</v>
+      <c r="M99" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N99" t="s">
         <v>335</v>
       </c>
       <c r="O99" t="s">
+        <v>335</v>
+      </c>
+      <c r="P99" t="s">
         <v>334</v>
       </c>
-      <c r="P99" t="s">
+      <c r="Q99" t="s">
         <v>343</v>
       </c>
-      <c r="Q99" s="1" t="s">
+      <c r="R99" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>329</v>
       </c>
@@ -7016,44 +7317,47 @@
       <c r="E100" s="14">
         <v>0</v>
       </c>
-      <c r="F100" s="10" t="s">
-        <v>45</v>
+      <c r="F100" s="14">
+        <v>0</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H100" s="10" t="s">
-        <v>346</v>
+        <v>48</v>
       </c>
       <c r="I100" s="10" t="s">
         <v>346</v>
       </c>
       <c r="J100" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="K100" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="L100" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L100" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M100" t="s">
-        <v>336</v>
+      <c r="M100" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N100" t="s">
         <v>336</v>
       </c>
       <c r="O100" t="s">
+        <v>336</v>
+      </c>
+      <c r="P100" t="s">
         <v>334</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q100" t="s">
         <v>343</v>
       </c>
-      <c r="Q100" s="1" t="s">
+      <c r="R100" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>330</v>
       </c>
@@ -7069,44 +7373,47 @@
       <c r="E101" s="14">
         <v>0</v>
       </c>
-      <c r="F101" s="10" t="s">
-        <v>45</v>
+      <c r="F101" s="14">
+        <v>0</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="I101" s="10" t="s">
         <v>402</v>
       </c>
       <c r="J101" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="K101" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="L101" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L101" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M101" t="s">
-        <v>338</v>
+      <c r="M101" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N101" t="s">
         <v>338</v>
       </c>
       <c r="O101" t="s">
+        <v>338</v>
+      </c>
+      <c r="P101" t="s">
         <v>337</v>
       </c>
-      <c r="P101" t="s">
+      <c r="Q101" t="s">
         <v>344</v>
       </c>
-      <c r="Q101" s="1" t="s">
+      <c r="R101" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>331</v>
       </c>
@@ -7122,44 +7429,47 @@
       <c r="E102" s="14">
         <v>0</v>
       </c>
-      <c r="F102" s="10" t="s">
-        <v>45</v>
+      <c r="F102" s="14">
+        <v>0</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="I102" s="10" t="s">
         <v>402</v>
       </c>
       <c r="J102" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="K102" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="L102" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L102" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M102" t="s">
-        <v>339</v>
+      <c r="M102" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N102" t="s">
         <v>339</v>
       </c>
       <c r="O102" t="s">
+        <v>339</v>
+      </c>
+      <c r="P102" t="s">
         <v>337</v>
       </c>
-      <c r="P102" t="s">
+      <c r="Q102" t="s">
         <v>344</v>
       </c>
-      <c r="Q102" s="1" t="s">
+      <c r="R102" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>332</v>
       </c>
@@ -7175,44 +7485,47 @@
       <c r="E103" s="14">
         <v>0</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>45</v>
+      <c r="F103" s="14">
+        <v>0</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H103" s="10" t="s">
-        <v>403</v>
+        <v>48</v>
       </c>
       <c r="I103" s="10" t="s">
         <v>403</v>
       </c>
       <c r="J103" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="K103" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="L103" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L103" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M103" t="s">
-        <v>341</v>
+      <c r="M103" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N103" t="s">
         <v>341</v>
       </c>
       <c r="O103" t="s">
+        <v>341</v>
+      </c>
+      <c r="P103" t="s">
         <v>340</v>
       </c>
-      <c r="P103" t="s">
+      <c r="Q103" t="s">
         <v>345</v>
       </c>
-      <c r="Q103" s="1" t="s">
+      <c r="R103" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>333</v>
       </c>
@@ -7228,40 +7541,43 @@
       <c r="E104" s="14">
         <v>0</v>
       </c>
-      <c r="F104" s="10" t="s">
-        <v>45</v>
+      <c r="F104" s="14">
+        <v>1</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H104" s="10" t="s">
-        <v>403</v>
+        <v>48</v>
       </c>
       <c r="I104" s="10" t="s">
         <v>403</v>
       </c>
       <c r="J104" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="K104" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="L104" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="L104" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M104" t="s">
-        <v>342</v>
+      <c r="M104" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="N104" t="s">
         <v>342</v>
       </c>
       <c r="O104" t="s">
+        <v>342</v>
+      </c>
+      <c r="P104" t="s">
         <v>340</v>
       </c>
-      <c r="P104" t="s">
+      <c r="Q104" t="s">
         <v>345</v>
       </c>
-      <c r="Q104" s="1" t="s">
+      <c r="R104" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/datasets_train.xlsx
+++ b/datasets_train.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\qiqilu\Project\2023 cytoSR\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58673F7A-C9FC-4E2A-A02C-A09169844A17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC63E06C-9587-4A1A-B651-2385AD25F177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1575" yWindow="5025" windowWidth="21570" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9495" yWindow="3150" windowWidth="18885" windowHeight="16170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1751,7 +1751,7 @@
     <col min="10" max="11" width="10.25" style="1" customWidth="1"/>
     <col min="12" max="12" width="10.125" style="1" customWidth="1"/>
     <col min="13" max="13" width="9.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="42.625" customWidth="1"/>
+    <col min="14" max="14" width="54.75" customWidth="1"/>
     <col min="15" max="15" width="99.625" customWidth="1"/>
     <col min="16" max="16" width="111.125" customWidth="1"/>
     <col min="17" max="17" width="11.875" customWidth="1"/>
